--- a/data/rateBuildUp/File1/RPT_RPT8588219622925VG_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT8588219622925VG_rateBuildUp.xlsx
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="C11" s="369" t="n">
-        <v>46576674.63854355</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="D11" s="368" t="n">
-        <v>53430343.59559114</v>
+        <v>53430343.59559113</v>
       </c>
       <c r="E11" s="368" t="n">
         <v>60385901.22126447</v>
@@ -2970,7 +2970,7 @@
         <v>77027357.53180352</v>
       </c>
       <c r="H11" s="371" t="n">
-        <v>297.2181477908225</v>
+        <v>285.985451492463</v>
       </c>
       <c r="I11" s="372" t="n">
         <v>325.0610632735838</v>
@@ -2985,7 +2985,7 @@
         <v>391.0995684445464</v>
       </c>
       <c r="M11" s="371" t="n">
-        <v>36.83999773386718</v>
+        <v>35.44771227198476</v>
       </c>
       <c r="N11" s="372" t="n">
         <v>41.57241017461948</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="T11" s="374" t="n">
-        <v>46576674.63854355</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="U11" s="375" t="n">
-        <v>53430343.59559114</v>
+        <v>53430343.59559113</v>
       </c>
       <c r="V11" s="375" t="n">
         <v>60385901.22126447</v>
@@ -3020,7 +3020,7 @@
         <v>77027357.53180352</v>
       </c>
       <c r="Y11" s="377" t="n">
-        <v>297.2181477908225</v>
+        <v>285.985451492463</v>
       </c>
       <c r="Z11" s="372" t="n">
         <v>325.0610632735838</v>
@@ -3035,7 +3035,7 @@
         <v>391.0995684445464</v>
       </c>
       <c r="AD11" s="377" t="n">
-        <v>36.83999773386718</v>
+        <v>35.44771227198476</v>
       </c>
       <c r="AE11" s="372" t="n">
         <v>41.57241017461948</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="AK11" s="379" t="n">
-        <v>46576674.63854355</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="AL11" s="368" t="n">
-        <v>53430343.59559114</v>
+        <v>53430343.59559113</v>
       </c>
       <c r="AM11" s="368" t="n">
         <v>60385901.22126447</v>
@@ -3070,10 +3070,10 @@
         <v>77027357.53180352</v>
       </c>
       <c r="AP11" s="381" t="n">
-        <v>297.2366573077144</v>
+        <v>286.0032614834901</v>
       </c>
       <c r="AQ11" s="372" t="n">
-        <v>325.0851884256385</v>
+        <v>325.0851884256384</v>
       </c>
       <c r="AR11" s="372" t="n">
         <v>349.5678434310159</v>
@@ -3085,10 +3085,10 @@
         <v>391.141430041976</v>
       </c>
       <c r="AU11" s="372" t="n">
-        <v>36.84028208826756</v>
+        <v>35.44798587984546</v>
       </c>
       <c r="AV11" s="372" t="n">
-        <v>41.57280474314827</v>
+        <v>41.57280474314826</v>
       </c>
       <c r="AW11" s="372" t="n">
         <v>46.27996769100665</v>
@@ -3105,13 +3105,13 @@
         </is>
       </c>
       <c r="BB11" s="383" t="n">
-        <v>48790680.66857278</v>
+        <v>46942406.17078204</v>
       </c>
       <c r="BC11" s="384" t="n">
-        <v>57940652.86013988</v>
+        <v>57940652.86013987</v>
       </c>
       <c r="BD11" s="384" t="n">
-        <v>67404504.6677935</v>
+        <v>67404504.66779351</v>
       </c>
       <c r="BE11" s="384" t="n">
         <v>77991280.33764645</v>
@@ -3120,13 +3120,13 @@
         <v>90998246.02856025</v>
       </c>
       <c r="BG11" s="386" t="n">
-        <v>311.3656984368213</v>
+        <v>299.5706328213858</v>
       </c>
       <c r="BH11" s="372" t="n">
         <v>352.5271743544865</v>
       </c>
       <c r="BI11" s="372" t="n">
-        <v>390.1978252824199</v>
+        <v>390.19782528242</v>
       </c>
       <c r="BJ11" s="372" t="n">
         <v>425.491874729779</v>
@@ -3135,13 +3135,13 @@
         <v>462.0849685545385</v>
       </c>
       <c r="BL11" s="388" t="n">
-        <v>38.59147208464196</v>
+        <v>37.12956106579875</v>
       </c>
       <c r="BM11" s="389" t="n">
         <v>45.08216279267744</v>
       </c>
       <c r="BN11" s="389" t="n">
-        <v>51.65905012866294</v>
+        <v>51.65905012866295</v>
       </c>
       <c r="BO11" s="389" t="n">
         <v>58.91512584299631</v>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.20939991</v>
       </c>
       <c r="BT11" s="375" t="n">
         <v>58312864.66497568</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>68266434.39100204</v>
+        <v>68266434.39100206</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>79412930.37978917</v>
@@ -3170,13 +3170,13 @@
         <v>93082485.59376031</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>309.2209694257514</v>
+        <v>297.5317153231277</v>
       </c>
       <c r="BY11" s="372" t="n">
         <v>350.2537801471804</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>387.8149181787844</v>
+        <v>387.8149181787845</v>
       </c>
       <c r="CA11" s="372" t="n">
         <v>422.9702052615251</v>
@@ -3185,7 +3185,7 @@
         <v>459.4487048068605</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>38.62868829423051</v>
+        <v>37.16843624870832</v>
       </c>
       <c r="CD11" s="389" t="n">
         <v>45.44826524829572</v>
@@ -3200,7 +3200,7 @@
         <v>69.20346589917921</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>2.144729011069956</v>
+        <v>2.038917498258115</v>
       </c>
       <c r="CX11" s="92" t="n">
         <v>2.273394207306183</v>
@@ -3215,7 +3215,7 @@
         <v>2.636263747678015</v>
       </c>
       <c r="DC11" s="393" t="n">
-        <v>0.01509919443924005</v>
+        <v>0.01501787004944703</v>
       </c>
       <c r="DD11" s="394" t="n">
         <v>0.01518172965937269</v>
@@ -3224,10 +3224,10 @@
         <v>0.01534942786781859</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.01557349634666997</v>
+        <v>0.01557349634666996</v>
       </c>
       <c r="DG11" s="395" t="n">
-        <v>0.01563046446487637</v>
+        <v>0.01563046446487636</v>
       </c>
     </row>
     <row r="12">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="C12" s="369" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="D12" s="368" t="n">
-        <v>19183612.89511096</v>
+        <v>19183612.89511097</v>
       </c>
       <c r="E12" s="368" t="n">
         <v>21291772.01909388</v>
@@ -3252,10 +3252,10 @@
         <v>26435764.07323312</v>
       </c>
       <c r="H12" s="371" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="I12" s="372" t="n">
-        <v>592.4035862418284</v>
+        <v>592.4035862418285</v>
       </c>
       <c r="J12" s="372" t="n">
         <v>635.2527167980257</v>
@@ -3267,7 +3267,7 @@
         <v>695.233240768574</v>
       </c>
       <c r="M12" s="371" t="n">
-        <v>60.98577537796256</v>
+        <v>59.23245962249033</v>
       </c>
       <c r="N12" s="372" t="n">
         <v>67.08361822745846</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="T12" s="374" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="U12" s="375" t="n">
-        <v>19183612.89511096</v>
+        <v>19183612.89511097</v>
       </c>
       <c r="V12" s="375" t="n">
         <v>21291772.01909388</v>
@@ -3302,10 +3302,10 @@
         <v>26435764.07323312</v>
       </c>
       <c r="Y12" s="377" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="Z12" s="372" t="n">
-        <v>592.4035862418284</v>
+        <v>592.4035862418285</v>
       </c>
       <c r="AA12" s="372" t="n">
         <v>635.2527167980257</v>
@@ -3317,7 +3317,7 @@
         <v>695.233240768574</v>
       </c>
       <c r="AD12" s="377" t="n">
-        <v>60.98577537796256</v>
+        <v>59.23245962249033</v>
       </c>
       <c r="AE12" s="372" t="n">
         <v>67.08361822745846</v>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="AK12" s="379" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="AL12" s="368" t="n">
-        <v>19183612.89511096</v>
+        <v>19183612.89511097</v>
       </c>
       <c r="AM12" s="368" t="n">
         <v>21291772.01909388</v>
@@ -3352,10 +3352,10 @@
         <v>26435764.07323312</v>
       </c>
       <c r="AP12" s="381" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="AQ12" s="372" t="n">
-        <v>592.4035862418284</v>
+        <v>592.4035862418285</v>
       </c>
       <c r="AR12" s="372" t="n">
         <v>635.2527167980257</v>
@@ -3367,10 +3367,10 @@
         <v>695.233240768574</v>
       </c>
       <c r="AU12" s="372" t="n">
-        <v>60.98577537796041</v>
+        <v>59.23245962248824</v>
       </c>
       <c r="AV12" s="372" t="n">
-        <v>67.08361822754759</v>
+        <v>67.0836182275476</v>
       </c>
       <c r="AW12" s="372" t="n">
         <v>73.82197421508097</v>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="BB12" s="383" t="n">
-        <v>18145030.69132207</v>
+        <v>17622941.59714621</v>
       </c>
       <c r="BC12" s="384" t="n">
         <v>20826724.18067933</v>
@@ -3399,10 +3399,10 @@
         <v>27130558.6629931</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>31269035.35373416</v>
+        <v>31269035.35373417</v>
       </c>
       <c r="BG12" s="386" t="n">
-        <v>570.048152209937</v>
+        <v>553.6460899325641</v>
       </c>
       <c r="BH12" s="372" t="n">
         <v>643.1440293214108</v>
@@ -3411,13 +3411,13 @@
         <v>709.9350070881703</v>
       </c>
       <c r="BJ12" s="372" t="n">
-        <v>765.5314427408264</v>
+        <v>765.5314427408265</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>822.3432742273289</v>
+        <v>822.3432742273291</v>
       </c>
       <c r="BL12" s="386" t="n">
-        <v>63.98269371453386</v>
+        <v>62.14171217128807</v>
       </c>
       <c r="BM12" s="372" t="n">
         <v>72.82945196539031</v>
@@ -3426,7 +3426,7 @@
         <v>82.50071570226635</v>
       </c>
       <c r="BO12" s="372" t="n">
-        <v>93.26595055881734</v>
+        <v>93.26595055881735</v>
       </c>
       <c r="BP12" s="387" t="n">
         <v>106.2320297817831</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="BS12" s="391" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="BT12" s="375" t="n">
         <v>21058880.08272808</v>
@@ -3446,13 +3446,13 @@
         <v>24238389.22827421</v>
       </c>
       <c r="BV12" s="375" t="n">
-        <v>27803304.50143995</v>
+        <v>27803304.50143996</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>32206181.46459539</v>
+        <v>32206181.4645954</v>
       </c>
       <c r="BX12" s="386" t="n">
-        <v>565.9086046083704</v>
+        <v>549.651884694979</v>
       </c>
       <c r="BY12" s="372" t="n">
         <v>638.8115762007227</v>
@@ -3461,13 +3461,13 @@
         <v>705.4030879692488</v>
       </c>
       <c r="CA12" s="372" t="n">
-        <v>760.7592100776445</v>
+        <v>760.7592100776446</v>
       </c>
       <c r="CB12" s="387" t="n">
-        <v>817.4262300366822</v>
+        <v>817.4262300366823</v>
       </c>
       <c r="CC12" s="386" t="n">
-        <v>64.2268940149862</v>
+        <v>62.38186353054734</v>
       </c>
       <c r="CD12" s="372" t="n">
         <v>73.73722693051934</v>
@@ -3476,13 +3476,13 @@
         <v>84.15733049819283</v>
       </c>
       <c r="CF12" s="372" t="n">
-        <v>95.72564424922405</v>
+        <v>95.72564424922406</v>
       </c>
       <c r="CG12" s="387" t="n">
         <v>109.5986592243803</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>4.139547601566619</v>
+        <v>3.994205237585106</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>4.332453120688115</v>
@@ -3497,10 +3497,10 @@
         <v>4.91704419064672</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.01565152476890455</v>
+        <v>0.01560453994728554</v>
       </c>
       <c r="DD12" s="397" t="n">
-        <v>0.01558388449696708</v>
+        <v>0.01558388449696707</v>
       </c>
       <c r="DE12" s="397" t="n">
         <v>0.01579708867016908</v>
@@ -3519,40 +3519,40 @@
         </is>
       </c>
       <c r="C13" s="369" t="n">
-        <v>8050790.236236955</v>
+        <v>7835324.895783427</v>
       </c>
       <c r="D13" s="368" t="n">
-        <v>9114259.644327775</v>
+        <v>9114259.644327773</v>
       </c>
       <c r="E13" s="368" t="n">
         <v>10278866.18808733</v>
       </c>
       <c r="F13" s="368" t="n">
-        <v>11623184.18433255</v>
+        <v>11623184.18433256</v>
       </c>
       <c r="G13" s="370" t="n">
         <v>13221332.43027924</v>
       </c>
       <c r="H13" s="371" t="n">
-        <v>688.9527768236627</v>
+        <v>670.5141589664299</v>
       </c>
       <c r="I13" s="372" t="n">
-        <v>740.1454183530595</v>
+        <v>740.1454183530594</v>
       </c>
       <c r="J13" s="372" t="n">
         <v>782.7715687376176</v>
       </c>
       <c r="K13" s="372" t="n">
-        <v>816.2714790591486</v>
+        <v>816.2714790591488</v>
       </c>
       <c r="L13" s="373" t="n">
         <v>845.0312067744577</v>
       </c>
       <c r="M13" s="371" t="n">
-        <v>117.4941092693843</v>
+        <v>114.3495846311613</v>
       </c>
       <c r="N13" s="372" t="n">
-        <v>130.6461209288345</v>
+        <v>130.6461209288344</v>
       </c>
       <c r="O13" s="372" t="n">
         <v>144.5591587229399</v>
@@ -3569,40 +3569,40 @@
         </is>
       </c>
       <c r="T13" s="374" t="n">
-        <v>8050790.236236955</v>
+        <v>7835324.895783427</v>
       </c>
       <c r="U13" s="375" t="n">
-        <v>9114259.644327775</v>
+        <v>9114259.644327773</v>
       </c>
       <c r="V13" s="375" t="n">
         <v>10278866.18808733</v>
       </c>
       <c r="W13" s="375" t="n">
-        <v>11623184.18433255</v>
+        <v>11623184.18433256</v>
       </c>
       <c r="X13" s="376" t="n">
         <v>13221332.43027924</v>
       </c>
       <c r="Y13" s="377" t="n">
-        <v>688.9527768236627</v>
+        <v>670.5141589664299</v>
       </c>
       <c r="Z13" s="372" t="n">
-        <v>740.1454183530595</v>
+        <v>740.1454183530594</v>
       </c>
       <c r="AA13" s="372" t="n">
         <v>782.7715687376176</v>
       </c>
       <c r="AB13" s="372" t="n">
-        <v>816.2714790591486</v>
+        <v>816.2714790591488</v>
       </c>
       <c r="AC13" s="378" t="n">
         <v>845.0312067744577</v>
       </c>
       <c r="AD13" s="377" t="n">
-        <v>117.4941092693843</v>
+        <v>114.3495846311613</v>
       </c>
       <c r="AE13" s="372" t="n">
-        <v>130.6461209288345</v>
+        <v>130.6461209288344</v>
       </c>
       <c r="AF13" s="372" t="n">
         <v>144.5591587229399</v>
@@ -3619,40 +3619,40 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>8050790.236236955</v>
+        <v>7835324.895783427</v>
       </c>
       <c r="AL13" s="368" t="n">
-        <v>9114259.644327775</v>
+        <v>9114259.644327773</v>
       </c>
       <c r="AM13" s="368" t="n">
         <v>10278866.18808733</v>
       </c>
       <c r="AN13" s="368" t="n">
-        <v>11623184.18433255</v>
+        <v>11623184.18433256</v>
       </c>
       <c r="AO13" s="380" t="n">
         <v>13221332.43027924</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>688.9527768236627</v>
+        <v>670.5141589664299</v>
       </c>
       <c r="AQ13" s="372" t="n">
-        <v>740.1454183530595</v>
+        <v>740.1454183530594</v>
       </c>
       <c r="AR13" s="372" t="n">
         <v>782.7715687376176</v>
       </c>
       <c r="AS13" s="372" t="n">
-        <v>816.2714790591486</v>
+        <v>816.2714790591488</v>
       </c>
       <c r="AT13" s="382" t="n">
         <v>845.0312067744577</v>
       </c>
       <c r="AU13" s="372" t="n">
-        <v>117.4941092696929</v>
+        <v>114.3495846314617</v>
       </c>
       <c r="AV13" s="372" t="n">
-        <v>130.6461209288345</v>
+        <v>130.6461209288344</v>
       </c>
       <c r="AW13" s="372" t="n">
         <v>144.5591587227366</v>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="BB13" s="383" t="n">
-        <v>8456624.195706248</v>
+        <v>8230385.588230044</v>
       </c>
       <c r="BC13" s="384" t="n">
         <v>9898183.571209885</v>
@@ -3684,7 +3684,7 @@
         <v>15641988.30953081</v>
       </c>
       <c r="BG13" s="386" t="n">
-        <v>723.6823406430276</v>
+        <v>704.3217918929332</v>
       </c>
       <c r="BH13" s="372" t="n">
         <v>803.8058499691623</v>
@@ -3693,13 +3693,13 @@
         <v>875.0442874841461</v>
       </c>
       <c r="BJ13" s="372" t="n">
-        <v>939.0341732711565</v>
+        <v>939.0341732711563</v>
       </c>
       <c r="BK13" s="387" t="n">
-        <v>999.7455496454539</v>
+        <v>999.7455496454542</v>
       </c>
       <c r="BL13" s="386" t="n">
-        <v>123.4168942609865</v>
+        <v>120.1151433908438</v>
       </c>
       <c r="BM13" s="372" t="n">
         <v>141.8830863157253</v>
@@ -3708,7 +3708,7 @@
         <v>161.5997196319295</v>
       </c>
       <c r="BO13" s="372" t="n">
-        <v>184.1878065101272</v>
+        <v>184.1878065101271</v>
       </c>
       <c r="BP13" s="387" t="n">
         <v>209.8439252162722</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="BS13" s="391" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597152</v>
       </c>
       <c r="BT13" s="375" t="n">
         <v>9952954.78023549</v>
@@ -3734,7 +3734,7 @@
         <v>15903215.82847833</v>
       </c>
       <c r="BX13" s="386" t="n">
-        <v>722.1068685387845</v>
+        <v>702.8801848671825</v>
       </c>
       <c r="BY13" s="372" t="n">
         <v>802.3898184552372</v>
@@ -3743,13 +3743,13 @@
         <v>873.7820185630105</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236421</v>
       </c>
       <c r="CB13" s="387" t="n">
-        <v>998.5916384034791</v>
+        <v>998.5916384034792</v>
       </c>
       <c r="CC13" s="386" t="n">
-        <v>123.6967833481126</v>
+        <v>120.4032557163351</v>
       </c>
       <c r="CD13" s="372" t="n">
         <v>142.9612665200117</v>
@@ -3758,13 +3758,13 @@
         <v>163.5829476219391</v>
       </c>
       <c r="CF13" s="372" t="n">
-        <v>187.1594979275484</v>
+        <v>187.1594979275483</v>
       </c>
       <c r="CG13" s="387" t="n">
         <v>213.9019892506383</v>
       </c>
       <c r="CW13" s="102" t="n">
-        <v>1.57547210424309</v>
+        <v>1.441607025750727</v>
       </c>
       <c r="CX13" s="103" t="n">
         <v>1.416031513925077</v>
@@ -3776,13 +3776,13 @@
         <v>1.195333547514224</v>
       </c>
       <c r="DA13" s="104" t="n">
-        <v>1.153911241974811</v>
+        <v>1.153911241974924</v>
       </c>
       <c r="DC13" s="396" t="n">
-        <v>0.01255052524219419</v>
+        <v>0.0124216590811804</v>
       </c>
       <c r="DD13" s="397" t="n">
-        <v>0.01250671103088636</v>
+        <v>0.01250671103088637</v>
       </c>
       <c r="DE13" s="397" t="n">
         <v>0.01253173068945309</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C14" s="369" t="n">
-        <v>71146187.32989205</v>
+        <v>71146187.32989207</v>
       </c>
       <c r="D14" s="368" t="n">
         <v>79803883.49063842</v>
@@ -3816,7 +3816,7 @@
         <v>121670204.0056975</v>
       </c>
       <c r="H14" s="371" t="n">
-        <v>3210.841122479659</v>
+        <v>3210.84112247966</v>
       </c>
       <c r="I14" s="372" t="n">
         <v>3266.727771821991</v>
@@ -3831,7 +3831,7 @@
         <v>3639.57085916715</v>
       </c>
       <c r="M14" s="372" t="n">
-        <v>2823.987813339367</v>
+        <v>2823.987813339368</v>
       </c>
       <c r="N14" s="372" t="n">
         <v>2869.321462856016</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="T14" s="401" t="n">
-        <v>71146187.32989205</v>
+        <v>71146187.32989207</v>
       </c>
       <c r="U14" s="402" t="n">
         <v>79803883.49063842</v>
@@ -3866,7 +3866,7 @@
         <v>121670204.0056975</v>
       </c>
       <c r="Y14" s="404" t="n">
-        <v>3210.841122479659</v>
+        <v>3210.84112247966</v>
       </c>
       <c r="Z14" s="405" t="n">
         <v>3266.727771821991</v>
@@ -3881,7 +3881,7 @@
         <v>3639.57085916715</v>
       </c>
       <c r="AD14" s="405" t="n">
-        <v>2823.987813339367</v>
+        <v>2823.987813339368</v>
       </c>
       <c r="AE14" s="405" t="n">
         <v>2869.321462856016</v>
@@ -3907,7 +3907,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="AM14" s="408" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="AN14" s="408" t="n">
         <v>104824680.999119</v>
@@ -3922,10 +3922,10 @@
         <v>3266.727771821991</v>
       </c>
       <c r="AR14" s="411" t="n">
-        <v>3389.394385627783</v>
+        <v>3389.394385627784</v>
       </c>
       <c r="AS14" s="411" t="n">
-        <v>3503.631779582347</v>
+        <v>3503.631779582348</v>
       </c>
       <c r="AT14" s="412" t="n">
         <v>3639.57085916715</v>
@@ -3937,7 +3937,7 @@
         <v>2869.321462784832</v>
       </c>
       <c r="AW14" s="411" t="n">
-        <v>2976.398170657375</v>
+        <v>2976.398170657376</v>
       </c>
       <c r="AX14" s="411" t="n">
         <v>3073.152424049543</v>
@@ -3960,7 +3960,7 @@
         <v>101643871.5811244</v>
       </c>
       <c r="BE14" s="414" t="n">
-        <v>118745142.8878008</v>
+        <v>118745142.8878007</v>
       </c>
       <c r="BF14" s="415" t="n">
         <v>140781626.0133759</v>
@@ -3975,7 +3975,7 @@
         <v>3760.113633814127</v>
       </c>
       <c r="BJ14" s="417" t="n">
-        <v>3968.905531858876</v>
+        <v>3968.905531858875</v>
       </c>
       <c r="BK14" s="418" t="n">
         <v>4211.258686805993</v>
@@ -4016,7 +4016,7 @@
         <v>134573833.4912403</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>3301.597169367806</v>
+        <v>3301.597169367807</v>
       </c>
       <c r="BY14" s="417" t="n">
         <v>3480.273585109801</v>
@@ -4031,7 +4031,7 @@
         <v>4130.885314437096</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>2900.977332425373</v>
+        <v>2900.977332425374</v>
       </c>
       <c r="CD14" s="417" t="n">
         <v>3057.045126093473</v>
@@ -4046,7 +4046,7 @@
         <v>3644.962699007892</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>67.81229001315251</v>
+        <v>67.81229001315205</v>
       </c>
       <c r="CX14" s="133" t="n">
         <v>71.20819560781501</v>
@@ -4055,25 +4055,25 @@
         <v>73.37099834241462</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>78.47102417561155</v>
+        <v>78.47102417561109</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>80.37337236889744</v>
+        <v>80.37337236889653</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0.04866627713558654</v>
       </c>
       <c r="DD14" s="423" t="n">
-        <v>0.04942471132771882</v>
+        <v>0.04942471132771883</v>
       </c>
       <c r="DE14" s="423" t="n">
-        <v>0.04960100930908168</v>
+        <v>0.04960100930908167</v>
       </c>
       <c r="DF14" s="423" t="n">
-        <v>0.04998498574654765</v>
+        <v>0.04998498574654767</v>
       </c>
       <c r="DG14" s="424" t="n">
-        <v>0.0501964676491023</v>
+        <v>0.05019646764910228</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C15" s="425" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="D15" s="425" t="n">
         <v>161532099.6256683</v>
@@ -4098,7 +4098,7 @@
         <v>238354658.0410133</v>
       </c>
       <c r="H15" s="427" t="n">
-        <v>643.3438188355617</v>
+        <v>632.22357308174</v>
       </c>
       <c r="I15" s="427" t="n">
         <v>691.7972564127136</v>
@@ -4113,7 +4113,7 @@
         <v>839.126686349459</v>
       </c>
       <c r="M15" s="427" t="n">
-        <v>87.1518501311496</v>
+        <v>85.64542392018085</v>
       </c>
       <c r="N15" s="427" t="n">
         <v>96.79669007575326</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="T15" s="429" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="U15" s="430" t="n">
         <v>161532099.6256683</v>
@@ -4148,7 +4148,7 @@
         <v>238354658.0410133</v>
       </c>
       <c r="Y15" s="432" t="n">
-        <v>643.3438188355617</v>
+        <v>632.22357308174</v>
       </c>
       <c r="Z15" s="433" t="n">
         <v>691.7972564127136</v>
@@ -4163,7 +4163,7 @@
         <v>839.126686349459</v>
       </c>
       <c r="AD15" s="433" t="n">
-        <v>87.1518501311496</v>
+        <v>85.64542392018085</v>
       </c>
       <c r="AE15" s="433" t="n">
         <v>96.79669007575326</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="AK15" s="435" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="AL15" s="408" t="n">
         <v>161532099.6256683</v>
@@ -4198,7 +4198,7 @@
         <v>238354658.0410134</v>
       </c>
       <c r="AP15" s="436" t="n">
-        <v>643.3720511397373</v>
+        <v>632.2513173884383</v>
       </c>
       <c r="AQ15" s="437" t="n">
         <v>691.8333988481108</v>
@@ -4207,13 +4207,13 @@
         <v>744.9695320502487</v>
       </c>
       <c r="AS15" s="437" t="n">
-        <v>790.9007843495842</v>
+        <v>790.900784349584</v>
       </c>
       <c r="AT15" s="438" t="n">
         <v>839.1889598517764</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>87.15236821113017</v>
+        <v>85.64593304511044</v>
       </c>
       <c r="AV15" s="437" t="n">
         <v>96.79739763240777</v>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="BB15" s="439" t="n">
-        <v>150052098.3541718</v>
+        <v>147455496.1547291</v>
       </c>
       <c r="BC15" s="440" t="n">
         <v>175425786.1478831</v>
@@ -4248,22 +4248,22 @@
         <v>278690895.7052011</v>
       </c>
       <c r="BG15" s="442" t="n">
-        <v>674.7756382273338</v>
+        <v>663.0988677884699</v>
       </c>
       <c r="BH15" s="443" t="n">
         <v>751.3393199094292</v>
       </c>
       <c r="BI15" s="443" t="n">
-        <v>829.1928544556764</v>
+        <v>829.1928544556765</v>
       </c>
       <c r="BJ15" s="443" t="n">
-        <v>902.4062819970376</v>
+        <v>902.4062819970372</v>
       </c>
       <c r="BK15" s="444" t="n">
         <v>981.2030728040784</v>
       </c>
       <c r="BL15" s="443" t="n">
-        <v>91.4063562110131</v>
+        <v>89.82459928669239</v>
       </c>
       <c r="BM15" s="443" t="n">
         <v>105.1231279484715</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>146573182.8131705</v>
+        <v>143982034.657172</v>
       </c>
       <c r="BT15" s="440" t="n">
         <v>172045860.0076335</v>
@@ -4298,22 +4298,22 @@
         <v>275765716.3780743</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>656.9627481758935</v>
+        <v>645.3488377672925</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>730.1653162186615</v>
+        <v>730.1653162186614</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>804.5121242644021</v>
+        <v>804.5121242644022</v>
       </c>
       <c r="CA15" s="443" t="n">
         <v>874.1245058957192</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>949.2839689357264</v>
+        <v>949.2839689357262</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>89.45645662511875</v>
+        <v>87.87502864370012</v>
       </c>
       <c r="CD15" s="443" t="n">
         <v>103.3101833037128</v>
@@ -6298,13 +6298,13 @@
         <v>0.09872293851570045</v>
       </c>
       <c r="AS24" s="437" t="n">
-        <v>0.1109410166478777</v>
+        <v>0.1109410166478776</v>
       </c>
       <c r="AT24" s="438" t="n">
         <v>0.1234609350729212</v>
       </c>
       <c r="AU24" s="437" t="n">
-        <v>0.01035224921079854</v>
+        <v>0.01035224921079855</v>
       </c>
       <c r="AV24" s="437" t="n">
         <v>0.01217085645581582</v>
@@ -6348,13 +6348,13 @@
         <v>0.09872293851570045</v>
       </c>
       <c r="BJ24" s="443" t="n">
-        <v>0.1109410166478777</v>
+        <v>0.1109410166478776</v>
       </c>
       <c r="BK24" s="444" t="n">
         <v>0.1234609350729212</v>
       </c>
       <c r="BL24" s="443" t="n">
-        <v>0.01035224921079854</v>
+        <v>0.01035224921079855</v>
       </c>
       <c r="BM24" s="443" t="n">
         <v>0.01217085645581582</v>
@@ -6392,7 +6392,7 @@
         <v>0.07718104575580055</v>
       </c>
       <c r="BY24" s="443" t="n">
-        <v>0.08797366820908517</v>
+        <v>0.08797366820908516</v>
       </c>
       <c r="BZ24" s="443" t="n">
         <v>0.09997933894145931</v>
@@ -7286,46 +7286,46 @@
         </is>
       </c>
       <c r="BB29" s="391" t="n">
-        <v>1082.764896368826</v>
+        <v>1087.098008869964</v>
       </c>
       <c r="BC29" s="375" t="n">
-        <v>1064.135841095291</v>
+        <v>1064.135841095292</v>
       </c>
       <c r="BD29" s="375" t="n">
         <v>1047.177933892141</v>
       </c>
       <c r="BE29" s="375" t="n">
-        <v>40.9911494618624</v>
+        <v>40.99114946186235</v>
       </c>
       <c r="BF29" s="392" t="n">
         <v>0</v>
       </c>
       <c r="BG29" s="386" t="n">
-        <v>0.006909841051221676</v>
+        <v>0.006937493516443198</v>
       </c>
       <c r="BH29" s="372" t="n">
-        <v>0.006474500763672482</v>
+        <v>0.006474500763672489</v>
       </c>
       <c r="BI29" s="372" t="n">
         <v>0.006062006604785379</v>
       </c>
       <c r="BJ29" s="372" t="n">
-        <v>0.0002236327055582062</v>
+        <v>0.0002236327055582059</v>
       </c>
       <c r="BK29" s="387" t="n">
         <v>0</v>
       </c>
       <c r="BL29" s="388" t="n">
-        <v>0.0008564236181964728</v>
+        <v>0.0008598509364432334</v>
       </c>
       <c r="BM29" s="389" t="n">
-        <v>0.0008279772983846359</v>
+        <v>0.0008279772983846368</v>
       </c>
       <c r="BN29" s="389" t="n">
         <v>0.0008025608621735258</v>
       </c>
       <c r="BO29" s="389" t="n">
-        <v>3.096498375894686e-05</v>
+        <v>3.096498375894682e-05</v>
       </c>
       <c r="BP29" s="390" t="n">
         <v>0</v>
@@ -7336,52 +7336,52 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="BT29" s="375" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="BU29" s="375" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="BV29" s="375" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="BW29" s="392" t="n">
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.006733567703092378</v>
+        <v>0.006760514740708186</v>
       </c>
       <c r="BY29" s="372" t="n">
-        <v>0.00631265298990767</v>
+        <v>0.006312652989907677</v>
       </c>
       <c r="BZ29" s="372" t="n">
         <v>0.005913511288780401</v>
       </c>
       <c r="CA29" s="372" t="n">
-        <v>0.0002182438534425571</v>
+        <v>0.0002182438534425569</v>
       </c>
       <c r="CB29" s="387" t="n">
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.0008411748025817804</v>
+        <v>0.0008445410966544206</v>
       </c>
       <c r="CD29" s="389" t="n">
-        <v>0.0008191178618692217</v>
+        <v>0.0008191178618692225</v>
       </c>
       <c r="CE29" s="389" t="n">
         <v>0.0007992417272445699</v>
       </c>
       <c r="CF29" s="389" t="n">
-        <v>3.101437433010643e-05</v>
+        <v>3.101437433010639e-05</v>
       </c>
       <c r="CG29" s="390" t="n">
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>0.000176273348129298</v>
+        <v>0.000176978775735012</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0.000161847773764812</v>
@@ -8388,13 +8388,13 @@
         <v>0.004857723902874456</v>
       </c>
       <c r="AS33" s="437" t="n">
-        <v>0.0001866963165992431</v>
+        <v>0.000186696316599243</v>
       </c>
       <c r="AT33" s="438" t="n">
         <v>0</v>
       </c>
       <c r="AU33" s="437" t="n">
-        <v>0.0006940171537542232</v>
+        <v>0.0006940171537542233</v>
       </c>
       <c r="AV33" s="437" t="n">
         <v>0.0006998122457593044</v>
@@ -8403,7 +8403,7 @@
         <v>0.0007061892919933395</v>
       </c>
       <c r="AX33" s="437" t="n">
-        <v>2.851273625649563e-05</v>
+        <v>2.851273625649562e-05</v>
       </c>
       <c r="AY33" s="438" t="n">
         <v>0</v>
@@ -8414,46 +8414,46 @@
         </is>
       </c>
       <c r="BB33" s="439" t="n">
-        <v>1082.764896368826</v>
+        <v>1087.098008869964</v>
       </c>
       <c r="BC33" s="440" t="n">
-        <v>1064.135841095291</v>
+        <v>1064.135841095292</v>
       </c>
       <c r="BD33" s="440" t="n">
         <v>1047.177933892141</v>
       </c>
       <c r="BE33" s="440" t="n">
-        <v>40.9911494618624</v>
+        <v>40.99114946186235</v>
       </c>
       <c r="BF33" s="441" t="n">
         <v>0</v>
       </c>
       <c r="BG33" s="442" t="n">
-        <v>0.004869131335124142</v>
+        <v>0.004888617092308055</v>
       </c>
       <c r="BH33" s="443" t="n">
-        <v>0.004557637259016112</v>
+        <v>0.004557637259016117</v>
       </c>
       <c r="BI33" s="443" t="n">
         <v>0.004249480121592991</v>
       </c>
       <c r="BJ33" s="443" t="n">
-        <v>0.0001559220494652495</v>
+        <v>0.0001559220494652492</v>
       </c>
       <c r="BK33" s="444" t="n">
         <v>0</v>
       </c>
       <c r="BL33" s="443" t="n">
-        <v>0.0006595815379846566</v>
+        <v>0.0006622211146991824</v>
       </c>
       <c r="BM33" s="443" t="n">
-        <v>0.0006376787052486838</v>
+        <v>0.0006376787052486846</v>
       </c>
       <c r="BN33" s="443" t="n">
         <v>0.0006177661428291104</v>
       </c>
       <c r="BO33" s="443" t="n">
-        <v>2.381281191807374e-05</v>
+        <v>2.381281191807371e-05</v>
       </c>
       <c r="BP33" s="444" t="n">
         <v>0</v>
@@ -8464,46 +8464,46 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="BT33" s="440" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="BU33" s="440" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="BV33" s="440" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="BW33" s="441" t="n">
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>0.004759294004793454</v>
+        <v>0.004778340204405135</v>
       </c>
       <c r="BY33" s="443" t="n">
-        <v>0.004460365371489595</v>
+        <v>0.004460365371489599</v>
       </c>
       <c r="BZ33" s="443" t="n">
         <v>0.004164063495649975</v>
       </c>
       <c r="CA33" s="443" t="n">
-        <v>0.0001529500751459862</v>
+        <v>0.000152950075145986</v>
       </c>
       <c r="CB33" s="444" t="n">
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>0.0006480574109995112</v>
+        <v>0.0006506508693564216</v>
       </c>
       <c r="CD33" s="443" t="n">
-        <v>0.0006310915540558595</v>
+        <v>0.0006310915540558603</v>
       </c>
       <c r="CE33" s="443" t="n">
         <v>0.0006154688139292611</v>
       </c>
       <c r="CF33" s="443" t="n">
-        <v>2.386171294871138e-05</v>
+        <v>2.386171294871135e-05</v>
       </c>
       <c r="CG33" s="444" t="n">
         <v>0</v>
@@ -9376,49 +9376,49 @@
         </is>
       </c>
       <c r="BB38" s="391" t="n">
-        <v>444.1441328636855</v>
+        <v>445.9215514897166</v>
       </c>
       <c r="BC38" s="375" t="n">
-        <v>689.3364752758298</v>
+        <v>689.3364752758305</v>
       </c>
       <c r="BD38" s="375" t="n">
         <v>969.3457246219497</v>
       </c>
       <c r="BE38" s="375" t="n">
-        <v>1274.632341559145</v>
+        <v>1274.632341559143</v>
       </c>
       <c r="BF38" s="392" t="n">
-        <v>1624.65718670356</v>
+        <v>1624.657186703561</v>
       </c>
       <c r="BG38" s="386" t="n">
-        <v>0.002834378332926075</v>
+        <v>0.002845721220221871</v>
       </c>
       <c r="BH38" s="372" t="n">
-        <v>0.004194116355489803</v>
+        <v>0.004194116355489806</v>
       </c>
       <c r="BI38" s="372" t="n">
         <v>0.005611443857624269</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.006953927442314572</v>
+        <v>0.006953927442314564</v>
       </c>
       <c r="BK38" s="387" t="n">
-        <v>0.00824993555144128</v>
+        <v>0.008249935551441287</v>
       </c>
       <c r="BL38" s="388" t="n">
-        <v>0.0003513002005730741</v>
+        <v>0.0003527060674384114</v>
       </c>
       <c r="BM38" s="389" t="n">
-        <v>0.0005363553509196756</v>
+        <v>0.0005363553509196761</v>
       </c>
       <c r="BN38" s="389" t="n">
         <v>0.0007429099824566611</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.0009628656496136736</v>
+        <v>0.0009628656496136725</v>
       </c>
       <c r="BP38" s="390" t="n">
-        <v>0.001205293589157693</v>
+        <v>0.001205293589157694</v>
       </c>
       <c r="BR38" s="83" t="inlineStr">
         <is>
@@ -9426,52 +9426,52 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>450.6865261022976</v>
+        <v>452.490126705621</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>704.4597020478222</v>
+        <v>704.4597020478228</v>
       </c>
       <c r="BU38" s="375" t="n">
         <v>997.0452295340147</v>
       </c>
       <c r="BV38" s="375" t="n">
-        <v>1318.398827527652</v>
+        <v>1318.39882752765</v>
       </c>
       <c r="BW38" s="392" t="n">
-        <v>1688.256854667008</v>
+        <v>1688.256854667009</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.002858008376089825</v>
+        <v>0.002869445828360694</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.004231307705790088</v>
+        <v>0.004231307705790091</v>
       </c>
       <c r="BZ38" s="372" t="n">
         <v>0.005664116158427144</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.007022073357940794</v>
+        <v>0.007022073357940787</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.008333118956914243</v>
+        <v>0.00833311895691425</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>0.0003570298447330324</v>
+        <v>0.00035845864103838</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>0.0005490464510592767</v>
+        <v>0.0005490464510592771</v>
       </c>
       <c r="CE38" s="389" t="n">
         <v>0.0007655346816305535</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.0009978984895167523</v>
+        <v>0.000997898489516751</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.00125515799160004</v>
+        <v>0.001255157991600041</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-2.363004316375e-05</v>
+        <v>-2.3724608138823e-05</v>
       </c>
       <c r="CX38" s="92" t="n">
         <v>-3.7191350300285e-05</v>
@@ -9480,7 +9480,7 @@
         <v>-5.2672300802875e-05</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>-6.8145915626222e-05</v>
+        <v>-6.8145915626223e-05</v>
       </c>
       <c r="DA38" s="93" t="n">
         <v>-8.318340547296301e-05</v>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="BB40" s="391" t="n">
-        <v>74.9759211272119</v>
+        <v>75.10914895326566</v>
       </c>
       <c r="BC40" s="375" t="n">
         <v>118.1051228030125</v>
@@ -9949,40 +9949,40 @@
         <v>168.7983275855672</v>
       </c>
       <c r="BE40" s="375" t="n">
-        <v>226.764681219807</v>
+        <v>226.7646812198072</v>
       </c>
       <c r="BF40" s="392" t="n">
         <v>294.2621680813407</v>
       </c>
       <c r="BG40" s="386" t="n">
-        <v>0.006416124074752782</v>
+        <v>0.00642752515191621</v>
       </c>
       <c r="BH40" s="372" t="n">
-        <v>0.009591011112030097</v>
+        <v>0.009591011112030095</v>
       </c>
       <c r="BI40" s="372" t="n">
         <v>0.01285458233103308</v>
       </c>
       <c r="BJ40" s="372" t="n">
-        <v>0.01592520077133213</v>
+        <v>0.01592520077133214</v>
       </c>
       <c r="BK40" s="387" t="n">
-        <v>0.01880753822000314</v>
+        <v>0.01880753822000313</v>
       </c>
       <c r="BL40" s="386" t="n">
-        <v>0.001094206756234412</v>
+        <v>0.001096151097633554</v>
       </c>
       <c r="BM40" s="372" t="n">
-        <v>0.001692948934765097</v>
+        <v>0.001692948934765096</v>
       </c>
       <c r="BN40" s="372" t="n">
         <v>0.00237393344587503</v>
       </c>
       <c r="BO40" s="372" t="n">
-        <v>0.003123664592617599</v>
+        <v>0.003123664592617602</v>
       </c>
       <c r="BP40" s="387" t="n">
-        <v>0.003947652125223407</v>
+        <v>0.003947652125223406</v>
       </c>
       <c r="BR40" s="111" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="BS40" s="391" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925451</v>
       </c>
       <c r="BT40" s="375" t="n">
         <v>120.2627442393418</v>
@@ -9999,49 +9999,49 @@
         <v>172.6544121934863</v>
       </c>
       <c r="BV40" s="375" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="BW40" s="392" t="n">
         <v>302.9560444208731</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.006483527712111256</v>
+        <v>0.006495048561595429</v>
       </c>
       <c r="BY40" s="372" t="n">
-        <v>0.00969537224350284</v>
+        <v>0.009695372243502838</v>
       </c>
       <c r="BZ40" s="372" t="n">
         <v>0.01299893853538077</v>
       </c>
       <c r="CA40" s="372" t="n">
-        <v>0.01610687589719862</v>
+        <v>0.01610687589719863</v>
       </c>
       <c r="CB40" s="387" t="n">
         <v>0.01902315707875442</v>
       </c>
       <c r="CC40" s="386" t="n">
-        <v>0.001110627190625365</v>
+        <v>0.001112600710175891</v>
       </c>
       <c r="CD40" s="372" t="n">
-        <v>0.001727418099574824</v>
+        <v>0.001727418099574823</v>
       </c>
       <c r="CE40" s="372" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248188</v>
       </c>
       <c r="CG40" s="387" t="n">
-        <v>0.004074829975022105</v>
+        <v>0.004074829975022104</v>
       </c>
       <c r="CW40" s="102" t="n">
-        <v>-6.7403637358474e-05</v>
+        <v>-6.7523409679218e-05</v>
       </c>
       <c r="CX40" s="103" t="n">
         <v>-0.000104361131472743</v>
       </c>
       <c r="CY40" s="103" t="n">
-        <v>-0.00014435620434769</v>
+        <v>-0.000144356204347688</v>
       </c>
       <c r="CZ40" s="103" t="n">
         <v>-0.000181675125866487</v>
@@ -10478,7 +10478,7 @@
         <v>0.005246115330499869</v>
       </c>
       <c r="AS42" s="437" t="n">
-        <v>0.006772942306571762</v>
+        <v>0.00677294230657176</v>
       </c>
       <c r="AT42" s="438" t="n">
         <v>0.008332752433835432</v>
@@ -10493,7 +10493,7 @@
         <v>0.000762651510261606</v>
       </c>
       <c r="AX42" s="437" t="n">
-        <v>0.001034380973258713</v>
+        <v>0.001034380973258712</v>
       </c>
       <c r="AY42" s="438" t="n">
         <v>0.001348701221301406</v>
@@ -10504,49 +10504,49 @@
         </is>
       </c>
       <c r="BB42" s="439" t="n">
-        <v>519.1200539908974</v>
+        <v>521.0307004429823</v>
       </c>
       <c r="BC42" s="440" t="n">
-        <v>807.4415980788423</v>
+        <v>807.441598078843</v>
       </c>
       <c r="BD42" s="440" t="n">
         <v>1138.144052207517</v>
       </c>
       <c r="BE42" s="440" t="n">
-        <v>1501.397022778952</v>
+        <v>1501.397022778951</v>
       </c>
       <c r="BF42" s="441" t="n">
-        <v>1918.919354784901</v>
+        <v>1918.919354784902</v>
       </c>
       <c r="BG42" s="442" t="n">
-        <v>0.00233445296394002</v>
+        <v>0.002343045030917246</v>
       </c>
       <c r="BH42" s="443" t="n">
-        <v>0.003458229456960942</v>
+        <v>0.003458229456960945</v>
       </c>
       <c r="BI42" s="443" t="n">
         <v>0.004618623415209681</v>
       </c>
       <c r="BJ42" s="443" t="n">
-        <v>0.005711010887131191</v>
+        <v>0.005711010887131184</v>
       </c>
       <c r="BK42" s="444" t="n">
-        <v>0.006756049789907167</v>
+        <v>0.00675604978990717</v>
       </c>
       <c r="BL42" s="443" t="n">
-        <v>0.0003162293169627845</v>
+        <v>0.0003173932142498479</v>
       </c>
       <c r="BM42" s="443" t="n">
-        <v>0.0004838558132736901</v>
+        <v>0.0004838558132736905</v>
       </c>
       <c r="BN42" s="443" t="n">
         <v>0.0006714301728101071</v>
       </c>
       <c r="BO42" s="443" t="n">
-        <v>0.0008722001062950107</v>
+        <v>0.0008722001062950099</v>
       </c>
       <c r="BP42" s="444" t="n">
-        <v>0.001093503338203322</v>
+        <v>0.001093503338203323</v>
       </c>
       <c r="BR42" s="155" t="inlineStr">
         <is>
@@ -10554,49 +10554,49 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>526.642464841529</v>
+        <v>528.5810347048755</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>824.7224462871641</v>
+        <v>824.7224462871645</v>
       </c>
       <c r="BU42" s="440" t="n">
         <v>1169.699641727501</v>
       </c>
       <c r="BV42" s="440" t="n">
-        <v>1551.187727295498</v>
+        <v>1551.187727295497</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>1991.212899087881</v>
+        <v>1991.212899087882</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>0.002360489650070753</v>
+        <v>0.002369178607767595</v>
       </c>
       <c r="BY42" s="443" t="n">
-        <v>0.003500134939365451</v>
+        <v>0.003500134939365452</v>
       </c>
       <c r="BZ42" s="443" t="n">
         <v>0.004679113298454359</v>
       </c>
       <c r="CA42" s="443" t="n">
-        <v>0.005790160302960493</v>
+        <v>0.005790160302960487</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>0.006854465118683066</v>
+        <v>0.006854465118683069</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.0003214201118433284</v>
+        <v>0.0003226032586343499</v>
       </c>
       <c r="CD42" s="443" t="n">
-        <v>0.0004952297433767545</v>
+        <v>0.0004952297433767547</v>
       </c>
       <c r="CE42" s="443" t="n">
         <v>0.0006915956769268278</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.0009033218384783037</v>
+        <v>0.0009033218384783031</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>0.001137719236600286</v>
+        <v>0.001137719236600287</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="C47" s="454" t="n">
-        <v>46594302.08771282</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="D47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11249,10 +11249,10 @@
         <v>77062920.15333699</v>
       </c>
       <c r="H47" s="371" t="n">
-        <v>297.3306332319371</v>
+        <v>286.0979369335776</v>
       </c>
       <c r="I47" s="372" t="n">
-        <v>325.1897713688447</v>
+        <v>325.1897713688446</v>
       </c>
       <c r="J47" s="372" t="n">
         <v>349.6854122178148</v>
@@ -11264,10 +11264,10 @@
         <v>391.2801344977017</v>
       </c>
       <c r="M47" s="371" t="n">
-        <v>36.85394023174813</v>
+        <v>35.46165476986572</v>
       </c>
       <c r="N47" s="372" t="n">
-        <v>41.58887079181889</v>
+        <v>41.58887079181888</v>
       </c>
       <c r="O47" s="372" t="n">
         <v>46.29893639166217</v>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="T47" s="374" t="n">
-        <v>46594302.08771282</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="U47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11299,10 +11299,10 @@
         <v>77062920.15333699</v>
       </c>
       <c r="Y47" s="377" t="n">
-        <v>297.3306332319371</v>
+        <v>286.0979369335776</v>
       </c>
       <c r="Z47" s="372" t="n">
-        <v>325.1897713688447</v>
+        <v>325.1897713688446</v>
       </c>
       <c r="AA47" s="372" t="n">
         <v>349.6854122178148</v>
@@ -11314,10 +11314,10 @@
         <v>391.2801344977017</v>
       </c>
       <c r="AD47" s="377" t="n">
-        <v>36.85394023174813</v>
+        <v>35.46165476986572</v>
       </c>
       <c r="AE47" s="372" t="n">
-        <v>41.58887079181889</v>
+        <v>41.58887079181888</v>
       </c>
       <c r="AF47" s="372" t="n">
         <v>46.29893639166217</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="AK47" s="379" t="n">
-        <v>46594302.08771282</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="AL47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11349,7 +11349,7 @@
         <v>77062920.15333699</v>
       </c>
       <c r="AP47" s="381" t="n">
-        <v>297.349149753957</v>
+        <v>286.1157539297327</v>
       </c>
       <c r="AQ47" s="372" t="n">
         <v>325.2139060732657</v>
@@ -11364,7 +11364,7 @@
         <v>391.3220154221365</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>36.85422469376553</v>
+        <v>35.46192848534343</v>
       </c>
       <c r="AV47" s="372" t="n">
         <v>41.58926551657729</v>
@@ -11384,13 +11384,13 @@
         </is>
       </c>
       <c r="BB47" s="391" t="n">
-        <v>48808228.4004522</v>
+        <v>46959960.01319259</v>
       </c>
       <c r="BC47" s="375" t="n">
-        <v>57961637.77898525</v>
+        <v>57961637.77898524</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>67429644.03037082</v>
+        <v>67429644.03037083</v>
       </c>
       <c r="BE47" s="375" t="n">
         <v>78020407.44910015</v>
@@ -11399,13 +11399,13 @@
         <v>91033404.66453953</v>
       </c>
       <c r="BG47" s="386" t="n">
-        <v>311.4776821541572</v>
+        <v>299.6826555340742</v>
       </c>
       <c r="BH47" s="372" t="n">
         <v>352.6548524833898</v>
       </c>
       <c r="BI47" s="372" t="n">
-        <v>390.3433544967506</v>
+        <v>390.3433544967507</v>
       </c>
       <c r="BJ47" s="372" t="n">
         <v>425.6507815871128</v>
@@ -11414,10 +11414,10 @@
         <v>462.2635025143668</v>
       </c>
       <c r="BL47" s="388" t="n">
-        <v>38.60535163696001</v>
+        <v>37.14344545130191</v>
       </c>
       <c r="BM47" s="389" t="n">
-        <v>45.09849062953945</v>
+        <v>45.09849062953944</v>
       </c>
       <c r="BN47" s="389" t="n">
         <v>51.67831702481455</v>
@@ -11434,13 +11434,13 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>48779577.64607866</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="BT47" s="375" t="n">
         <v>58334248.70010031</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>68292230.10798056</v>
+        <v>68292230.10798058</v>
       </c>
       <c r="BV47" s="375" t="n">
         <v>79443029.17070328</v>
@@ -11449,13 +11449,13 @@
         <v>93118992.35702755</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>309.3335021579338</v>
+        <v>297.6442864398001</v>
       </c>
       <c r="BY47" s="372" t="n">
         <v>350.3822224588424</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>387.9614611168861</v>
+        <v>387.9614611168862</v>
       </c>
       <c r="CA47" s="372" t="n">
         <v>423.1305178417331</v>
@@ -11464,13 +11464,13 @@
         <v>459.6288996629908</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>38.64274617601792</v>
+        <v>37.18249892558611</v>
       </c>
       <c r="CD47" s="389" t="n">
         <v>45.46493167869674</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>52.43500403485943</v>
+        <v>52.43500403485944</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>60.13057441862553</v>
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="C48" s="454" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="D48" s="375" t="n">
-        <v>19183960.51387433</v>
+        <v>19183960.51387434</v>
       </c>
       <c r="E48" s="375" t="n">
         <v>21292132.6666085</v>
@@ -11501,10 +11501,10 @@
         <v>26436153.51971607</v>
       </c>
       <c r="H48" s="371" t="n">
-        <v>543.357928207859</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="I48" s="372" t="n">
-        <v>592.4143209560447</v>
+        <v>592.4143209560448</v>
       </c>
       <c r="J48" s="372" t="n">
         <v>635.2634769317179</v>
@@ -11516,10 +11516,10 @@
         <v>695.2434828080966</v>
       </c>
       <c r="M48" s="371" t="n">
-        <v>60.98696007190096</v>
+        <v>59.23364431642874</v>
       </c>
       <c r="N48" s="372" t="n">
-        <v>67.08483382352672</v>
+        <v>67.08483382352674</v>
       </c>
       <c r="O48" s="372" t="n">
         <v>73.82322463750509</v>
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="T48" s="374" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="U48" s="375" t="n">
-        <v>19183960.51387433</v>
+        <v>19183960.51387434</v>
       </c>
       <c r="V48" s="375" t="n">
         <v>21292132.6666085</v>
@@ -11551,10 +11551,10 @@
         <v>26436153.51971607</v>
       </c>
       <c r="Y48" s="377" t="n">
-        <v>543.357928207859</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="Z48" s="372" t="n">
-        <v>592.4143209560447</v>
+        <v>592.4143209560448</v>
       </c>
       <c r="AA48" s="372" t="n">
         <v>635.2634769317179</v>
@@ -11566,10 +11566,10 @@
         <v>695.2434828080966</v>
       </c>
       <c r="AD48" s="377" t="n">
-        <v>60.98696007190096</v>
+        <v>59.23364431642874</v>
       </c>
       <c r="AE48" s="372" t="n">
-        <v>67.08483382352672</v>
+        <v>67.08483382352674</v>
       </c>
       <c r="AF48" s="372" t="n">
         <v>73.82322463750509</v>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="AK48" s="379" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="AL48" s="375" t="n">
-        <v>19183960.51387433</v>
+        <v>19183960.51387434</v>
       </c>
       <c r="AM48" s="375" t="n">
         <v>21292132.6666085</v>
@@ -11601,10 +11601,10 @@
         <v>26436153.51971607</v>
       </c>
       <c r="AP48" s="381" t="n">
-        <v>543.3579282078591</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="AQ48" s="372" t="n">
-        <v>592.4143209560447</v>
+        <v>592.4143209560448</v>
       </c>
       <c r="AR48" s="372" t="n">
         <v>635.2634769317179</v>
@@ -11616,10 +11616,10 @@
         <v>695.2434828080965</v>
       </c>
       <c r="AU48" s="372" t="n">
-        <v>60.98696007189881</v>
+        <v>59.23364431642665</v>
       </c>
       <c r="AV48" s="372" t="n">
-        <v>67.08483382361587</v>
+        <v>67.08483382361588</v>
       </c>
       <c r="AW48" s="372" t="n">
         <v>73.82322463761514</v>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="BB48" s="391" t="n">
-        <v>18145366.66198264</v>
+        <v>17623277.56780678</v>
       </c>
       <c r="BC48" s="375" t="n">
         <v>20827071.7994427</v>
@@ -11651,7 +11651,7 @@
         <v>31269424.80021711</v>
       </c>
       <c r="BG48" s="386" t="n">
-        <v>570.058707135829</v>
+        <v>553.656644858456</v>
       </c>
       <c r="BH48" s="372" t="n">
         <v>643.1547640356271</v>
@@ -11660,13 +11660,13 @@
         <v>709.9457672218625</v>
       </c>
       <c r="BJ48" s="372" t="n">
-        <v>765.5420174799297</v>
+        <v>765.5420174799298</v>
       </c>
       <c r="BK48" s="387" t="n">
-        <v>822.3535162668514</v>
+        <v>822.3535162668516</v>
       </c>
       <c r="BL48" s="386" t="n">
-        <v>63.98387840847226</v>
+        <v>62.14289686522648</v>
       </c>
       <c r="BM48" s="372" t="n">
         <v>72.83066756145858</v>
@@ -11675,7 +11675,7 @@
         <v>82.50196612480052</v>
       </c>
       <c r="BO48" s="372" t="n">
-        <v>93.26723889661682</v>
+        <v>93.26723889661683</v>
       </c>
       <c r="BP48" s="387" t="n">
         <v>106.2333528699406</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="BT48" s="375" t="n">
         <v>21059235.76827997</v>
@@ -11695,13 +11695,13 @@
         <v>24238761.05928575</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>27803693.30867689</v>
+        <v>27803693.3086769</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>32206587.52847742</v>
+        <v>32206587.52847743</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>565.9192085784429</v>
+        <v>549.6624886650515</v>
       </c>
       <c r="BY48" s="372" t="n">
         <v>638.8223657606205</v>
@@ -11710,13 +11710,13 @@
         <v>705.4139092635713</v>
       </c>
       <c r="CA48" s="372" t="n">
-        <v>760.7698486938721</v>
+        <v>760.7698486938722</v>
       </c>
       <c r="CB48" s="387" t="n">
-        <v>817.4365363584238</v>
+        <v>817.436536358424</v>
       </c>
       <c r="CC48" s="386" t="n">
-        <v>64.22809749564799</v>
+        <v>62.38306701120912</v>
       </c>
       <c r="CD48" s="372" t="n">
         <v>73.73847235601929</v>
@@ -11725,7 +11725,7 @@
         <v>84.15862152067098</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>95.72698289669464</v>
+        <v>95.72698289669465</v>
       </c>
       <c r="CG48" s="387" t="n">
         <v>109.600041072678</v>
@@ -11738,10 +11738,10 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030711</v>
       </c>
       <c r="D49" s="375" t="n">
-        <v>9115116.960997043</v>
+        <v>9115116.960997041</v>
       </c>
       <c r="E49" s="375" t="n">
         <v>10279895.17897305</v>
@@ -11753,22 +11753,22 @@
         <v>13222813.69470703</v>
       </c>
       <c r="H49" s="371" t="n">
-        <v>689.0139876707992</v>
+        <v>670.5753698135665</v>
       </c>
       <c r="I49" s="372" t="n">
-        <v>740.2150388191861</v>
+        <v>740.215038819186</v>
       </c>
       <c r="J49" s="372" t="n">
         <v>782.8499299882747</v>
       </c>
       <c r="K49" s="372" t="n">
-        <v>816.3581376986849</v>
+        <v>816.358137698685</v>
       </c>
       <c r="L49" s="373" t="n">
         <v>845.1258806413747</v>
       </c>
       <c r="M49" s="371" t="n">
-        <v>117.5045481763804</v>
+        <v>114.3600235381574</v>
       </c>
       <c r="N49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030711</v>
       </c>
       <c r="U49" s="375" t="n">
-        <v>9115116.960997043</v>
+        <v>9115116.960997041</v>
       </c>
       <c r="V49" s="375" t="n">
         <v>10279895.17897305</v>
@@ -11803,22 +11803,22 @@
         <v>13222813.69470703</v>
       </c>
       <c r="Y49" s="377" t="n">
-        <v>689.0139876707992</v>
+        <v>670.5753698135665</v>
       </c>
       <c r="Z49" s="372" t="n">
-        <v>740.2150388191861</v>
+        <v>740.215038819186</v>
       </c>
       <c r="AA49" s="372" t="n">
         <v>782.8499299882747</v>
       </c>
       <c r="AB49" s="372" t="n">
-        <v>816.3581376986849</v>
+        <v>816.358137698685</v>
       </c>
       <c r="AC49" s="378" t="n">
         <v>845.1258806413747</v>
       </c>
       <c r="AD49" s="377" t="n">
-        <v>117.5045481763804</v>
+        <v>114.3600235381574</v>
       </c>
       <c r="AE49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030711</v>
       </c>
       <c r="AL49" s="375" t="n">
-        <v>9115116.960997043</v>
+        <v>9115116.960997041</v>
       </c>
       <c r="AM49" s="375" t="n">
         <v>10279895.17897305</v>
@@ -11853,22 +11853,22 @@
         <v>13222813.69470703</v>
       </c>
       <c r="AP49" s="381" t="n">
-        <v>689.0139876707992</v>
+        <v>670.5753698135665</v>
       </c>
       <c r="AQ49" s="372" t="n">
-        <v>740.215038819186</v>
+        <v>740.2150388191859</v>
       </c>
       <c r="AR49" s="372" t="n">
         <v>782.8499299882745</v>
       </c>
       <c r="AS49" s="372" t="n">
-        <v>816.3581376986849</v>
+        <v>816.358137698685</v>
       </c>
       <c r="AT49" s="382" t="n">
         <v>845.1258806413746</v>
       </c>
       <c r="AU49" s="372" t="n">
-        <v>117.504548176689</v>
+        <v>114.3600235384578</v>
       </c>
       <c r="AV49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="BB49" s="391" t="n">
-        <v>8457336.565185849</v>
+        <v>8231098.090937469</v>
       </c>
       <c r="BC49" s="375" t="n">
         <v>9899032.909102421</v>
@@ -11897,13 +11897,13 @@
         <v>11491546.87076943</v>
       </c>
       <c r="BE49" s="375" t="n">
-        <v>13372452.85318192</v>
+        <v>13372452.85318191</v>
       </c>
       <c r="BF49" s="392" t="n">
-        <v>15643425.7290032</v>
+        <v>15643425.72900321</v>
       </c>
       <c r="BG49" s="386" t="n">
-        <v>723.7433022277532</v>
+        <v>704.382764878736</v>
       </c>
       <c r="BH49" s="372" t="n">
         <v>803.8748224994966</v>
@@ -11912,13 +11912,13 @@
         <v>875.1214391407373</v>
       </c>
       <c r="BJ49" s="372" t="n">
-        <v>939.1188934121109</v>
+        <v>939.1188934121107</v>
       </c>
       <c r="BK49" s="387" t="n">
-        <v>999.8374211960561</v>
+        <v>999.8374211960563</v>
       </c>
       <c r="BL49" s="386" t="n">
-        <v>123.4272906587339</v>
+        <v>120.1255417329325</v>
       </c>
       <c r="BM49" s="372" t="n">
         <v>141.8952609415696</v>
@@ -11927,7 +11927,7 @@
         <v>161.6139676948591</v>
       </c>
       <c r="BO49" s="372" t="n">
-        <v>184.2044240277573</v>
+        <v>184.2044240277572</v>
       </c>
       <c r="BP49" s="387" t="n">
         <v>209.8632088097835</v>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="BS49" s="391" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497285</v>
       </c>
       <c r="BT49" s="375" t="n">
         <v>9953819.634386763</v>
@@ -11953,7 +11953,7 @@
         <v>15904695.7160234</v>
       </c>
       <c r="BX49" s="386" t="n">
-        <v>722.1684705463732</v>
+        <v>702.9417983956207</v>
       </c>
       <c r="BY49" s="372" t="n">
         <v>802.4595414853076</v>
@@ -11962,13 +11962,13 @@
         <v>873.8600366281723</v>
       </c>
       <c r="CA49" s="372" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542811</v>
       </c>
       <c r="CB49" s="387" t="n">
-        <v>998.6845632146761</v>
+        <v>998.6845632146762</v>
       </c>
       <c r="CC49" s="386" t="n">
-        <v>123.7073357614998</v>
+        <v>120.4138101032417</v>
       </c>
       <c r="CD49" s="372" t="n">
         <v>142.9736890264484</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="C50" s="454" t="n">
-        <v>71146187.32989205</v>
+        <v>71146187.32989207</v>
       </c>
       <c r="D50" s="375" t="n">
         <v>79803883.49063842</v>
@@ -12005,7 +12005,7 @@
         <v>121670204.0056975</v>
       </c>
       <c r="H50" s="371" t="n">
-        <v>3210.841122479659</v>
+        <v>3210.84112247966</v>
       </c>
       <c r="I50" s="372" t="n">
         <v>3266.727771821991</v>
@@ -12020,7 +12020,7 @@
         <v>3639.57085916715</v>
       </c>
       <c r="M50" s="372" t="n">
-        <v>2823.987813339367</v>
+        <v>2823.987813339368</v>
       </c>
       <c r="N50" s="372" t="n">
         <v>2869.321462856016</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="T50" s="401" t="n">
-        <v>71146187.32989205</v>
+        <v>71146187.32989207</v>
       </c>
       <c r="U50" s="402" t="n">
         <v>79803883.49063842</v>
@@ -12055,7 +12055,7 @@
         <v>121670204.0056975</v>
       </c>
       <c r="Y50" s="404" t="n">
-        <v>3210.841122479659</v>
+        <v>3210.84112247966</v>
       </c>
       <c r="Z50" s="405" t="n">
         <v>3266.727771821991</v>
@@ -12070,7 +12070,7 @@
         <v>3639.57085916715</v>
       </c>
       <c r="AD50" s="405" t="n">
-        <v>2823.987813339367</v>
+        <v>2823.987813339368</v>
       </c>
       <c r="AE50" s="405" t="n">
         <v>2869.321462856016</v>
@@ -12096,7 +12096,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="AM50" s="458" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="AN50" s="458" t="n">
         <v>104824680.999119</v>
@@ -12111,10 +12111,10 @@
         <v>3266.727771821991</v>
       </c>
       <c r="AR50" s="411" t="n">
-        <v>3389.394385627783</v>
+        <v>3389.394385627784</v>
       </c>
       <c r="AS50" s="411" t="n">
-        <v>3503.631779582347</v>
+        <v>3503.631779582348</v>
       </c>
       <c r="AT50" s="412" t="n">
         <v>3639.57085916715</v>
@@ -12126,7 +12126,7 @@
         <v>2869.321462784832</v>
       </c>
       <c r="AW50" s="411" t="n">
-        <v>2976.398170657375</v>
+        <v>2976.398170657376</v>
       </c>
       <c r="AX50" s="411" t="n">
         <v>3073.152424049543</v>
@@ -12149,7 +12149,7 @@
         <v>101643871.5811244</v>
       </c>
       <c r="BE50" s="420" t="n">
-        <v>118745142.8878008</v>
+        <v>118745142.8878007</v>
       </c>
       <c r="BF50" s="421" t="n">
         <v>140781626.0133759</v>
@@ -12164,7 +12164,7 @@
         <v>3760.113633814127</v>
       </c>
       <c r="BJ50" s="417" t="n">
-        <v>3968.905531858876</v>
+        <v>3968.905531858875</v>
       </c>
       <c r="BK50" s="418" t="n">
         <v>4211.258686805993</v>
@@ -12205,7 +12205,7 @@
         <v>134573833.4912403</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>3301.597169367806</v>
+        <v>3301.597169367807</v>
       </c>
       <c r="BY50" s="417" t="n">
         <v>3480.273585109801</v>
@@ -12220,7 +12220,7 @@
         <v>4130.885314437096</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>2900.977332425373</v>
+        <v>2900.977332425374</v>
       </c>
       <c r="CD50" s="417" t="n">
         <v>3057.045126093473</v>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="C51" s="425" t="n">
-        <v>143087457.162364</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="D51" s="425" t="n">
         <v>161554460.3331398</v>
@@ -12257,7 +12257,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="H51" s="427" t="n">
-        <v>643.4278121963389</v>
+        <v>632.3075664425172</v>
       </c>
       <c r="I51" s="427" t="n">
         <v>691.8930211314048</v>
@@ -12272,7 +12272,7 @@
         <v>839.2584702569818</v>
       </c>
       <c r="M51" s="427" t="n">
-        <v>87.16322845884336</v>
+        <v>85.65680224787461</v>
       </c>
       <c r="N51" s="427" t="n">
         <v>96.81008953305006</v>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="T51" s="429" t="n">
-        <v>143087457.162364</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="U51" s="430" t="n">
         <v>161554460.3331398</v>
@@ -12307,7 +12307,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="Y51" s="432" t="n">
-        <v>643.4278121963389</v>
+        <v>632.3075664425172</v>
       </c>
       <c r="Z51" s="433" t="n">
         <v>691.8930211314047</v>
@@ -12319,10 +12319,10 @@
         <v>790.9658363967468</v>
       </c>
       <c r="AC51" s="434" t="n">
-        <v>839.2584702569819</v>
+        <v>839.2584702569818</v>
       </c>
       <c r="AD51" s="433" t="n">
-        <v>87.16322845884336</v>
+        <v>85.65680224787461</v>
       </c>
       <c r="AE51" s="433" t="n">
         <v>96.81008953305005</v>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="AK51" s="435" t="n">
-        <v>143087457.162364</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="AL51" s="408" t="n">
         <v>161554460.3331398</v>
@@ -12357,13 +12357,13 @@
         <v>238392091.3734576</v>
       </c>
       <c r="AP51" s="436" t="n">
-        <v>643.4560481864537</v>
+        <v>632.3353144351547</v>
       </c>
       <c r="AQ51" s="437" t="n">
         <v>691.9291685699586</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>745.0783588279978</v>
+        <v>745.0783588279979</v>
       </c>
       <c r="AS51" s="437" t="n">
         <v>791.0186850048551</v>
@@ -12372,7 +12372,7 @@
         <v>839.3207535392833</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>87.16374660646318</v>
+        <v>85.65731144044345</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>96.81079718765081</v>
@@ -12392,37 +12392,37 @@
         </is>
       </c>
       <c r="BB51" s="439" t="n">
-        <v>150070694.4261914</v>
+        <v>147474098.4705076</v>
       </c>
       <c r="BC51" s="440" t="n">
-        <v>175447968.0233844</v>
+        <v>175447968.0233843</v>
       </c>
       <c r="BD51" s="440" t="n">
-        <v>204360322.2613969</v>
+        <v>204360322.261397</v>
       </c>
       <c r="BE51" s="440" t="n">
         <v>237268936.6235472</v>
       </c>
       <c r="BF51" s="441" t="n">
-        <v>278727881.2071358</v>
+        <v>278727881.2071357</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>674.8592636914437</v>
+        <v>663.1825213304039</v>
       </c>
       <c r="BH51" s="443" t="n">
-        <v>751.4343237034519</v>
+        <v>751.4343237034518</v>
       </c>
       <c r="BI51" s="443" t="n">
-        <v>829.3004454977289</v>
+        <v>829.300445497729</v>
       </c>
       <c r="BJ51" s="443" t="n">
-        <v>902.523089946622</v>
+        <v>902.5230899466218</v>
       </c>
       <c r="BK51" s="444" t="n">
-        <v>981.3332897889413</v>
+        <v>981.3332897889409</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>91.41768427107884</v>
+        <v>89.83593115023213</v>
       </c>
       <c r="BM51" s="443" t="n">
         <v>105.1364203394458</v>
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="BT51" s="440" t="n">
         <v>172068464.5824613</v>
@@ -12457,10 +12457,10 @@
         <v>275804109.0927686</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>657.0470490053042</v>
+        <v>645.4331663318603</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>730.2612503871813</v>
+        <v>730.2612503871812</v>
       </c>
       <c r="BZ51" s="417" t="n">
         <v>804.6209467801377</v>
@@ -12469,10 +12469,10 @@
         <v>874.2429304181999</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>949.4161303554341</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>89.46793559178859</v>
+        <v>87.8865113869751</v>
       </c>
       <c r="CD51" s="417" t="n">
         <v>103.3237569100109</v>
@@ -13668,13 +13668,13 @@
         <v>2879.554573333057</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.009848161142163607</v>
+        <v>0.009848161142163608</v>
       </c>
       <c r="DD58" s="394" t="n">
         <v>0.01024095992489387</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.01065955492973541</v>
+        <v>0.0106595549297354</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.01099740955273805</v>
@@ -13968,13 +13968,13 @@
         <v>372.0859813343213</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315903</v>
       </c>
       <c r="CZ59" s="103" t="n">
         <v>446.7528256294415</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>490.9710966469168</v>
+        <v>490.971096646917</v>
       </c>
       <c r="DC59" s="396" t="n">
         <v>0.009375041997651625</v>
@@ -13986,7 +13986,7 @@
         <v>0.01026840829288288</v>
       </c>
       <c r="DF59" s="397" t="n">
-        <v>0.01058323089473215</v>
+        <v>0.01058323089473216</v>
       </c>
       <c r="DG59" s="398" t="n">
         <v>0.01076943133572349</v>
@@ -14538,7 +14538,7 @@
         <v>32577.47994622752</v>
       </c>
       <c r="CC61" s="212" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="CD61" s="212" t="n">
         <v>27059.18855224806</v>
@@ -14580,19 +14580,19 @@
         <v>837210</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>663.9327169755761</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CX61" s="133" t="n">
         <v>753.6182474419381</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>854.169368624498</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>950.5574286398316</v>
+        <v>950.5574286398318</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0.0294741231667958</v>
@@ -14601,13 +14601,13 @@
         <v>0.03031253335912443</v>
       </c>
       <c r="DE61" s="423" t="n">
-        <v>0.03101698224883411</v>
+        <v>0.0310169822488341</v>
       </c>
       <c r="DF61" s="423" t="n">
         <v>0.03114673314234719</v>
       </c>
       <c r="DG61" s="424" t="n">
-        <v>0.03202818225091575</v>
+        <v>0.03202818225091576</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" thickBot="1">
@@ -14832,7 +14832,7 @@
         <v>1459680.857487855</v>
       </c>
       <c r="BX62" s="221" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="BY62" s="222" t="n">
         <v>235625.9003079122</v>
@@ -14844,7 +14844,7 @@
         <v>267900.6531999434</v>
       </c>
       <c r="CB62" s="214" t="n">
-        <v>290498.6551992912</v>
+        <v>290498.6551992913</v>
       </c>
       <c r="CC62" s="222" t="n">
         <v>1638486.346797842</v>
@@ -14892,10 +14892,10 @@
         <v>3107.351651027931</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.87611565303</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218107</v>
       </c>
       <c r="CZ62" s="133" t="n">
         <v>4186.715162875308</v>
@@ -15778,7 +15778,7 @@
         <v>0.7041227667525718</v>
       </c>
       <c r="CA67" s="463" t="n">
-        <v>0.721646058437451</v>
+        <v>0.7216460584374508</v>
       </c>
       <c r="CB67" s="464" t="n">
         <v>0.74335960479618</v>
@@ -16026,7 +16026,7 @@
         <v>22795.83730997828</v>
       </c>
       <c r="BV68" s="237" t="n">
-        <v>24689.40128114245</v>
+        <v>24689.40128114244</v>
       </c>
       <c r="BW68" s="238" t="n">
         <v>27292.71916327555</v>
@@ -16041,10 +16041,10 @@
         <v>0.6763319833499948</v>
       </c>
       <c r="CA68" s="463" t="n">
-        <v>0.6929421555022223</v>
+        <v>0.6929421555022222</v>
       </c>
       <c r="CB68" s="464" t="n">
-        <v>0.714253308151782</v>
+        <v>0.7142533081517819</v>
       </c>
       <c r="CC68" s="197" t="n">
         <v>19824.70474124874</v>
@@ -16286,7 +16286,7 @@
         <v>8517.104467793557</v>
       </c>
       <c r="BU69" s="237" t="n">
-        <v>9425.600245674357</v>
+        <v>9425.600245674355</v>
       </c>
       <c r="BV69" s="237" t="n">
         <v>10560.09983204437</v>
@@ -16301,13 +16301,13 @@
         <v>0.688096819087734</v>
       </c>
       <c r="BZ69" s="463" t="n">
-        <v>0.7144401067588553</v>
+        <v>0.7144401067588552</v>
       </c>
       <c r="CA69" s="463" t="n">
-        <v>0.73849796762568</v>
+        <v>0.7384979676256799</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.7670945895092585</v>
+        <v>0.7670945895092586</v>
       </c>
       <c r="CC69" s="197" t="n">
         <v>7684.536209253197</v>
@@ -16316,13 +16316,13 @@
         <v>8535.248537910204</v>
       </c>
       <c r="CE69" s="190" t="n">
-        <v>9489.331482271567</v>
+        <v>9489.331482271566</v>
       </c>
       <c r="CF69" s="190" t="n">
         <v>10673.33792484693</v>
       </c>
       <c r="CG69" s="198" t="n">
-        <v>12216.47603351414</v>
+        <v>12216.47603351415</v>
       </c>
       <c r="CW69" s="465" t="n"/>
       <c r="CX69" s="465" t="n"/>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="BS70" s="254" t="n">
-        <v>15709.70744138703</v>
+        <v>15709.70744138704</v>
       </c>
       <c r="BT70" s="255" t="n">
         <v>17732.88691759677</v>
@@ -16552,22 +16552,22 @@
         <v>19920.31722773356</v>
       </c>
       <c r="BV70" s="255" t="n">
-        <v>22371.86578071989</v>
+        <v>22371.86578071988</v>
       </c>
       <c r="BW70" s="256" t="n">
         <v>25652.86382685493</v>
       </c>
       <c r="BX70" s="466" t="n">
-        <v>0.7000174703382455</v>
+        <v>0.7000174703382456</v>
       </c>
       <c r="BY70" s="467" t="n">
         <v>0.7171947087988736</v>
       </c>
       <c r="BZ70" s="467" t="n">
-        <v>0.7283718889056493</v>
+        <v>0.7283718889056494</v>
       </c>
       <c r="CA70" s="467" t="n">
-        <v>0.7395256919006069</v>
+        <v>0.7395256919006068</v>
       </c>
       <c r="CB70" s="468" t="n">
         <v>0.7595570753160313</v>
@@ -16579,10 +16579,10 @@
         <v>17046.69967774026</v>
       </c>
       <c r="CE70" s="212" t="n">
-        <v>19164.59816197564</v>
+        <v>19164.59816197565</v>
       </c>
       <c r="CF70" s="212" t="n">
-        <v>21557.50857484998</v>
+        <v>21557.50857484997</v>
       </c>
       <c r="CG70" s="213" t="n">
         <v>24744.45538912324</v>
@@ -16630,7 +16630,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="K71" s="215" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="L71" s="216" t="n">
         <v>11125.79579552732</v>
@@ -16680,7 +16680,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="AB71" s="218" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="AC71" s="219" t="n">
         <v>11125.79579552732</v>
@@ -16815,7 +16815,7 @@
         <v>174456.5589318115</v>
       </c>
       <c r="BV71" s="272" t="n">
-        <v>190597.6540256326</v>
+        <v>190597.6540256325</v>
       </c>
       <c r="BW71" s="273" t="n">
         <v>212088.9797710218</v>
@@ -16824,16 +16824,16 @@
         <v>0.64795100239417</v>
       </c>
       <c r="BY71" s="467" t="n">
-        <v>0.6803922139883308</v>
+        <v>0.6803922139883307</v>
       </c>
       <c r="BZ71" s="467" t="n">
         <v>0.703403312819713</v>
       </c>
       <c r="CA71" s="467" t="n">
-        <v>0.7205849213555851</v>
+        <v>0.7205849213555849</v>
       </c>
       <c r="CB71" s="468" t="n">
-        <v>0.7425296329386262</v>
+        <v>0.7425296329386261</v>
       </c>
       <c r="CC71" s="212" t="n">
         <v>144562.5965727818</v>
@@ -18502,7 +18502,7 @@
         <v>0</v>
       </c>
       <c r="BX79" s="466" t="n">
-        <v>0.1213412225632432</v>
+        <v>0.1213412225632433</v>
       </c>
       <c r="BY79" s="467" t="n">
         <v>0.1216078129107701</v>
@@ -18575,7 +18575,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="N80" s="495" t="n">
-        <v>0.8567393958367391</v>
+        <v>0.856739395836739</v>
       </c>
       <c r="O80" s="495" t="n">
         <v>0.8502780977298359</v>
@@ -18625,7 +18625,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="AE80" s="498" t="n">
-        <v>0.8567393958367391</v>
+        <v>0.856739395836739</v>
       </c>
       <c r="AF80" s="498" t="n">
         <v>0.8502780977298359</v>
@@ -18657,22 +18657,22 @@
         <v>1459680.857487855</v>
       </c>
       <c r="AP80" s="500" t="n">
-        <v>0.8645381501158789</v>
+        <v>0.864538150115879</v>
       </c>
       <c r="AQ80" s="501" t="n">
         <v>0.8600856827762674</v>
       </c>
       <c r="AR80" s="501" t="n">
-        <v>0.8546254776696</v>
+        <v>0.8546254776696001</v>
       </c>
       <c r="AS80" s="501" t="n">
-        <v>0.8472774569104101</v>
+        <v>0.84727745691041</v>
       </c>
       <c r="AT80" s="502" t="n">
         <v>0.8381445708353271</v>
       </c>
       <c r="AU80" s="501" t="n">
-        <v>0.862198150115879</v>
+        <v>0.8621981501158791</v>
       </c>
       <c r="AV80" s="501" t="n">
         <v>0.8567456827762674</v>
@@ -18681,7 +18681,7 @@
         <v>0.8502854776696002</v>
       </c>
       <c r="AX80" s="501" t="n">
-        <v>0.84193745691041</v>
+        <v>0.8419374569104099</v>
       </c>
       <c r="AY80" s="502" t="n">
         <v>0.8318045708353272</v>
@@ -18707,22 +18707,22 @@
         <v>1459680.857487855</v>
       </c>
       <c r="BG80" s="503" t="n">
-        <v>0.8645381501158789</v>
+        <v>0.864538150115879</v>
       </c>
       <c r="BH80" s="504" t="n">
         <v>0.8600856827762674</v>
       </c>
       <c r="BI80" s="504" t="n">
-        <v>0.8546254776696</v>
+        <v>0.8546254776696001</v>
       </c>
       <c r="BJ80" s="504" t="n">
-        <v>0.8472774569104101</v>
+        <v>0.84727745691041</v>
       </c>
       <c r="BK80" s="505" t="n">
         <v>0.8381445708353271</v>
       </c>
       <c r="BL80" s="504" t="n">
-        <v>0.862198150115879</v>
+        <v>0.8621981501158791</v>
       </c>
       <c r="BM80" s="504" t="n">
         <v>0.8567456827762674</v>
@@ -18731,7 +18731,7 @@
         <v>0.8502854776696002</v>
       </c>
       <c r="BO80" s="504" t="n">
-        <v>0.84193745691041</v>
+        <v>0.8419374569104099</v>
       </c>
       <c r="BP80" s="505" t="n">
         <v>0.8318045708353272</v>
@@ -18766,7 +18766,7 @@
         <v>0.8521951419395463</v>
       </c>
       <c r="CA80" s="504" t="n">
-        <v>0.8439901848630272</v>
+        <v>0.8439901848630273</v>
       </c>
       <c r="CB80" s="505" t="n">
         <v>0.8340177946928011</v>
@@ -19443,7 +19443,7 @@
         <v>173883609.5679228</v>
       </c>
       <c r="AO87" s="380" t="n">
-        <v>181212790.6116943</v>
+        <v>181212790.6116944</v>
       </c>
       <c r="AP87" s="381" t="n">
         <v>138.6418887510874</v>
@@ -19458,7 +19458,7 @@
         <v>152.4634568955569</v>
       </c>
       <c r="AT87" s="382" t="n">
-        <v>157.4387342265009</v>
+        <v>157.438734226501</v>
       </c>
       <c r="BA87" s="83" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>173883609.5679228</v>
       </c>
       <c r="BF87" s="392" t="n">
-        <v>181212790.6116943</v>
+        <v>181212790.6116944</v>
       </c>
       <c r="BG87" s="386" t="n">
         <v>138.6418887510874</v>
@@ -19493,7 +19493,7 @@
         <v>152.4634568955569</v>
       </c>
       <c r="BK87" s="387" t="n">
-        <v>157.4387342265009</v>
+        <v>157.438734226501</v>
       </c>
       <c r="BR87" s="83" t="inlineStr">
         <is>
@@ -19528,25 +19528,25 @@
         <v>152.4634568955569</v>
       </c>
       <c r="CB87" s="387" t="n">
-        <v>157.4387342265009</v>
+        <v>157.438734226501</v>
       </c>
       <c r="CI87" s="199" t="n">
-        <v>140012326.4220065</v>
+        <v>140012326.4220066</v>
       </c>
       <c r="CJ87" s="201" t="n">
-        <v>101860600.7648326</v>
+        <v>101860600.7648325</v>
       </c>
       <c r="CK87" s="344" t="n">
-        <v>241872927.1868391</v>
+        <v>241872927.1868392</v>
       </c>
       <c r="CL87" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950559</v>
       </c>
       <c r="CM87" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064114</v>
       </c>
       <c r="CN87" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018314</v>
       </c>
     </row>
     <row r="88">
@@ -19626,22 +19626,22 @@
         </is>
       </c>
       <c r="AK88" s="506" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557581</v>
       </c>
       <c r="AL88" s="368" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="AM88" s="368" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="AN88" s="368" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="AO88" s="380" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="AP88" s="381" t="n">
-        <v>395.696041549289</v>
+        <v>395.6960415492891</v>
       </c>
       <c r="AQ88" s="372" t="n">
         <v>405.6559433826607</v>
@@ -19650,10 +19650,10 @@
         <v>415.6208472109494</v>
       </c>
       <c r="AS88" s="372" t="n">
-        <v>427.1601692831934</v>
+        <v>427.1601692831933</v>
       </c>
       <c r="AT88" s="382" t="n">
-        <v>437.5536311497444</v>
+        <v>437.5536311497445</v>
       </c>
       <c r="BA88" s="101" t="inlineStr">
         <is>
@@ -19661,22 +19661,22 @@
         </is>
       </c>
       <c r="BB88" s="391" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557581</v>
       </c>
       <c r="BC88" s="375" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="BD88" s="375" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="BE88" s="375" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="BF88" s="392" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="BG88" s="386" t="n">
-        <v>395.696041549289</v>
+        <v>395.6960415492891</v>
       </c>
       <c r="BH88" s="372" t="n">
         <v>405.6559433826607</v>
@@ -19685,10 +19685,10 @@
         <v>415.6208472109494</v>
       </c>
       <c r="BJ88" s="372" t="n">
-        <v>427.1601692831934</v>
+        <v>427.1601692831933</v>
       </c>
       <c r="BK88" s="387" t="n">
-        <v>437.5536311497444</v>
+        <v>437.5536311497445</v>
       </c>
       <c r="BR88" s="101" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         </is>
       </c>
       <c r="BS88" s="391" t="n">
-        <v>99358676.85064487</v>
+        <v>99358676.85064489</v>
       </c>
       <c r="BT88" s="375" t="n">
         <v>102480003.1332629</v>
@@ -19711,7 +19711,7 @@
         <v>111338199.0650384</v>
       </c>
       <c r="BX88" s="386" t="n">
-        <v>395.696041549289</v>
+        <v>395.6960415492891</v>
       </c>
       <c r="BY88" s="372" t="n">
         <v>405.6559433826607</v>
@@ -19720,13 +19720,13 @@
         <v>415.6208472109494</v>
       </c>
       <c r="CA88" s="372" t="n">
-        <v>427.1601692831934</v>
+        <v>427.1601692831933</v>
       </c>
       <c r="CB88" s="387" t="n">
-        <v>437.5536311497444</v>
+        <v>437.5536311497445</v>
       </c>
       <c r="CI88" s="197" t="n">
-        <v>92468586.6202051</v>
+        <v>92468586.62020506</v>
       </c>
       <c r="CJ88" s="198" t="n">
         <v>50146632.66768061</v>
@@ -19735,13 +19735,13 @@
         <v>142615219.2878857</v>
       </c>
       <c r="CL88" s="386" t="n">
-        <v>373.770530490655</v>
+        <v>373.7705304906548</v>
       </c>
       <c r="CM88" s="387" t="n">
         <v>1595.654458512763</v>
       </c>
       <c r="CN88" s="508" t="n">
-        <v>511.4938232338516</v>
+        <v>511.4938232338513</v>
       </c>
     </row>
     <row r="89">
@@ -19830,7 +19830,7 @@
         <v>26068955.30914956</v>
       </c>
       <c r="AN89" s="368" t="n">
-        <v>26915839.64328328</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="AO89" s="380" t="n">
         <v>27898487.10720396</v>
@@ -19845,7 +19845,7 @@
         <v>449.6699082011643</v>
       </c>
       <c r="AS89" s="372" t="n">
-        <v>461.2323301146864</v>
+        <v>461.2323301146865</v>
       </c>
       <c r="AT89" s="382" t="n">
         <v>473.6980203171656</v>
@@ -19865,7 +19865,7 @@
         <v>26068955.30914956</v>
       </c>
       <c r="BE89" s="375" t="n">
-        <v>26915839.64328328</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="BF89" s="392" t="n">
         <v>27898487.10720396</v>
@@ -19880,7 +19880,7 @@
         <v>449.6699082011643</v>
       </c>
       <c r="BJ89" s="372" t="n">
-        <v>461.2323301146864</v>
+        <v>461.2323301146865</v>
       </c>
       <c r="BK89" s="387" t="n">
         <v>473.6980203171656</v>
@@ -19900,7 +19900,7 @@
         <v>25930189.281765</v>
       </c>
       <c r="BV89" s="375" t="n">
-        <v>26737037.7893205</v>
+        <v>26737037.78932051</v>
       </c>
       <c r="BW89" s="392" t="n">
         <v>27674622.0124554</v>
@@ -19915,28 +19915,28 @@
         <v>449.6699082011643</v>
       </c>
       <c r="CA89" s="372" t="n">
-        <v>461.2323301146864</v>
+        <v>461.2323301146865</v>
       </c>
       <c r="CB89" s="387" t="n">
         <v>473.6980203171656</v>
       </c>
       <c r="CI89" s="197" t="n">
-        <v>22520192.04029756</v>
+        <v>22520192.04029757</v>
       </c>
       <c r="CJ89" s="198" t="n">
-        <v>23188084.77820082</v>
+        <v>23188084.77820083</v>
       </c>
       <c r="CK89" s="346" t="n">
-        <v>45708276.81849838</v>
+        <v>45708276.8184984</v>
       </c>
       <c r="CL89" s="386" t="n">
-        <v>408.0188433579295</v>
+        <v>408.0188433579297</v>
       </c>
       <c r="CM89" s="387" t="n">
-        <v>2158.838541867686</v>
+        <v>2158.838541867688</v>
       </c>
       <c r="CN89" s="508" t="n">
-        <v>693.2323776218758</v>
+        <v>693.2323776218761</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" thickBot="1">
@@ -20116,16 +20116,16 @@
         <v>10051.38944352971</v>
       </c>
       <c r="CI90" s="211" t="n">
-        <v>17230897.74462213</v>
+        <v>17230897.74462212</v>
       </c>
       <c r="CJ90" s="213" t="n">
-        <v>211983483.7044854</v>
+        <v>211983483.7044855</v>
       </c>
       <c r="CK90" s="214" t="n">
         <v>229214381.4491076</v>
       </c>
       <c r="CL90" s="416" t="n">
-        <v>6864.899499849453</v>
+        <v>6864.899499849451</v>
       </c>
       <c r="CM90" s="418" t="n">
         <v>11988.65986339133</v>
@@ -20217,7 +20217,7 @@
         <v>316369942.7622774</v>
       </c>
       <c r="AM91" s="408" t="n">
-        <v>331898217.3375401</v>
+        <v>331898217.33754</v>
       </c>
       <c r="AN91" s="408" t="n">
         <v>350263780.7229214</v>
@@ -20232,13 +20232,13 @@
         <v>220.4237268581867</v>
       </c>
       <c r="AR91" s="437" t="n">
-        <v>229.1040173800722</v>
+        <v>229.1040173800721</v>
       </c>
       <c r="AS91" s="437" t="n">
         <v>240.1541879531747</v>
       </c>
       <c r="AT91" s="438" t="n">
-        <v>249.7553771891609</v>
+        <v>249.755377189161</v>
       </c>
       <c r="BA91" s="155" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>316369942.7622774</v>
       </c>
       <c r="BD91" s="440" t="n">
-        <v>331898217.3375401</v>
+        <v>331898217.33754</v>
       </c>
       <c r="BE91" s="440" t="n">
         <v>350263780.7229214</v>
@@ -20267,13 +20267,13 @@
         <v>220.4237268581867</v>
       </c>
       <c r="BI91" s="443" t="n">
-        <v>229.1040173800722</v>
+        <v>229.1040173800721</v>
       </c>
       <c r="BJ91" s="443" t="n">
         <v>240.1541879531747</v>
       </c>
       <c r="BK91" s="444" t="n">
-        <v>249.7553771891609</v>
+        <v>249.755377189161</v>
       </c>
       <c r="BR91" s="155" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>329203076.1069089</v>
       </c>
       <c r="BV91" s="440" t="n">
-        <v>346590229.4588985</v>
+        <v>346590229.4588984</v>
       </c>
       <c r="BW91" s="441" t="n">
         <v>362533508.233274</v>
@@ -20308,7 +20308,7 @@
         <v>239.1426675081981</v>
       </c>
       <c r="CB91" s="444" t="n">
-        <v>248.3649123529663</v>
+        <v>248.3649123529664</v>
       </c>
       <c r="CI91" s="349" t="n">
         <v>272232002.8271313</v>
@@ -20320,7 +20320,7 @@
         <v>659410804.7423308</v>
       </c>
       <c r="CL91" s="509" t="n">
-        <v>197.9014177345432</v>
+        <v>197.9014177345433</v>
       </c>
       <c r="CM91" s="510" t="n">
         <v>1925.419726265115</v>
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="C96" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D96" s="368" t="n">
         <v>141265555.356126</v>
@@ -20902,7 +20902,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H96" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I96" s="372" t="n">
         <v>859.4354544219096</v>
@@ -20922,7 +20922,7 @@
         </is>
       </c>
       <c r="T96" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U96" s="375" t="n">
         <v>141265555.356126</v>
@@ -20937,7 +20937,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y96" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z96" s="372" t="n">
         <v>859.4354544219096</v>
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="AK96" s="506" t="n">
-        <v>126617344.103984</v>
+        <v>126640275.655196</v>
       </c>
       <c r="AL96" s="368" t="n">
         <v>141248374.026126</v>
@@ -20972,7 +20972,7 @@
         <v>194794539.810586</v>
       </c>
       <c r="AP96" s="381" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="AQ96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -20987,7 +20987,7 @@
         <v>989.1578434898606</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>109383903.5623858</v>
+        <v>109406835.1135978</v>
       </c>
       <c r="AV96" s="375" t="n">
         <v>125092448.4504667</v>
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="BB96" s="391" t="n">
-        <v>126617344.103984</v>
+        <v>126640275.655196</v>
       </c>
       <c r="BC96" s="375" t="n">
         <v>141248374.026126</v>
@@ -21022,7 +21022,7 @@
         <v>194794539.810586</v>
       </c>
       <c r="BG96" s="386" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="BH96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -21042,7 +21042,7 @@
         </is>
       </c>
       <c r="BS96" s="391" t="n">
-        <v>127420166.0637988</v>
+        <v>127443243.0133605</v>
       </c>
       <c r="BT96" s="375" t="n">
         <v>143078447.3193804</v>
@@ -21057,7 +21057,7 @@
         <v>200399456.4644709</v>
       </c>
       <c r="BX96" s="386" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="BY96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>91214772.24990708</v>
+        <v>91237642.06254114</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>104988005.1745433</v>
+        <v>104988005.1745432</v>
       </c>
       <c r="DE96" s="375" t="n">
         <v>118016580.220932</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>131624915.604641</v>
+        <v>131624915.6046411</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>150667262.2450605</v>
+        <v>150667262.2450604</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="C97" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D97" s="368" t="n">
         <v>53602589.259965</v>
@@ -21129,7 +21129,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H97" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="T97" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U97" s="375" t="n">
         <v>53602589.259965</v>
@@ -21164,7 +21164,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y97" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="AK97" s="506" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="AL97" s="368" t="n">
         <v>53602589.259965</v>
@@ -21199,7 +21199,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="AP97" s="381" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="AQ97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21214,19 +21214,19 @@
         <v>1911.879093778504</v>
       </c>
       <c r="AU97" s="379" t="n">
-        <v>41689376.3923699</v>
+        <v>41695853.95444989</v>
       </c>
       <c r="AV97" s="375" t="n">
-        <v>46504050.28654233</v>
+        <v>46504050.28654232</v>
       </c>
       <c r="AW97" s="375" t="n">
         <v>51437235.63014472</v>
       </c>
       <c r="AX97" s="375" t="n">
-        <v>56974314.50595677</v>
+        <v>56974314.50595678</v>
       </c>
       <c r="AY97" s="456" t="n">
-        <v>65212950.89794063</v>
+        <v>65212950.89794064</v>
       </c>
       <c r="BA97" s="101" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="BB97" s="391" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="BC97" s="375" t="n">
         <v>53602589.259965</v>
@@ -21249,7 +21249,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="BG97" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BH97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21269,7 +21269,7 @@
         </is>
       </c>
       <c r="BS97" s="391" t="n">
-        <v>50132747.34533089</v>
+        <v>50139289.15891635</v>
       </c>
       <c r="BT97" s="375" t="n">
         <v>54567686.23949162</v>
@@ -21284,7 +21284,7 @@
         <v>75327072.67031734</v>
       </c>
       <c r="BX97" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BY97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21314,19 +21314,19 @@
         <v>0</v>
       </c>
       <c r="DC97" s="391" t="n">
-        <v>34750578.12386221</v>
+        <v>34757061.96014754</v>
       </c>
       <c r="DD97" s="375" t="n">
         <v>39059424.72252001</v>
       </c>
       <c r="DE97" s="375" t="n">
-        <v>43435991.25102003</v>
+        <v>43435991.25102002</v>
       </c>
       <c r="DF97" s="375" t="n">
         <v>48299721.45663895</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>55445858.27455472</v>
+        <v>55445858.27455471</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="C98" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D98" s="368" t="n">
         <v>30609035.168748</v>
@@ -21356,7 +21356,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H98" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="T98" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U98" s="375" t="n">
         <v>30609035.168748</v>
@@ -21391,7 +21391,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y98" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AK98" s="506" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="AL98" s="368" t="n">
         <v>30609035.168748</v>
@@ -21426,7 +21426,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="AP98" s="381" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="AQ98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21441,7 +21441,7 @@
         <v>2797.787340780611</v>
       </c>
       <c r="AU98" s="379" t="n">
-        <v>22190726.19047777</v>
+        <v>22193533.13404577</v>
       </c>
       <c r="AV98" s="375" t="n">
         <v>25281751.22556119</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="BB98" s="391" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="BC98" s="375" t="n">
         <v>30609035.168748</v>
@@ -21476,7 +21476,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="BG98" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BH98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="BS98" s="391" t="n">
-        <v>27524559.52788378</v>
+        <v>27527373.59848597</v>
       </c>
       <c r="BT98" s="375" t="n">
         <v>30832725.79709084</v>
@@ -21511,7 +21511,7 @@
         <v>44556567.68141378</v>
       </c>
       <c r="BX98" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BY98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21541,7 +21541,7 @@
         <v>0</v>
       </c>
       <c r="DC98" s="391" t="n">
-        <v>18936636.22699493</v>
+        <v>18939430.84554148</v>
       </c>
       <c r="DD98" s="375" t="n">
         <v>21655757.83449386</v>
@@ -21550,10 +21550,10 @@
         <v>24654357.0821007</v>
       </c>
       <c r="DF98" s="375" t="n">
-        <v>28165319.75427984</v>
+        <v>28165319.75427985</v>
       </c>
       <c r="DG98" s="392" t="n">
-        <v>32487496.48841153</v>
+        <v>32487496.48841152</v>
       </c>
       <c r="DI98" s="368" t="n"/>
       <c r="DJ98" s="368" t="n"/>
@@ -21680,7 +21680,7 @@
         <v>309202778.7597014</v>
       </c>
       <c r="AY99" s="459" t="n">
-        <v>359467632.6431751</v>
+        <v>359467632.643175</v>
       </c>
       <c r="BA99" s="111" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         </is>
       </c>
       <c r="BS99" s="419" t="n">
-        <v>269873908.3383856</v>
+        <v>269873908.3383855</v>
       </c>
       <c r="BT99" s="420" t="n">
         <v>304550625.5077929</v>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>163797061.6705361</v>
+        <v>163797061.670536</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>188089957.4893995</v>
+        <v>188089957.4893994</v>
       </c>
       <c r="DE99" s="420" t="n">
-        <v>215978942.3423741</v>
+        <v>215978942.3423742</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>246346883.7616734</v>
+        <v>246346883.7616735</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>286688358.6587337</v>
+        <v>286688358.6587338</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="C100" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D100" s="425" t="n">
         <v>538493761.125447</v>
@@ -21810,7 +21810,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="H100" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I100" s="427" t="n">
         <v>2306.219676493023</v>
@@ -21830,7 +21830,7 @@
         </is>
       </c>
       <c r="T100" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U100" s="430" t="n">
         <v>538493761.125447</v>
@@ -21845,7 +21845,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="Y100" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z100" s="433" t="n">
         <v>2306.219676493023</v>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="AK100" s="435" t="n">
-        <v>481161614.8533111</v>
+        <v>481193830.910171</v>
       </c>
       <c r="AL100" s="408" t="n">
-        <v>538476579.7954479</v>
+        <v>538476579.7954481</v>
       </c>
       <c r="AM100" s="408" t="n">
         <v>602828595.0017819</v>
@@ -21880,22 +21880,22 @@
         <v>769448594.4916779</v>
       </c>
       <c r="AP100" s="436" t="n">
-        <v>2163.756050827067</v>
+        <v>2163.900924578033</v>
       </c>
       <c r="AQ100" s="437" t="n">
-        <v>2306.266576508938</v>
+        <v>2306.266576508939</v>
       </c>
       <c r="AR100" s="437" t="n">
         <v>2446.29689786011</v>
       </c>
       <c r="AS100" s="437" t="n">
-        <v>2570.842398783472</v>
+        <v>2570.842398783471</v>
       </c>
       <c r="AT100" s="438" t="n">
         <v>2709.041941860333</v>
       </c>
       <c r="AU100" s="435" t="n">
-        <v>379489526.4173333</v>
+        <v>379521742.4741934</v>
       </c>
       <c r="AV100" s="408" t="n">
         <v>433432828.6743559</v>
@@ -21904,7 +21904,7 @@
         <v>491407974.4457932</v>
       </c>
       <c r="AX100" s="408" t="n">
-        <v>554204976.4714397</v>
+        <v>554204976.4714398</v>
       </c>
       <c r="AY100" s="409" t="n">
         <v>639528011.3196728</v>
@@ -21915,10 +21915,10 @@
         </is>
       </c>
       <c r="BB100" s="439" t="n">
-        <v>481161614.8533111</v>
+        <v>481193830.910171</v>
       </c>
       <c r="BC100" s="440" t="n">
-        <v>538476579.7954479</v>
+        <v>538476579.7954481</v>
       </c>
       <c r="BD100" s="440" t="n">
         <v>602828595.0017819</v>
@@ -21930,16 +21930,16 @@
         <v>769448594.4916779</v>
       </c>
       <c r="BG100" s="442" t="n">
-        <v>2163.756050827067</v>
+        <v>2163.900924578033</v>
       </c>
       <c r="BH100" s="443" t="n">
-        <v>2306.266576508938</v>
+        <v>2306.266576508939</v>
       </c>
       <c r="BI100" s="443" t="n">
         <v>2446.29689786011</v>
       </c>
       <c r="BJ100" s="443" t="n">
-        <v>2570.842398783472</v>
+        <v>2570.842398783471</v>
       </c>
       <c r="BK100" s="444" t="n">
         <v>2709.041941860333</v>
@@ -21950,7 +21950,7 @@
         </is>
       </c>
       <c r="BS100" s="439" t="n">
-        <v>474951381.275399</v>
+        <v>474983814.1091484</v>
       </c>
       <c r="BT100" s="440" t="n">
         <v>533029484.8637558</v>
@@ -21965,7 +21965,7 @@
         <v>766783160.6296258</v>
       </c>
       <c r="BX100" s="442" t="n">
-        <v>2128.802545622182</v>
+        <v>2128.947914394165</v>
       </c>
       <c r="BY100" s="443" t="n">
         <v>2262.185456552957</v>
@@ -21997,16 +21997,16 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>308699048.2713003</v>
+        <v>308731196.5387662</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>353793145.2209566</v>
+        <v>353793145.2209565</v>
       </c>
       <c r="DE100" s="440" t="n">
         <v>402085870.8964269</v>
       </c>
       <c r="DF100" s="440" t="n">
-        <v>454436840.5772332</v>
+        <v>454436840.5772333</v>
       </c>
       <c r="DG100" s="441" t="n">
         <v>525288975.6667606</v>
@@ -23382,13 +23382,13 @@
         <v>372.0859813343213</v>
       </c>
       <c r="BZ109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315903</v>
       </c>
       <c r="CA109" s="190" t="n">
         <v>446.7528256294415</v>
       </c>
       <c r="CB109" s="198" t="n">
-        <v>490.9710966469168</v>
+        <v>490.971096646917</v>
       </c>
       <c r="CC109" s="197" t="n">
         <v>347.8756485030455</v>
@@ -23397,13 +23397,13 @@
         <v>372.0859813343213</v>
       </c>
       <c r="CE109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315903</v>
       </c>
       <c r="CF109" s="190" t="n">
         <v>446.7528256294415</v>
       </c>
       <c r="CG109" s="198" t="n">
-        <v>490.9710966469168</v>
+        <v>490.971096646917</v>
       </c>
       <c r="CI109" s="197" t="n">
         <v>0</v>
@@ -23439,13 +23439,13 @@
         <v>372.0859813343213</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315903</v>
       </c>
       <c r="CZ109" s="190" t="n">
         <v>446.7528256294415</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>490.9710966469168</v>
+        <v>490.971096646917</v>
       </c>
     </row>
     <row r="110">
@@ -23966,34 +23966,34 @@
         <v>0</v>
       </c>
       <c r="BX111" s="211" t="n">
-        <v>663.9327169755761</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="BY111" s="212" t="n">
         <v>753.6182474419381</v>
       </c>
       <c r="BZ111" s="212" t="n">
-        <v>854.169368624498</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CA111" s="212" t="n">
-        <v>950.5574286398316</v>
+        <v>950.5574286398318</v>
       </c>
       <c r="CB111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CC111" s="212" t="n">
-        <v>663.9327169755761</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CD111" s="212" t="n">
         <v>753.6182474419381</v>
       </c>
       <c r="CE111" s="212" t="n">
-        <v>854.169368624498</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CF111" s="212" t="n">
-        <v>950.5574286398316</v>
+        <v>950.5574286398318</v>
       </c>
       <c r="CG111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CI111" s="211" t="n">
         <v>0</v>
@@ -24023,19 +24023,19 @@
         <v>0</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>663.9327169755761</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CX111" s="212" t="n">
         <v>753.6182474419381</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>854.169368624498</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>950.5574286398316</v>
+        <v>950.5574286398318</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24267,10 +24267,10 @@
         <v>3431.876115653031</v>
       </c>
       <c r="BZ112" s="222" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218107</v>
       </c>
       <c r="CA112" s="222" t="n">
-        <v>4186.715162875307</v>
+        <v>4186.715162875308</v>
       </c>
       <c r="CB112" s="214" t="n">
         <v>4656.789813563189</v>
@@ -24282,10 +24282,10 @@
         <v>3431.876115653031</v>
       </c>
       <c r="CE112" s="222" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218107</v>
       </c>
       <c r="CF112" s="222" t="n">
-        <v>4186.715162875307</v>
+        <v>4186.715162875308</v>
       </c>
       <c r="CG112" s="214" t="n">
         <v>4656.789813563189</v>
@@ -24321,10 +24321,10 @@
         <v>3107.351651027931</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.87611565303</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218107</v>
       </c>
       <c r="CZ112" s="212" t="n">
         <v>4186.715162875308</v>
@@ -30296,7 +30296,7 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>1587676.55772197</v>
+        <v>1587964.100369063</v>
       </c>
       <c r="BT146" s="375" t="n">
         <v>1859004.22412202</v>
@@ -30308,10 +30308,10 @@
         <v>2465352.40680323</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>2848333.991969492</v>
+        <v>2848333.991969493</v>
       </c>
       <c r="BX146" s="386" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="BY146" s="372" t="n">
         <v>859.3947033664067</v>
@@ -30326,7 +30326,7 @@
         <v>989.1578434898606</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>1587676.55772197</v>
+        <v>1587964.100369063</v>
       </c>
       <c r="CX146" s="512" t="n">
         <v>1859004.22412202</v>
@@ -30338,7 +30338,7 @@
         <v>2465352.40680323</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>2848333.991969492</v>
+        <v>2848333.991969493</v>
       </c>
     </row>
     <row r="147">
@@ -30488,22 +30488,22 @@
         </is>
       </c>
       <c r="BS147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542587.0899172613</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>615908.7206401868</v>
+        <v>615908.7206401867</v>
       </c>
       <c r="BU147" s="375" t="n">
-        <v>709964.9410228858</v>
+        <v>709964.9410228857</v>
       </c>
       <c r="BV147" s="375" t="n">
-        <v>811268.0615034181</v>
+        <v>811268.0615034183</v>
       </c>
       <c r="BW147" s="392" t="n">
-        <v>938677.3753287457</v>
+        <v>938677.375328746</v>
       </c>
       <c r="BX147" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BY147" s="372" t="n">
         <v>1655.286013279789</v>
@@ -30518,19 +30518,19 @@
         <v>1911.879093778504</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542587.0899172613</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>615908.7206401868</v>
+        <v>615908.7206401867</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>709964.9410228858</v>
+        <v>709964.9410228857</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>811268.0615034181</v>
+        <v>811268.0615034183</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>938677.3753287457</v>
+        <v>938677.375328746</v>
       </c>
     </row>
     <row r="148">
@@ -30680,7 +30680,7 @@
         </is>
       </c>
       <c r="BS148" s="391" t="n">
-        <v>307001.1257340743</v>
+        <v>307032.5130789613</v>
       </c>
       <c r="BT148" s="375" t="n">
         <v>355493.4875790516</v>
@@ -30689,13 +30689,13 @@
         <v>411894.9442355951</v>
       </c>
       <c r="BV148" s="375" t="n">
-        <v>471930.3932149257</v>
+        <v>471930.3932149258</v>
       </c>
       <c r="BW148" s="392" t="n">
         <v>539734.7192076781</v>
       </c>
       <c r="BX148" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BY148" s="372" t="n">
         <v>2485.680463849397</v>
@@ -30710,7 +30710,7 @@
         <v>2797.787340780611</v>
       </c>
       <c r="CW148" s="391" t="n">
-        <v>307001.1257340743</v>
+        <v>307032.5130789613</v>
       </c>
       <c r="CX148" s="375" t="n">
         <v>355493.4875790516</v>
@@ -30719,7 +30719,7 @@
         <v>411894.9442355951</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>471930.3932149257</v>
+        <v>471930.3932149258</v>
       </c>
       <c r="DA148" s="392" t="n">
         <v>539734.7192076781</v>
@@ -30872,7 +30872,7 @@
         </is>
       </c>
       <c r="BS149" s="419" t="n">
-        <v>8313320.311779677</v>
+        <v>8313320.311779679</v>
       </c>
       <c r="BT149" s="420" t="n">
         <v>9656231.481041208</v>
@@ -30902,7 +30902,7 @@
         <v>13705.78892383383</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>8313320.311779677</v>
+        <v>8313320.311779679</v>
       </c>
       <c r="CX149" s="420" t="n">
         <v>9656231.481041208</v>
@@ -31064,7 +31064,7 @@
         </is>
       </c>
       <c r="BS150" s="439" t="n">
-        <v>10750514.29229461</v>
+        <v>10750904.01514496</v>
       </c>
       <c r="BT150" s="440" t="n">
         <v>12486637.91338247</v>
@@ -31079,7 +31079,7 @@
         <v>19311960.75363057</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>3459.703149058871</v>
+        <v>3459.82856867471</v>
       </c>
       <c r="BY150" s="443" t="n">
         <v>3638.429096094123</v>
@@ -31094,7 +31094,7 @@
         <v>4147.054414477392</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>10750514.29229462</v>
+        <v>10750904.01514496</v>
       </c>
       <c r="CX150" s="420" t="n">
         <v>12486637.91338247</v>
@@ -34180,16 +34180,16 @@
         <v>1120865.475386333</v>
       </c>
       <c r="AM172" s="179" t="n">
-        <v>1132051.225420706</v>
+        <v>1132051.225420705</v>
       </c>
       <c r="AN172" s="179" t="n">
-        <v>1140493.683591603</v>
+        <v>1140493.683591604</v>
       </c>
       <c r="AO172" s="195" t="n">
-        <v>1151005.129087175</v>
+        <v>1151005.129087176</v>
       </c>
       <c r="AP172" s="194" t="n">
-        <v>156698.958534845</v>
+        <v>156698.958534844</v>
       </c>
       <c r="AQ172" s="179" t="n">
         <v>164357.97599524</v>
@@ -34204,7 +34204,7 @@
         <v>196929.682247454</v>
       </c>
       <c r="AU172" s="190" t="n">
-        <v>1264286.590611399</v>
+        <v>1264286.590611398</v>
       </c>
       <c r="AV172" s="190" t="n">
         <v>1285223.451381573</v>
@@ -34213,10 +34213,10 @@
         <v>1304795.66503686</v>
       </c>
       <c r="AX172" s="190" t="n">
-        <v>1323790.43958049</v>
+        <v>1323790.439580491</v>
       </c>
       <c r="AY172" s="196" t="n">
-        <v>1347934.811334629</v>
+        <v>1347934.81133463</v>
       </c>
       <c r="BA172" s="83" t="inlineStr">
         <is>
@@ -34230,16 +34230,16 @@
         <v>1120865.475386333</v>
       </c>
       <c r="BD172" s="190" t="n">
-        <v>1132051.225420706</v>
+        <v>1132051.225420705</v>
       </c>
       <c r="BE172" s="190" t="n">
-        <v>1140493.683591603</v>
+        <v>1140493.683591604</v>
       </c>
       <c r="BF172" s="198" t="n">
-        <v>1151005.129087175</v>
+        <v>1151005.129087176</v>
       </c>
       <c r="BG172" s="197" t="n">
-        <v>156698.958534845</v>
+        <v>156698.958534844</v>
       </c>
       <c r="BH172" s="190" t="n">
         <v>164357.97599524</v>
@@ -34254,19 +34254,19 @@
         <v>196929.682247454</v>
       </c>
       <c r="BL172" s="199" t="n">
-        <v>1264286.590611399</v>
+        <v>1264286.590611398</v>
       </c>
       <c r="BM172" s="200" t="n">
         <v>1285223.451381573</v>
       </c>
       <c r="BN172" s="200" t="n">
-        <v>1304795.665036861</v>
+        <v>1304795.66503686</v>
       </c>
       <c r="BO172" s="200" t="n">
-        <v>1323790.43958049</v>
+        <v>1323790.439580491</v>
       </c>
       <c r="BP172" s="201" t="n">
-        <v>1347934.811334629</v>
+        <v>1347934.81133463</v>
       </c>
       <c r="BR172" s="83" t="inlineStr">
         <is>
@@ -34280,16 +34280,16 @@
         <v>1116572.829058719</v>
       </c>
       <c r="BU172" s="190" t="n">
-        <v>1126388.412234446</v>
+        <v>1126388.412234445</v>
       </c>
       <c r="BV172" s="190" t="n">
-        <v>1133424.642644243</v>
+        <v>1133424.642644244</v>
       </c>
       <c r="BW172" s="198" t="n">
-        <v>1142459.222383313</v>
+        <v>1142459.222383314</v>
       </c>
       <c r="BX172" s="197" t="n">
-        <v>157692.5140850912</v>
+        <v>157692.5140850902</v>
       </c>
       <c r="BY172" s="190" t="n">
         <v>166487.4670033722</v>
@@ -34304,7 +34304,7 @@
         <v>202596.0343779827</v>
       </c>
       <c r="CC172" s="199" t="n">
-        <v>1262321.715539614</v>
+        <v>1262321.715539613</v>
       </c>
       <c r="CD172" s="200" t="n">
         <v>1283060.296062091</v>
@@ -34313,10 +34313,10 @@
         <v>1302416.798949552</v>
       </c>
       <c r="CF172" s="200" t="n">
-        <v>1321175.291252316</v>
+        <v>1321175.291252317</v>
       </c>
       <c r="CG172" s="201" t="n">
-        <v>1345055.256761296</v>
+        <v>1345055.256761297</v>
       </c>
       <c r="CI172" s="199" t="n">
         <v>1070496</v>
@@ -34486,16 +34486,16 @@
         <v>283592.7910795131</v>
       </c>
       <c r="AV173" s="190" t="n">
-        <v>285965.6858407319</v>
+        <v>285965.685840732</v>
       </c>
       <c r="AW173" s="190" t="n">
         <v>288420.5176779922</v>
       </c>
       <c r="AX173" s="190" t="n">
-        <v>290894.5708527548</v>
+        <v>290894.5708527549</v>
       </c>
       <c r="AY173" s="196" t="n">
-        <v>294346.5865991133</v>
+        <v>294346.5865991132</v>
       </c>
       <c r="BA173" s="101" t="inlineStr">
         <is>
@@ -35296,16 +35296,16 @@
         <v>1435280.798812643</v>
       </c>
       <c r="AM176" s="207" t="n">
-        <v>1448679.168235342</v>
+        <v>1448679.168235341</v>
       </c>
       <c r="AN176" s="207" t="n">
-        <v>1458495.409587514</v>
+        <v>1458495.409587515</v>
       </c>
       <c r="AO176" s="208" t="n">
-        <v>1470806.51964571</v>
+        <v>1470806.519645711</v>
       </c>
       <c r="AP176" s="206" t="n">
-        <v>222373.319148925</v>
+        <v>222373.319148924</v>
       </c>
       <c r="AQ176" s="207" t="n">
         <v>233484.101656684</v>
@@ -35320,19 +35320,19 @@
         <v>284029.782855784</v>
       </c>
       <c r="AU176" s="207" t="n">
-        <v>1641593.698447801</v>
+        <v>1641593.6984478</v>
       </c>
       <c r="AV176" s="207" t="n">
-        <v>1668764.900469327</v>
+        <v>1668764.900469328</v>
       </c>
       <c r="AW176" s="207" t="n">
         <v>1695104.119977998</v>
       </c>
       <c r="AX176" s="207" t="n">
-        <v>1721390.552400115</v>
+        <v>1721390.552400116</v>
       </c>
       <c r="AY176" s="208" t="n">
-        <v>1754836.302501494</v>
+        <v>1754836.302501495</v>
       </c>
       <c r="BA176" s="155" t="inlineStr">
         <is>
@@ -35346,16 +35346,16 @@
         <v>1435280.798812643</v>
       </c>
       <c r="BD176" s="222" t="n">
-        <v>1448679.168235342</v>
+        <v>1448679.168235341</v>
       </c>
       <c r="BE176" s="222" t="n">
-        <v>1458495.409587514</v>
+        <v>1458495.409587515</v>
       </c>
       <c r="BF176" s="214" t="n">
-        <v>1470806.51964571</v>
+        <v>1470806.519645711</v>
       </c>
       <c r="BG176" s="221" t="n">
-        <v>222373.319148925</v>
+        <v>222373.319148924</v>
       </c>
       <c r="BH176" s="222" t="n">
         <v>233484.101656684</v>
@@ -35370,19 +35370,19 @@
         <v>284029.782855784</v>
       </c>
       <c r="BL176" s="222" t="n">
-        <v>1641593.698447801</v>
+        <v>1641593.6984478</v>
       </c>
       <c r="BM176" s="222" t="n">
         <v>1668764.900469327</v>
       </c>
       <c r="BN176" s="222" t="n">
-        <v>1695104.119977998</v>
+        <v>1695104.119977997</v>
       </c>
       <c r="BO176" s="222" t="n">
-        <v>1721390.552400115</v>
+        <v>1721390.552400116</v>
       </c>
       <c r="BP176" s="214" t="n">
-        <v>1754836.302501494</v>
+        <v>1754836.302501495</v>
       </c>
       <c r="BR176" s="155" t="inlineStr">
         <is>
@@ -35396,16 +35396,16 @@
         <v>1429707.124045076</v>
       </c>
       <c r="BU176" s="222" t="n">
-        <v>1441322.416354638</v>
+        <v>1441322.416354637</v>
       </c>
       <c r="BV176" s="222" t="n">
-        <v>1449303.184037697</v>
+        <v>1449303.184037698</v>
       </c>
       <c r="BW176" s="214" t="n">
-        <v>1459680.857487851</v>
+        <v>1459680.857487852</v>
       </c>
       <c r="BX176" s="221" t="n">
-        <v>223107.2967522648</v>
+        <v>223107.2967522637</v>
       </c>
       <c r="BY176" s="222" t="n">
         <v>235625.9003085986</v>
@@ -35420,19 +35420,19 @@
         <v>290498.6552000805</v>
       </c>
       <c r="CC176" s="222" t="n">
-        <v>1638486.346796773</v>
+        <v>1638486.346796772</v>
       </c>
       <c r="CD176" s="222" t="n">
         <v>1665333.024353675</v>
       </c>
       <c r="CE176" s="222" t="n">
-        <v>1691305.600586781</v>
+        <v>1691305.60058678</v>
       </c>
       <c r="CF176" s="222" t="n">
-        <v>1717203.837237239</v>
+        <v>1717203.83723724</v>
       </c>
       <c r="CG176" s="214" t="n">
-        <v>1750179.512687931</v>
+        <v>1750179.512687932</v>
       </c>
       <c r="CI176" s="349" t="n">
         <v>1375594</v>
@@ -38452,13 +38452,13 @@
         <v>1120865.475386333</v>
       </c>
       <c r="AM190" s="179" t="n">
-        <v>1132051.225420706</v>
+        <v>1132051.225420705</v>
       </c>
       <c r="AN190" s="179" t="n">
-        <v>1140493.683591603</v>
+        <v>1140493.683591604</v>
       </c>
       <c r="AO190" s="195" t="n">
-        <v>1151005.129087175</v>
+        <v>1151005.129087176</v>
       </c>
       <c r="AP190" s="194" t="n">
         <v>156698.9585348445</v>
@@ -38473,22 +38473,22 @@
         <v>183296.7559888872</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>196929.6822474543</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>1264286.590611399</v>
+        <v>1264286.590611398</v>
       </c>
       <c r="AV190" s="190" t="n">
-        <v>1285223.451381572</v>
+        <v>1285223.451381573</v>
       </c>
       <c r="AW190" s="190" t="n">
         <v>1304795.66503686</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>1323790.43958049</v>
+        <v>1323790.439580491</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>1347934.811334629</v>
+        <v>1347934.81133463</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38502,13 +38502,13 @@
         <v>1120865.475386333</v>
       </c>
       <c r="BD190" s="190" t="n">
-        <v>1132051.225420706</v>
+        <v>1132051.225420705</v>
       </c>
       <c r="BE190" s="190" t="n">
-        <v>1140493.683591603</v>
+        <v>1140493.683591604</v>
       </c>
       <c r="BF190" s="198" t="n">
-        <v>1151005.129087175</v>
+        <v>1151005.129087176</v>
       </c>
       <c r="BG190" s="197" t="n">
         <v>156698.9585348445</v>
@@ -38523,7 +38523,7 @@
         <v>183296.7559888872</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>196929.6822474543</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="BL190" s="199" t="n">
         <v>1264286.590611398</v>
@@ -38532,13 +38532,13 @@
         <v>1285223.451381573</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>1304795.665036861</v>
+        <v>1304795.66503686</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>1323790.43958049</v>
+        <v>1323790.439580491</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>1347934.811334629</v>
+        <v>1347934.81133463</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38552,19 +38552,19 @@
         <v>1116572.829058719</v>
       </c>
       <c r="BU190" s="190" t="n">
-        <v>1126388.412234446</v>
+        <v>1126388.412234445</v>
       </c>
       <c r="BV190" s="190" t="n">
-        <v>1133424.642644243</v>
+        <v>1133424.642644244</v>
       </c>
       <c r="BW190" s="198" t="n">
-        <v>1142459.222383313</v>
+        <v>1142459.222383314</v>
       </c>
       <c r="BX190" s="197" t="n">
         <v>157692.5140850907</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>166487.4670033717</v>
+        <v>166487.4670033718</v>
       </c>
       <c r="BZ190" s="190" t="n">
         <v>176028.3867151063</v>
@@ -38573,7 +38573,7 @@
         <v>187750.6486080732</v>
       </c>
       <c r="CB190" s="198" t="n">
-        <v>202596.034377983</v>
+        <v>202596.0343779832</v>
       </c>
       <c r="CC190" s="199" t="n">
         <v>1262321.715539614</v>
@@ -38582,13 +38582,13 @@
         <v>1283060.296062091</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>1302416.798949552</v>
+        <v>1302416.798949551</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>1321175.291252316</v>
+        <v>1321175.291252317</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>1345055.256761296</v>
+        <v>1345055.256761297</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>1070496</v>
@@ -38618,7 +38618,7 @@
         <v>29501926</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178444</v>
       </c>
       <c r="CX190" s="92" t="n">
         <v>2163.155319482305</v>
@@ -38630,22 +38630,22 @@
         <v>2615.148328173791</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>2879.554573332821</v>
+        <v>2879.554573332822</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.00984816114217338</v>
+        <v>0.009848161142173384</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.01024095992487895</v>
+        <v>0.01024095992487894</v>
       </c>
       <c r="DE190" s="394" t="n">
         <v>0.01065955492972585</v>
       </c>
       <c r="DF190" s="394" t="n">
-        <v>0.01099740955274481</v>
+        <v>0.01099740955274482</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.01119286179102341</v>
+        <v>0.0111928617910234</v>
       </c>
     </row>
     <row r="191">
@@ -38770,16 +38770,16 @@
         <v>256322.276880836</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>31830.69819750123</v>
+        <v>31830.69819750122</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.67515711239</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>33517.01056342493</v>
+        <v>33517.01056342497</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>35440.16241287874</v>
+        <v>35440.16241287873</v>
       </c>
       <c r="AT191" s="195" t="n">
         <v>38024.30971827688</v>
@@ -38788,16 +38788,16 @@
         <v>283592.7910795134</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>285965.6858407323</v>
+        <v>285965.6858407324</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>288420.5176779921</v>
+        <v>288420.5176779922</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>290894.5708527545</v>
+        <v>290894.5708527546</v>
       </c>
       <c r="AY191" s="196" t="n">
-        <v>294346.5865991132</v>
+        <v>294346.5865991131</v>
       </c>
       <c r="BA191" s="101" t="inlineStr">
         <is>
@@ -38820,16 +38820,16 @@
         <v>256322.276880836</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>31830.69819750123</v>
+        <v>31830.69819750122</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.67515711239</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>33517.01056342493</v>
+        <v>33517.01056342497</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>35440.16241287874</v>
+        <v>35440.16241287873</v>
       </c>
       <c r="BK191" s="198" t="n">
         <v>38024.30971827688</v>
@@ -38841,10 +38841,10 @@
         <v>285965.6858407324</v>
       </c>
       <c r="BN191" s="190" t="n">
-        <v>288420.5176779919</v>
+        <v>288420.517677992</v>
       </c>
       <c r="BO191" s="190" t="n">
-        <v>290894.5708527548</v>
+        <v>290894.5708527547</v>
       </c>
       <c r="BP191" s="198" t="n">
         <v>294346.5865991129</v>
@@ -38870,16 +38870,16 @@
         <v>254456.119521798</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>32146.42968012415</v>
+        <v>32146.42968012413</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>32965.71456648616</v>
+        <v>32965.71456648615</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>34361.04780651599</v>
+        <v>34361.04780651603</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>36546.78659560295</v>
+        <v>36546.78659560294</v>
       </c>
       <c r="CB191" s="198" t="n">
         <v>39399.49598066849</v>
@@ -38927,28 +38927,28 @@
         <v>24983100</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>347.8756485031443</v>
+        <v>347.8756485031444</v>
       </c>
       <c r="CX191" s="103" t="n">
         <v>372.0859813342885</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314257</v>
       </c>
       <c r="CZ191" s="103" t="n">
         <v>446.7528256294977</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>490.9710966467709</v>
+        <v>490.971096646771</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.009375041997798525</v>
+        <v>0.00937504199779853</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.009757353086475152</v>
+        <v>0.009757353086475155</v>
       </c>
       <c r="DE191" s="397" t="n">
-        <v>0.0102684082927527</v>
+        <v>0.01026840829275268</v>
       </c>
       <c r="DF191" s="397" t="n">
         <v>0.01058323089476837</v>
@@ -39079,7 +39079,7 @@
         <v>58895.089087613</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>11685.54726389713</v>
+        <v>11685.54726389712</v>
       </c>
       <c r="AQ192" s="179" t="n">
         <v>12314.14721798622</v>
@@ -39088,25 +39088,25 @@
         <v>13131.37395224123</v>
       </c>
       <c r="AS192" s="179" t="n">
-        <v>14239.36090163693</v>
+        <v>14239.36090163694</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>15645.96943166314</v>
+        <v>15645.96943166313</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>68520.79892571832</v>
+        <v>68520.79892571831</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>69762.95644698222</v>
+        <v>69762.95644698221</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>71104.91150434423</v>
+        <v>71104.91150434421</v>
       </c>
       <c r="AX192" s="190" t="n">
-        <v>72595.72034546072</v>
+        <v>72595.72034546074</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>74541.05851927646</v>
+        <v>74541.05851927644</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>58895.089087613</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>11685.54726389713</v>
+        <v>11685.54726389712</v>
       </c>
       <c r="BH192" s="190" t="n">
         <v>12314.14721798622</v>
@@ -39138,10 +39138,10 @@
         <v>13131.37395224123</v>
       </c>
       <c r="BJ192" s="190" t="n">
-        <v>14239.36090163693</v>
+        <v>14239.36090163694</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>15645.96943166314</v>
+        <v>15645.96943166313</v>
       </c>
       <c r="BL192" s="197" t="n">
         <v>68520.79892571812</v>
@@ -39188,10 +39188,10 @@
         <v>13282.19313651668</v>
       </c>
       <c r="CA192" s="190" t="n">
-        <v>14452.7654678493</v>
+        <v>14452.76546784931</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>15925.64489480941</v>
+        <v>15925.6448948094</v>
       </c>
       <c r="CC192" s="197" t="n">
         <v>68390.13071195339</v>
@@ -39263,7 +39263,7 @@
         <v>0.01164983319324695</v>
       </c>
       <c r="DG192" s="398" t="n">
-        <v>0.01169494806471412</v>
+        <v>0.01169494806471413</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" thickBot="1">
@@ -39388,28 +39388,28 @@
         <v>4584.024590086</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>22158.11515268234</v>
+        <v>22158.11515268233</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>24429.30328634562</v>
+        <v>24429.30328634563</v>
       </c>
       <c r="AR193" s="207" t="n">
-        <v>27032.12761083536</v>
+        <v>27032.12761083537</v>
       </c>
       <c r="AS193" s="207" t="n">
         <v>29918.86350919777</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>33429.82145839032</v>
+        <v>33429.82145839031</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>25193.51783117101</v>
+        <v>25193.517831171</v>
       </c>
       <c r="AV193" s="209" t="n">
         <v>27812.80680003976</v>
       </c>
       <c r="AW193" s="209" t="n">
-        <v>30783.02575880154</v>
+        <v>30783.02575880155</v>
       </c>
       <c r="AX193" s="209" t="n">
         <v>34109.82162140912</v>
@@ -39438,34 +39438,34 @@
         <v>4584.024590086</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>22158.11515268234</v>
+        <v>22158.11515268233</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>24429.30328634562</v>
+        <v>24429.30328634563</v>
       </c>
       <c r="BI193" s="212" t="n">
-        <v>27032.12761083536</v>
+        <v>27032.12761083537</v>
       </c>
       <c r="BJ193" s="212" t="n">
         <v>29918.86350919777</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>33429.82145839032</v>
+        <v>33429.82145839031</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>25193.51783117134</v>
+        <v>25193.51783117133</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>27812.80680003962</v>
+        <v>27812.80680003963</v>
       </c>
       <c r="BN193" s="212" t="n">
-        <v>30783.02575880136</v>
+        <v>30783.02575880137</v>
       </c>
       <c r="BO193" s="212" t="n">
         <v>34109.82162140877</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>38013.84604847632</v>
+        <v>38013.84604847631</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,25 +39488,25 @@
         <v>4343.016806139</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>21553.1352674317</v>
+        <v>21553.13526743169</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>23768.57981361582</v>
+        <v>23768.57981361583</v>
       </c>
       <c r="BZ193" s="212" t="n">
-        <v>26311.55657400406</v>
+        <v>26311.55657400407</v>
       </c>
       <c r="CA193" s="212" t="n">
         <v>29150.45252801627</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>32577.4799466203</v>
+        <v>32577.47994662029</v>
       </c>
       <c r="CC193" s="212" t="n">
         <v>24529.5851141957</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>27059.18855259782</v>
+        <v>27059.18855259783</v>
       </c>
       <c r="CE193" s="212" t="n">
         <v>29928.85639017706</v>
@@ -39515,7 +39515,7 @@
         <v>33159.26419276927</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>36920.4967527593</v>
+        <v>36920.49675275929</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>2510</v>
@@ -39545,34 +39545,34 @@
         <v>837210</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>663.9327169755791</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>753.6182474419337</v>
+        <v>753.6182474419338</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>854.1693686245005</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>950.5574286398272</v>
+        <v>950.5574286398273</v>
       </c>
       <c r="DA193" s="134" t="n">
         <v>1093.349295717359</v>
       </c>
       <c r="DC193" s="422" t="n">
-        <v>0.02947412316721834</v>
+        <v>0.02947412316721836</v>
       </c>
       <c r="DD193" s="423" t="n">
         <v>0.03031253335869557</v>
       </c>
       <c r="DE193" s="423" t="n">
-        <v>0.03101698224902302</v>
+        <v>0.031016982249023</v>
       </c>
       <c r="DF193" s="423" t="n">
-        <v>0.0311467331421413</v>
+        <v>0.03114673314214131</v>
       </c>
       <c r="DG193" s="424" t="n">
-        <v>0.0320281822505418</v>
+        <v>0.03202818225054181</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" thickBot="1">
@@ -39688,28 +39688,28 @@
         <v>1435280.798812643</v>
       </c>
       <c r="AM194" s="209" t="n">
-        <v>1448679.168235342</v>
+        <v>1448679.168235341</v>
       </c>
       <c r="AN194" s="209" t="n">
-        <v>1458495.409587514</v>
+        <v>1458495.409587515</v>
       </c>
       <c r="AO194" s="210" t="n">
-        <v>1470806.51964571</v>
+        <v>1470806.519645711</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>222373.3191489252</v>
+        <v>222373.3191489251</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>233484.1016566838</v>
+        <v>233484.1016566839</v>
       </c>
       <c r="AR194" s="207" t="n">
         <v>246424.9517426564</v>
       </c>
       <c r="AS194" s="207" t="n">
-        <v>262895.1428126007</v>
+        <v>262895.1428126006</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>284029.7828557846</v>
+        <v>284029.7828557848</v>
       </c>
       <c r="AU194" s="207" t="n">
         <v>1641593.698447801</v>
@@ -39721,7 +39721,7 @@
         <v>1695104.119977998</v>
       </c>
       <c r="AX194" s="207" t="n">
-        <v>1721390.552400115</v>
+        <v>1721390.552400116</v>
       </c>
       <c r="AY194" s="208" t="n">
         <v>1754836.302501495</v>
@@ -39738,28 +39738,28 @@
         <v>1435280.798812643</v>
       </c>
       <c r="BD194" s="222" t="n">
-        <v>1448679.168235342</v>
+        <v>1448679.168235341</v>
       </c>
       <c r="BE194" s="222" t="n">
-        <v>1458495.409587514</v>
+        <v>1458495.409587515</v>
       </c>
       <c r="BF194" s="214" t="n">
-        <v>1470806.51964571</v>
+        <v>1470806.519645711</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>222373.3191489252</v>
+        <v>222373.3191489251</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>233484.1016566838</v>
+        <v>233484.1016566839</v>
       </c>
       <c r="BI194" s="222" t="n">
         <v>246424.9517426564</v>
       </c>
       <c r="BJ194" s="222" t="n">
-        <v>262895.1428126007</v>
+        <v>262895.1428126006</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>284029.7828557846</v>
+        <v>284029.7828557848</v>
       </c>
       <c r="BL194" s="222" t="n">
         <v>1641593.698447801</v>
@@ -39771,10 +39771,10 @@
         <v>1695104.119977998</v>
       </c>
       <c r="BO194" s="222" t="n">
-        <v>1721390.552400115</v>
+        <v>1721390.552400116</v>
       </c>
       <c r="BP194" s="214" t="n">
-        <v>1754836.302501495</v>
+        <v>1754836.302501496</v>
       </c>
       <c r="BR194" s="155" t="inlineStr">
         <is>
@@ -39788,16 +39788,16 @@
         <v>1429707.124045076</v>
       </c>
       <c r="BU194" s="222" t="n">
-        <v>1441322.416354638</v>
+        <v>1441322.416354637</v>
       </c>
       <c r="BV194" s="222" t="n">
-        <v>1449303.184037697</v>
+        <v>1449303.184037698</v>
       </c>
       <c r="BW194" s="214" t="n">
-        <v>1459680.857487851</v>
+        <v>1459680.857487852</v>
       </c>
       <c r="BX194" s="221" t="n">
-        <v>223107.296752265</v>
+        <v>223107.2967522649</v>
       </c>
       <c r="BY194" s="222" t="n">
         <v>235625.9003085985</v>
@@ -39806,10 +39806,10 @@
         <v>249983.184232143</v>
       </c>
       <c r="CA194" s="222" t="n">
-        <v>267900.6531995418</v>
+        <v>267900.6531995417</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>290498.6552000812</v>
+        <v>290498.6552000814</v>
       </c>
       <c r="CC194" s="222" t="n">
         <v>1638486.346796773</v>
@@ -39818,13 +39818,13 @@
         <v>1665333.024353674</v>
       </c>
       <c r="CE194" s="222" t="n">
-        <v>1691305.600586781</v>
+        <v>1691305.60058678</v>
       </c>
       <c r="CF194" s="222" t="n">
-        <v>1717203.837237239</v>
+        <v>1717203.83723724</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>1750179.512687932</v>
+        <v>1750179.512687933</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>1375594</v>
@@ -39854,10 +39854,10 @@
         <v>60466650</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028078</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652925</v>
       </c>
       <c r="CY194" s="133" t="n">
         <v>3798.519391217832</v>
@@ -39866,7 +39866,7 @@
         <v>4186.715162875506</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>4656.789813562892</v>
+        <v>4656.789813562893</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40645,16 +40645,16 @@
         <v>0.9999999999999977</v>
       </c>
       <c r="CK198" s="397" t="n">
-        <v>1.000000000000004</v>
+        <v>1.000000000000005</v>
       </c>
       <c r="CL198" s="397" t="n">
-        <v>0.9999999999999969</v>
+        <v>0.9999999999999961</v>
       </c>
       <c r="CM198" s="398" t="n">
-        <v>0.9999999999999983</v>
+        <v>0.9999999999999976</v>
       </c>
       <c r="CN198" s="396" t="n">
-        <v>1.000000000000986</v>
+        <v>1.000000000000992</v>
       </c>
       <c r="CO198" s="397" t="n">
         <v>0.9999999999985529</v>
@@ -40663,7 +40663,7 @@
         <v>0.9999999999991155</v>
       </c>
       <c r="CQ198" s="397" t="n">
-        <v>1.000000000000606</v>
+        <v>1.000000000000605</v>
       </c>
       <c r="CR198" s="398" t="n">
         <v>0.9999999999977436</v>
@@ -40676,16 +40676,16 @@
         <v>0.9999999999999977</v>
       </c>
       <c r="CV198" s="397" t="n">
-        <v>1.000000000000004</v>
+        <v>1.000000000000005</v>
       </c>
       <c r="CW198" s="397" t="n">
-        <v>0.9999999999999969</v>
+        <v>0.9999999999999961</v>
       </c>
       <c r="CX198" s="398" t="n">
-        <v>0.9999999999999983</v>
+        <v>0.9999999999999976</v>
       </c>
       <c r="CY198" s="396" t="n">
-        <v>1.012460167074764</v>
+        <v>1.012460167074771</v>
       </c>
       <c r="CZ198" s="397" t="n">
         <v>1.012992901857277</v>
@@ -40822,25 +40822,25 @@
         <v>0.00634</v>
       </c>
       <c r="AP199" s="233" t="n">
-        <v>2958.430622030673</v>
+        <v>2958.430622030672</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>4292.646327614451</v>
+        <v>4292.646327614454</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>5662.813186259974</v>
+        <v>5662.813186259973</v>
       </c>
       <c r="AS199" s="190" t="n">
-        <v>7069.040947359818</v>
+        <v>7069.040947359824</v>
       </c>
       <c r="AT199" s="196" t="n">
-        <v>8545.906703861547</v>
+        <v>8545.906703861554</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>159657.3891568752</v>
+        <v>159657.3891568751</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>168650.622322854</v>
+        <v>168650.6223228541</v>
       </c>
       <c r="AW199" s="190" t="n">
         <v>178407.2528024148</v>
@@ -40849,7 +40849,7 @@
         <v>190365.796936247</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>205475.5889513158</v>
+        <v>205475.588951316</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40878,19 +40878,19 @@
         <v>4292.646327614452</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>5662.813186259977</v>
+        <v>5662.813186259972</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>7069.040947359818</v>
+        <v>7069.040947359824</v>
       </c>
       <c r="BK199" s="198" t="n">
-        <v>8545.90670386155</v>
+        <v>8545.906703861558</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>159657.3891568752</v>
+        <v>159657.3891568751</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>168650.622322854</v>
+        <v>168650.6223228541</v>
       </c>
       <c r="BN199" s="200" t="n">
         <v>178407.2528024148</v>
@@ -40899,7 +40899,7 @@
         <v>190365.796936247</v>
       </c>
       <c r="BP199" s="201" t="n">
-        <v>205475.5889513158</v>
+        <v>205475.588951316</v>
       </c>
       <c r="BR199" s="83" t="inlineStr">
         <is>
@@ -40922,19 +40922,19 @@
         <v>147097.8447281431</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.6466114449749492</v>
+        <v>0.6466114449749494</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.6803881747816336</v>
+        <v>0.6803881747816334</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.7041227667519323</v>
+        <v>0.7041227667519324</v>
       </c>
       <c r="CA199" s="463" t="n">
-        <v>0.7216460584379012</v>
+        <v>0.7216460584379011</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.7433596047944406</v>
+        <v>0.7433596047944401</v>
       </c>
       <c r="CC199" s="199" t="n">
         <v>101965.784394293</v>
@@ -40946,7 +40946,7 @@
         <v>123945.5946807197</v>
       </c>
       <c r="CF199" s="200" t="n">
-        <v>135489.5155371755</v>
+        <v>135489.5155371754</v>
       </c>
       <c r="CG199" s="201" t="n">
         <v>150601.7080481384</v>
@@ -40992,7 +40992,7 @@
         <v>1.000000000000017</v>
       </c>
       <c r="CW199" s="397" t="n">
-        <v>0.9999999999999969</v>
+        <v>0.9999999999999961</v>
       </c>
       <c r="CX199" s="398" t="n">
         <v>1.000000000000021</v>
@@ -41138,7 +41138,7 @@
         <v>663.6071311260613</v>
       </c>
       <c r="AQ200" s="190" t="n">
-        <v>955.1253907080459</v>
+        <v>955.1253907080461</v>
       </c>
       <c r="AR200" s="190" t="n">
         <v>1251.745046722486</v>
@@ -41147,19 +41147,19 @@
         <v>1553.377008353709</v>
       </c>
       <c r="AT200" s="196" t="n">
-        <v>1866.157359038378</v>
+        <v>1866.157359038377</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>32494.30532862729</v>
+        <v>32494.30532862728</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782044</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>34768.75561014742</v>
+        <v>34768.75561014745</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>36993.53942123245</v>
+        <v>36993.53942123244</v>
       </c>
       <c r="AY200" s="196" t="n">
         <v>39890.46707731526</v>
@@ -41200,16 +41200,16 @@
         <v>1866.157359038376</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>32494.30532862729</v>
+        <v>32494.30532862728</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782044</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>34768.75561014742</v>
+        <v>34768.75561014745</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>36993.53942123245</v>
+        <v>36993.53942123244</v>
       </c>
       <c r="BP200" s="198" t="n">
         <v>39890.46707731526</v>
@@ -41229,37 +41229,37 @@
         <v>22795.83730997828</v>
       </c>
       <c r="BV200" s="336" t="n">
-        <v>24689.40128114245</v>
+        <v>24689.40128114244</v>
       </c>
       <c r="BW200" s="337" t="n">
         <v>27292.71916327555</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.6167000484508492</v>
+        <v>0.6167000484508496</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>0.6509786380063288</v>
+        <v>0.650978638006329</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.6763319833413184</v>
+        <v>0.6763319833413177</v>
       </c>
       <c r="CA200" s="463" t="n">
         <v>0.6929421555046223</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.714253308146516</v>
+        <v>0.7142533081465159</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>19824.70474125438</v>
       </c>
       <c r="CD200" s="190" t="n">
-        <v>21459.97596939655</v>
+        <v>21459.97596939656</v>
       </c>
       <c r="CE200" s="190" t="n">
         <v>23239.47561266682</v>
       </c>
       <c r="CF200" s="190" t="n">
-        <v>25324.80908032455</v>
+        <v>25324.80908032454</v>
       </c>
       <c r="CG200" s="198" t="n">
         <v>28141.22034349783</v>
@@ -41448,7 +41448,7 @@
         <v>0.00634</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>160.3386694861809</v>
+        <v>160.3386694861808</v>
       </c>
       <c r="AQ201" s="190" t="n">
         <v>233.0082745329206</v>
@@ -41460,10 +41460,10 @@
         <v>387.6611466447603</v>
       </c>
       <c r="AT201" s="196" t="n">
-        <v>472.5903110122127</v>
+        <v>472.5903110122126</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>11845.88593338331</v>
+        <v>11845.8859333833</v>
       </c>
       <c r="AV201" s="190" t="n">
         <v>12547.15549251914</v>
@@ -41472,7 +41472,7 @@
         <v>13439.96926817009</v>
       </c>
       <c r="AX201" s="190" t="n">
-        <v>14627.02204828169</v>
+        <v>14627.0220482817</v>
       </c>
       <c r="AY201" s="196" t="n">
         <v>16118.55974267535</v>
@@ -41513,7 +41513,7 @@
         <v>472.5903110122107</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>11845.88593338331</v>
+        <v>11845.8859333833</v>
       </c>
       <c r="BM201" s="190" t="n">
         <v>12547.15549251914</v>
@@ -41522,10 +41522,10 @@
         <v>13439.96926817009</v>
       </c>
       <c r="BO201" s="190" t="n">
-        <v>14627.02204828169</v>
+        <v>14627.0220482817</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>16118.55974267535</v>
+        <v>16118.55974267534</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>8517.104467793557</v>
       </c>
       <c r="BU201" s="336" t="n">
-        <v>9425.600245674357</v>
+        <v>9425.600245674355</v>
       </c>
       <c r="BV201" s="336" t="n">
         <v>10560.09983204437</v>
@@ -41548,19 +41548,19 @@
         <v>12045.55205274821</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.6559448055656172</v>
+        <v>0.6559448055656174</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.6880968190885128</v>
+        <v>0.6880968190885129</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.7144401067455748</v>
+        <v>0.7144401067455746</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.7384979676447369</v>
+        <v>0.7384979676447362</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.7670945895259744</v>
+        <v>0.7670945895259746</v>
       </c>
       <c r="CC201" s="197" t="n">
         <v>7684.536209253959</v>
@@ -41569,10 +41569,10 @@
         <v>8535.24853791034</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>9489.331482268315</v>
+        <v>9489.331482268313</v>
       </c>
       <c r="CF201" s="190" t="n">
-        <v>10673.33792485275</v>
+        <v>10673.33792485274</v>
       </c>
       <c r="CG201" s="198" t="n">
         <v>12216.47603352025</v>
@@ -41760,7 +41760,7 @@
         <v>0.00634</v>
       </c>
       <c r="AP202" s="220" t="n">
-        <v>58.95283172494016</v>
+        <v>58.95283172494014</v>
       </c>
       <c r="AQ202" s="209" t="n">
         <v>92.8947747121328</v>
@@ -41775,19 +41775,19 @@
         <v>241.0077839473381</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>22217.06798440728</v>
+        <v>22217.06798440727</v>
       </c>
       <c r="AV202" s="209" t="n">
         <v>24522.19806105776</v>
       </c>
       <c r="AW202" s="209" t="n">
-        <v>27165.72594262856</v>
+        <v>27165.72594262857</v>
       </c>
       <c r="AX202" s="209" t="n">
         <v>30101.0099566561</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>33670.82924233766</v>
+        <v>33670.82924233765</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41810,34 +41810,34 @@
         <v>0.00634</v>
       </c>
       <c r="BG202" s="211" t="n">
-        <v>58.95283172494094</v>
+        <v>58.95283172494091</v>
       </c>
       <c r="BH202" s="212" t="n">
-        <v>92.89477471213235</v>
+        <v>92.89477471213237</v>
       </c>
       <c r="BI202" s="212" t="n">
-        <v>133.5983317931979</v>
+        <v>133.598331793198</v>
       </c>
       <c r="BJ202" s="212" t="n">
         <v>182.1464474583229</v>
       </c>
       <c r="BK202" s="213" t="n">
-        <v>241.0077839473399</v>
+        <v>241.0077839473398</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>22217.06798440728</v>
+        <v>22217.06798440727</v>
       </c>
       <c r="BM202" s="212" t="n">
         <v>24522.19806105776</v>
       </c>
       <c r="BN202" s="212" t="n">
-        <v>27165.72594262856</v>
+        <v>27165.72594262857</v>
       </c>
       <c r="BO202" s="212" t="n">
         <v>30101.00995665609</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>33670.82924233766</v>
+        <v>33670.82924233765</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         </is>
       </c>
       <c r="BS202" s="271" t="n">
-        <v>15709.70744138703</v>
+        <v>15709.70744138704</v>
       </c>
       <c r="BT202" s="272" t="n">
         <v>17732.88691759677</v>
@@ -41854,25 +41854,25 @@
         <v>19920.31722773356</v>
       </c>
       <c r="BV202" s="272" t="n">
-        <v>22371.86578071989</v>
+        <v>22371.86578071988</v>
       </c>
       <c r="BW202" s="273" t="n">
         <v>25652.86382685493</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.70001747034859</v>
+        <v>0.7000174703485904</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.717194708788405</v>
+        <v>0.7171947087884047</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.7283718889102294</v>
+        <v>0.7283718889102293</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.7395256918955591</v>
+        <v>0.7395256918955589</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>0.7595570753068652</v>
+        <v>0.7595570753068654</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>15087.57122798852</v>
@@ -41931,7 +41931,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="K203" s="215" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="L203" s="216" t="n">
         <v>11125.79579552732</v>
@@ -41981,7 +41981,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="AB203" s="218" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="AC203" s="219" t="n">
         <v>11125.79579552732</v>
@@ -42022,19 +42022,19 @@
         <v>0.02536</v>
       </c>
       <c r="AP203" s="206" t="n">
-        <v>3841.329254367855</v>
+        <v>3841.329254367854</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>5573.674767567551</v>
+        <v>5573.674767567553</v>
       </c>
       <c r="AR203" s="207" t="n">
-        <v>7356.751880704513</v>
+        <v>7356.751880704512</v>
       </c>
       <c r="AS203" s="207" t="n">
-        <v>9192.225549816612</v>
+        <v>9192.225549816618</v>
       </c>
       <c r="AT203" s="208" t="n">
-        <v>11125.66215785947</v>
+        <v>11125.66215785948</v>
       </c>
       <c r="AU203" s="207" t="n">
         <v>226214.648403293</v>
@@ -42046,10 +42046,10 @@
         <v>253781.7036233609</v>
       </c>
       <c r="AX203" s="207" t="n">
-        <v>272087.3683624173</v>
+        <v>272087.3683624172</v>
       </c>
       <c r="AY203" s="208" t="n">
-        <v>295155.4450136441</v>
+        <v>295155.4450136442</v>
       </c>
       <c r="BA203" s="155" t="inlineStr">
         <is>
@@ -42078,10 +42078,10 @@
         <v>5573.674767567551</v>
       </c>
       <c r="BI203" s="222" t="n">
-        <v>7356.751880704513</v>
+        <v>7356.751880704509</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>9192.225549816612</v>
+        <v>9192.225549816618</v>
       </c>
       <c r="BK203" s="214" t="n">
         <v>11125.66215785948</v>
@@ -42093,13 +42093,13 @@
         <v>239057.7764242514</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>253781.7036233608</v>
+        <v>253781.7036233609</v>
       </c>
       <c r="BO203" s="222" t="n">
-        <v>272087.3683624173</v>
+        <v>272087.3683624172</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>295155.4450136441</v>
+        <v>295155.4450136442</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42116,16 +42116,16 @@
         <v>174456.5589318115</v>
       </c>
       <c r="BV203" s="272" t="n">
-        <v>190597.6540256326</v>
+        <v>190597.6540256325</v>
       </c>
       <c r="BW203" s="273" t="n">
         <v>212088.9797710218</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.6479510023973357</v>
+        <v>0.6479510023973358</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.6803922139863258</v>
+        <v>0.6803922139863257</v>
       </c>
       <c r="BZ203" s="467" t="n">
         <v>0.7034033128177949</v>
@@ -42134,7 +42134,7 @@
         <v>0.7205849213567084</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.7425296329365558</v>
+        <v>0.7425296329365555</v>
       </c>
       <c r="CC203" s="212" t="n">
         <v>144562.5965727899</v>
@@ -42928,40 +42928,40 @@
         <v>1116572.829058718</v>
       </c>
       <c r="AM208" s="190" t="n">
-        <v>1126388.412234446</v>
+        <v>1126388.412234445</v>
       </c>
       <c r="AN208" s="190" t="n">
-        <v>1133424.642644243</v>
+        <v>1133424.642644244</v>
       </c>
       <c r="AO208" s="196" t="n">
-        <v>1142459.222383313</v>
+        <v>1142459.222383314</v>
       </c>
       <c r="AP208" s="473" t="n">
-        <v>0.8760574068423315</v>
+        <v>0.8760574068423314</v>
       </c>
       <c r="AQ208" s="463" t="n">
-        <v>0.8721171981272515</v>
+        <v>0.8721171981272516</v>
       </c>
       <c r="AR208" s="463" t="n">
-        <v>0.8676080521686322</v>
+        <v>0.8676080521686321</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.8615364256241539</v>
+        <v>0.861536425624154</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0.8539026660699797</v>
+        <v>0.8539026660699796</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.8737174068423312</v>
+        <v>0.8737174068423316</v>
       </c>
       <c r="AV208" s="463" t="n">
-        <v>0.8687771981272516</v>
+        <v>0.8687771981272512</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.8632680521686326</v>
+        <v>0.863268052168632</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.8561964256241539</v>
+        <v>0.856196425624154</v>
       </c>
       <c r="AY208" s="474" t="n">
         <v>0.8475626660699799</v>
@@ -42978,13 +42978,13 @@
         <v>1116572.829058719</v>
       </c>
       <c r="BD208" s="190" t="n">
-        <v>1126388.412234446</v>
+        <v>1126388.412234445</v>
       </c>
       <c r="BE208" s="190" t="n">
-        <v>1133424.642644243</v>
+        <v>1133424.642644244</v>
       </c>
       <c r="BF208" s="198" t="n">
-        <v>1142459.222383313</v>
+        <v>1142459.222383314</v>
       </c>
       <c r="BG208" s="462" t="n">
         <v>0.8760574068423315</v>
@@ -42993,10 +42993,10 @@
         <v>0.8721171981272515</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.8676080521686322</v>
+        <v>0.8676080521686321</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.8615364256241539</v>
+        <v>0.861536425624154</v>
       </c>
       <c r="BK208" s="464" t="n">
         <v>0.8539026660699797</v>
@@ -43011,10 +43011,10 @@
         <v>0.8632680521686322</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.8561964256241538</v>
+        <v>0.8561964256241539</v>
       </c>
       <c r="BP208" s="477" t="n">
-        <v>0.8475626660699794</v>
+        <v>0.8475626660699793</v>
       </c>
       <c r="BR208" s="83" t="inlineStr">
         <is>
@@ -43046,10 +43046,10 @@
         <v>0.8648448124616638</v>
       </c>
       <c r="CA208" s="463" t="n">
-        <v>0.8578911898737464</v>
+        <v>0.8578911898737466</v>
       </c>
       <c r="CB208" s="464" t="n">
-        <v>0.8493771662096575</v>
+        <v>0.8493771662096576</v>
       </c>
       <c r="CC208" s="478" t="n">
         <v>0</v>
@@ -43195,10 +43195,10 @@
         <v>0.8877591419854653</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.8867602766328131</v>
+        <v>0.8867602766328132</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.8837911711924562</v>
+        <v>0.8837911711924561</v>
       </c>
       <c r="AS209" s="463" t="n">
         <v>0.8781683607604425</v>
@@ -43210,16 +43210,16 @@
         <v>0.8854191419854648</v>
       </c>
       <c r="AV209" s="463" t="n">
-        <v>0.8834202766328134</v>
+        <v>0.8834202766328133</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.8794511711924556</v>
+        <v>0.8794511711924552</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.872828360760443</v>
+        <v>0.8728283607604429</v>
       </c>
       <c r="AY209" s="474" t="n">
-        <v>0.8644779015846221</v>
+        <v>0.8644779015846223</v>
       </c>
       <c r="BA209" s="101" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>0.8867602766328131</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.8837911711924562</v>
+        <v>0.883791171192456</v>
       </c>
       <c r="BJ209" s="463" t="n">
-        <v>0.8781683607604424</v>
+        <v>0.8781683607604425</v>
       </c>
       <c r="BK209" s="464" t="n">
         <v>0.870817901584623</v>
@@ -43263,10 +43263,10 @@
         <v>0.8834202766328132</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.8794511711924579</v>
+        <v>0.8794511711924576</v>
       </c>
       <c r="BO209" s="463" t="n">
-        <v>0.8728283607604413</v>
+        <v>0.8728283607604415</v>
       </c>
       <c r="BP209" s="464" t="n">
         <v>0.8644779015846242</v>
@@ -43298,7 +43298,7 @@
         <v>0.8845712418530539</v>
       </c>
       <c r="BZ209" s="463" t="n">
-        <v>0.8806961127128158</v>
+        <v>0.8806961127128157</v>
       </c>
       <c r="CA209" s="463" t="n">
         <v>0.8741709032491688</v>
@@ -43447,34 +43447,34 @@
         <v>58422.49877660078</v>
       </c>
       <c r="AP210" s="473" t="n">
-        <v>0.8294598509196436</v>
+        <v>0.8294598509196437</v>
       </c>
       <c r="AQ210" s="463" t="n">
         <v>0.8234858749522089</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.8153239533750216</v>
+        <v>0.8153239533750217</v>
       </c>
       <c r="AS210" s="463" t="n">
-        <v>0.8038539898236949</v>
+        <v>0.8038539898236948</v>
       </c>
       <c r="AT210" s="474" t="n">
         <v>0.7901026663363379</v>
       </c>
       <c r="AU210" s="463" t="n">
-        <v>0.8271198509196407</v>
+        <v>0.8271198509196409</v>
       </c>
       <c r="AV210" s="463" t="n">
-        <v>0.8201458749522089</v>
+        <v>0.820145874952209</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.8109839533750217</v>
+        <v>0.8109839533750219</v>
       </c>
       <c r="AX210" s="463" t="n">
-        <v>0.7985139898236979</v>
+        <v>0.7985139898236978</v>
       </c>
       <c r="AY210" s="474" t="n">
-        <v>0.7837626663363335</v>
+        <v>0.7837626663363336</v>
       </c>
       <c r="BA210" s="111" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>0.1205882873372004</v>
       </c>
       <c r="AU211" s="490" t="n">
-        <v>0.1181434790770429</v>
+        <v>0.118143479077043</v>
       </c>
       <c r="AV211" s="490" t="n">
         <v>0.1183127169666732</v>
@@ -43729,7 +43729,7 @@
         <v>0.1175266088825435</v>
       </c>
       <c r="AY211" s="491" t="n">
-        <v>0.1142482873372075</v>
+        <v>0.1142482873372076</v>
       </c>
       <c r="BA211" s="111" t="inlineStr">
         <is>
@@ -43752,13 +43752,13 @@
         <v>4343.016806139</v>
       </c>
       <c r="BG211" s="466" t="n">
-        <v>0.1204834790770413</v>
+        <v>0.1204834790770414</v>
       </c>
       <c r="BH211" s="467" t="n">
-        <v>0.1216527169666738</v>
+        <v>0.1216527169666737</v>
       </c>
       <c r="BI211" s="467" t="n">
-        <v>0.121849560123035</v>
+        <v>0.1218495601230349</v>
       </c>
       <c r="BJ211" s="467" t="n">
         <v>0.1228666088825447</v>
@@ -43808,13 +43808,13 @@
         <v>0.1216078129093078</v>
       </c>
       <c r="BZ211" s="467" t="n">
-        <v>0.1208632822121541</v>
+        <v>0.120863282212154</v>
       </c>
       <c r="CA211" s="467" t="n">
         <v>0.1208956761358765</v>
       </c>
       <c r="CB211" s="468" t="n">
-        <v>0.1176315918830214</v>
+        <v>0.1176315918830215</v>
       </c>
       <c r="CC211" s="492" t="n">
         <v>0</v>
@@ -43875,7 +43875,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="N212" s="495" t="n">
-        <v>0.856739395836739</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="O212" s="495" t="n">
         <v>0.850278097729836</v>
@@ -43925,7 +43925,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="AE212" s="498" t="n">
-        <v>0.856739395836739</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="AF212" s="498" t="n">
         <v>0.850278097729836</v>
@@ -43948,43 +43948,43 @@
         <v>1429707.124045075</v>
       </c>
       <c r="AM212" s="207" t="n">
-        <v>1441322.416354638</v>
+        <v>1441322.416354637</v>
       </c>
       <c r="AN212" s="207" t="n">
         <v>1449303.184037698</v>
       </c>
       <c r="AO212" s="208" t="n">
-        <v>1459680.85748785</v>
+        <v>1459680.857487851</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.8645381501164453</v>
+        <v>0.8645381501164456</v>
       </c>
       <c r="AQ212" s="501" t="n">
-        <v>0.8600856827759151</v>
+        <v>0.8600856827759148</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.8546254776692687</v>
+        <v>0.8546254776692682</v>
       </c>
       <c r="AS212" s="501" t="n">
-        <v>0.847277456910607</v>
+        <v>0.8472774569106071</v>
       </c>
       <c r="AT212" s="502" t="n">
         <v>0.8381445708349525</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.8621981501164453</v>
+        <v>0.8621981501164456</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.8567456827759151</v>
+        <v>0.8567456827759148</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.8502854776692687</v>
+        <v>0.8502854776692682</v>
       </c>
       <c r="AX212" s="501" t="n">
-        <v>0.841937456910607</v>
+        <v>0.8419374569106071</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.8318045708349524</v>
+        <v>0.8318045708349525</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -43998,13 +43998,13 @@
         <v>1429707.124045076</v>
       </c>
       <c r="BD212" s="222" t="n">
-        <v>1441322.416354638</v>
+        <v>1441322.416354637</v>
       </c>
       <c r="BE212" s="222" t="n">
-        <v>1449303.184037697</v>
+        <v>1449303.184037698</v>
       </c>
       <c r="BF212" s="214" t="n">
-        <v>1459680.857487851</v>
+        <v>1459680.857487852</v>
       </c>
       <c r="BG212" s="503" t="n">
         <v>0.8645381501164454</v>
@@ -44013,13 +44013,13 @@
         <v>0.860085682775915</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.8546254776692687</v>
+        <v>0.8546254776692684</v>
       </c>
       <c r="BJ212" s="504" t="n">
-        <v>0.8472774569106069</v>
+        <v>0.8472774569106071</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.8381445708349525</v>
+        <v>0.8381445708349523</v>
       </c>
       <c r="BL212" s="504" t="n">
         <v>0.8621981501164453</v>
@@ -44028,13 +44028,13 @@
         <v>0.8567456827759153</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.850285477669269</v>
+        <v>0.8502854776692688</v>
       </c>
       <c r="BO212" s="504" t="n">
-        <v>0.8419374569106066</v>
+        <v>0.8419374569106067</v>
       </c>
       <c r="BP212" s="505" t="n">
-        <v>0.8318045708349527</v>
+        <v>0.8318045708349526</v>
       </c>
       <c r="BR212" s="155" t="inlineStr">
         <is>
@@ -44060,16 +44060,16 @@
         <v>0.8638332890668037</v>
       </c>
       <c r="BY212" s="504" t="n">
-        <v>0.858511242578615</v>
+        <v>0.8585112425786148</v>
       </c>
       <c r="BZ212" s="504" t="n">
-        <v>0.8521951419392133</v>
+        <v>0.8521951419392132</v>
       </c>
       <c r="CA212" s="504" t="n">
-        <v>0.8439901848632252</v>
+        <v>0.8439901848632253</v>
       </c>
       <c r="CB212" s="505" t="n">
-        <v>0.8340177946924243</v>
+        <v>0.8340177946924242</v>
       </c>
       <c r="CC212" s="492" t="n">
         <v>0</v>
@@ -44737,28 +44737,28 @@
         <v>159778964.190028</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>166038998.9901031</v>
+        <v>166038998.9901032</v>
       </c>
       <c r="AN219" s="368" t="n">
         <v>173883609.5679228</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>181212790.6116944</v>
+        <v>181212790.6116943</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="AQ219" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="AR219" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="AS219" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44772,28 +44772,28 @@
         <v>159778964.190028</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>166038998.9901031</v>
+        <v>166038998.9901032</v>
       </c>
       <c r="BE219" s="375" t="n">
         <v>173883609.5679228</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>181212790.6116944</v>
+        <v>181212790.6116943</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="BH219" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="BI219" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="BJ219" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44807,46 +44807,46 @@
         <v>159167049.0236483</v>
       </c>
       <c r="BU219" s="375" t="n">
-        <v>165208428.9489239</v>
+        <v>165208428.948924</v>
       </c>
       <c r="BV219" s="375" t="n">
-        <v>172805839.1481521</v>
+        <v>172805839.148152</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>179867333.8774206</v>
+        <v>179867333.8774205</v>
       </c>
       <c r="BX219" s="386" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="BY219" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="BZ219" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="CA219" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="CI219" s="199" t="n">
-        <v>140012326.4220065</v>
+        <v>140012326.4220066</v>
       </c>
       <c r="CJ219" s="201" t="n">
-        <v>101860600.7648326</v>
+        <v>101860600.7648325</v>
       </c>
       <c r="CK219" s="344" t="n">
-        <v>241872927.1868391</v>
+        <v>241872927.1868392</v>
       </c>
       <c r="CL219" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950559</v>
       </c>
       <c r="CM219" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064114</v>
       </c>
       <c r="CN219" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018314</v>
       </c>
     </row>
     <row r="220">
@@ -44926,25 +44926,25 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557573</v>
       </c>
       <c r="AL220" s="368" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="AM220" s="368" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="AO220" s="380" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="AP220" s="381" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="AQ220" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="AR220" s="372" t="n">
         <v>415.6208472109543</v>
@@ -44953,7 +44953,7 @@
         <v>427.1601692832</v>
       </c>
       <c r="AT220" s="382" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="BA220" s="101" t="inlineStr">
         <is>
@@ -44961,25 +44961,25 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557573</v>
       </c>
       <c r="BC220" s="375" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="BD220" s="375" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="BF220" s="392" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="BG220" s="386" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="BH220" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="BI220" s="372" t="n">
         <v>415.6208472109543</v>
@@ -44988,7 +44988,7 @@
         <v>427.1601692832</v>
       </c>
       <c r="BK220" s="387" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="BR220" s="101" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         </is>
       </c>
       <c r="BS220" s="391" t="n">
-        <v>99358676.85064536</v>
+        <v>99358676.8506453</v>
       </c>
       <c r="BT220" s="375" t="n">
         <v>102480003.1332628</v>
@@ -45011,10 +45011,10 @@
         <v>111338199.0650378</v>
       </c>
       <c r="BX220" s="386" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="BY220" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="BZ220" s="372" t="n">
         <v>415.6208472109543</v>
@@ -45023,10 +45023,10 @@
         <v>427.1601692832</v>
       </c>
       <c r="CB220" s="387" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="CI220" s="197" t="n">
-        <v>92468586.6202051</v>
+        <v>92468586.62020506</v>
       </c>
       <c r="CJ220" s="198" t="n">
         <v>50146632.66768061</v>
@@ -45035,13 +45035,13 @@
         <v>142615219.2878857</v>
       </c>
       <c r="CL220" s="386" t="n">
-        <v>373.770530490655</v>
+        <v>373.7705304906548</v>
       </c>
       <c r="CM220" s="387" t="n">
         <v>1595.654458512763</v>
       </c>
       <c r="CN220" s="508" t="n">
-        <v>511.4938232338516</v>
+        <v>511.4938232338513</v>
       </c>
     </row>
     <row r="221">
@@ -45121,31 +45121,31 @@
         </is>
       </c>
       <c r="AK221" s="506" t="n">
-        <v>24428704.35144111</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="AL221" s="368" t="n">
-        <v>25266859.46546122</v>
+        <v>25266859.46546123</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914955</v>
       </c>
       <c r="AN221" s="368" t="n">
-        <v>26915839.6432833</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="AO221" s="380" t="n">
         <v>27898487.10720396</v>
       </c>
       <c r="AP221" s="381" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="AQ221" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="AR221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="AS221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="AT221" s="382" t="n">
         <v>473.6980203171415</v>
@@ -45156,31 +45156,31 @@
         </is>
       </c>
       <c r="BB221" s="391" t="n">
-        <v>24428704.35144111</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="BC221" s="375" t="n">
-        <v>25266859.46546122</v>
+        <v>25266859.46546123</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914955</v>
       </c>
       <c r="BE221" s="375" t="n">
-        <v>26915839.6432833</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="BF221" s="392" t="n">
         <v>27898487.10720396</v>
       </c>
       <c r="BG221" s="386" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BH221" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="BI221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="BJ221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="BK221" s="387" t="n">
         <v>473.6980203171415</v>
@@ -45191,52 +45191,52 @@
         </is>
       </c>
       <c r="BS221" s="391" t="n">
-        <v>24359788.21509174</v>
+        <v>24359788.21509175</v>
       </c>
       <c r="BT221" s="375" t="n">
-        <v>25164378.88482034</v>
+        <v>25164378.88482035</v>
       </c>
       <c r="BU221" s="375" t="n">
         <v>25930189.28176446</v>
       </c>
       <c r="BV221" s="375" t="n">
-        <v>26737037.78932131</v>
+        <v>26737037.7893213</v>
       </c>
       <c r="BW221" s="392" t="n">
-        <v>27674622.01245651</v>
+        <v>27674622.01245652</v>
       </c>
       <c r="BX221" s="386" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BY221" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="BZ221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="CA221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="CB221" s="387" t="n">
         <v>473.6980203171415</v>
       </c>
       <c r="CI221" s="197" t="n">
-        <v>22520192.04029756</v>
+        <v>22520192.04029757</v>
       </c>
       <c r="CJ221" s="198" t="n">
-        <v>23188084.77820082</v>
+        <v>23188084.77820083</v>
       </c>
       <c r="CK221" s="346" t="n">
-        <v>45708276.81849838</v>
+        <v>45708276.8184984</v>
       </c>
       <c r="CL221" s="386" t="n">
-        <v>408.0188433579295</v>
+        <v>408.0188433579297</v>
       </c>
       <c r="CM221" s="387" t="n">
-        <v>2158.838541867686</v>
+        <v>2158.838541867688</v>
       </c>
       <c r="CN221" s="508" t="n">
-        <v>693.2323776218758</v>
+        <v>693.2323776218761</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1" thickBot="1">
@@ -45316,10 +45316,10 @@
         </is>
       </c>
       <c r="AK222" s="435" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="AL222" s="408" t="n">
-        <v>28456663.68210901</v>
+        <v>28456663.682109</v>
       </c>
       <c r="AM222" s="408" t="n">
         <v>33847051.4542876</v>
@@ -45328,19 +45328,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="AO222" s="409" t="n">
-        <v>46075816.37371121</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="AP222" s="410" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="AQ222" s="411" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="AR222" s="411" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="AS222" s="411" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="AT222" s="412" t="n">
         <v>10051.38944353848</v>
@@ -45351,10 +45351,10 @@
         </is>
       </c>
       <c r="BB222" s="419" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="BC222" s="420" t="n">
-        <v>28456663.68210901</v>
+        <v>28456663.682109</v>
       </c>
       <c r="BD222" s="420" t="n">
         <v>33847051.4542876</v>
@@ -45363,19 +45363,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="BF222" s="421" t="n">
-        <v>46075816.37371121</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="BG222" s="416" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="BH222" s="417" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="BI222" s="417" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="BJ222" s="417" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="BK222" s="418" t="n">
         <v>10051.38944353848</v>
@@ -45389,43 +45389,43 @@
         <v>23896135.38091505</v>
       </c>
       <c r="BT222" s="420" t="n">
-        <v>27675380.21333004</v>
+        <v>27675380.21333003</v>
       </c>
       <c r="BU222" s="420" t="n">
-        <v>32641497.62903731</v>
+        <v>32641497.6290373</v>
       </c>
       <c r="BV222" s="420" t="n">
-        <v>38590944.95395144</v>
+        <v>38590944.95395145</v>
       </c>
       <c r="BW222" s="421" t="n">
-        <v>43653353.27833574</v>
+        <v>43653353.27833575</v>
       </c>
       <c r="BX222" s="416" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="BY222" s="417" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="BZ222" s="417" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="CA222" s="417" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="CB222" s="418" t="n">
         <v>10051.38944353848</v>
       </c>
       <c r="CI222" s="211" t="n">
-        <v>17230897.74462213</v>
+        <v>17230897.74462212</v>
       </c>
       <c r="CJ222" s="213" t="n">
-        <v>211983483.7044854</v>
+        <v>211983483.7044855</v>
       </c>
       <c r="CK222" s="214" t="n">
         <v>229214381.4491076</v>
       </c>
       <c r="CL222" s="416" t="n">
-        <v>6864.899499849453</v>
+        <v>6864.899499849451</v>
       </c>
       <c r="CM222" s="418" t="n">
         <v>11988.65986339133</v>
@@ -45511,7 +45511,7 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>301977441.5881622</v>
+        <v>301977441.5881621</v>
       </c>
       <c r="AL223" s="408" t="n">
         <v>316369942.7622774</v>
@@ -45523,22 +45523,22 @@
         <v>350263780.7229214</v>
       </c>
       <c r="AO223" s="409" t="n">
-        <v>367341837.0863913</v>
+        <v>367341837.0863912</v>
       </c>
       <c r="AP223" s="436" t="n">
-        <v>212.7769907992339</v>
+        <v>212.7769907992338</v>
       </c>
       <c r="AQ223" s="437" t="n">
-        <v>220.4237268581863</v>
+        <v>220.4237268581862</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>229.1040173800734</v>
+        <v>229.1040173800736</v>
       </c>
       <c r="AS223" s="437" t="n">
-        <v>240.154187953174</v>
+        <v>240.1541879531738</v>
       </c>
       <c r="AT223" s="438" t="n">
-        <v>249.7553771891609</v>
+        <v>249.7553771891607</v>
       </c>
       <c r="BA223" s="155" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>301977441.5881622</v>
+        <v>301977441.5881621</v>
       </c>
       <c r="BC223" s="440" t="n">
         <v>316369942.7622774</v>
@@ -45558,22 +45558,22 @@
         <v>350263780.7229214</v>
       </c>
       <c r="BF223" s="441" t="n">
-        <v>367341837.0863913</v>
+        <v>367341837.0863912</v>
       </c>
       <c r="BG223" s="442" t="n">
-        <v>212.7769907992339</v>
+        <v>212.7769907992338</v>
       </c>
       <c r="BH223" s="443" t="n">
-        <v>220.4237268581863</v>
+        <v>220.4237268581862</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>229.1040173800734</v>
+        <v>229.1040173800736</v>
       </c>
       <c r="BJ223" s="443" t="n">
-        <v>240.154187953174</v>
+        <v>240.1541879531738</v>
       </c>
       <c r="BK223" s="444" t="n">
-        <v>249.7553771891609</v>
+        <v>249.7553771891607</v>
       </c>
       <c r="BR223" s="155" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         </is>
       </c>
       <c r="BS223" s="439" t="n">
-        <v>300762479.3059122</v>
+        <v>300762479.3059121</v>
       </c>
       <c r="BT223" s="440" t="n">
         <v>314486811.2550614</v>
@@ -45593,22 +45593,22 @@
         <v>346590229.4588928</v>
       </c>
       <c r="BW223" s="441" t="n">
-        <v>362533508.2332507</v>
+        <v>362533508.2332506</v>
       </c>
       <c r="BX223" s="442" t="n">
-        <v>212.4960654861003</v>
+        <v>212.4960654861002</v>
       </c>
       <c r="BY223" s="443" t="n">
-        <v>219.9658978863327</v>
+        <v>219.9658978863326</v>
       </c>
       <c r="BZ223" s="443" t="n">
-        <v>228.4034941602645</v>
+        <v>228.4034941602646</v>
       </c>
       <c r="CA223" s="443" t="n">
-        <v>239.1426675081933</v>
+        <v>239.1426675081931</v>
       </c>
       <c r="CB223" s="444" t="n">
-        <v>248.3649123529512</v>
+        <v>248.364912352951</v>
       </c>
       <c r="CI223" s="349" t="n">
         <v>272232002.8271313</v>
@@ -45620,7 +45620,7 @@
         <v>659410804.7423308</v>
       </c>
       <c r="CL223" s="509" t="n">
-        <v>197.9014177345432</v>
+        <v>197.9014177345433</v>
       </c>
       <c r="CM223" s="510" t="n">
         <v>1925.419726265115</v>
@@ -47635,28 +47635,28 @@
         <v>159778964.190028</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>166038998.9901031</v>
+        <v>166038998.9901032</v>
       </c>
       <c r="AN237" s="368" t="n">
         <v>173883609.5679228</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>181212790.6116944</v>
+        <v>181212790.6116943</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="AQ237" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="AR237" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="AS237" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47670,28 +47670,28 @@
         <v>159778964.190028</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>166038998.9901031</v>
+        <v>166038998.9901032</v>
       </c>
       <c r="BE237" s="375" t="n">
         <v>173883609.5679228</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>181212790.6116944</v>
+        <v>181212790.6116943</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="BH237" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="BI237" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="BJ237" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47705,46 +47705,46 @@
         <v>159167049.0236483</v>
       </c>
       <c r="BU237" s="375" t="n">
-        <v>165208428.9489239</v>
+        <v>165208428.948924</v>
       </c>
       <c r="BV237" s="375" t="n">
-        <v>172805839.1481521</v>
+        <v>172805839.148152</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>179867333.8774206</v>
+        <v>179867333.8774205</v>
       </c>
       <c r="BX237" s="386" t="n">
         <v>138.641888751087</v>
       </c>
       <c r="BY237" s="372" t="n">
-        <v>142.5496348122922</v>
+        <v>142.5496348122921</v>
       </c>
       <c r="BZ237" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723743</v>
       </c>
       <c r="CA237" s="372" t="n">
-        <v>152.4634568955565</v>
+        <v>152.4634568955563</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>157.4387342265003</v>
+        <v>157.4387342265001</v>
       </c>
       <c r="CI237" s="199" t="n">
-        <v>140012326.4220065</v>
+        <v>140012326.4220066</v>
       </c>
       <c r="CJ237" s="201" t="n">
-        <v>101860600.7648326</v>
+        <v>101860600.7648325</v>
       </c>
       <c r="CK237" s="344" t="n">
-        <v>241872927.1868391</v>
+        <v>241872927.1868392</v>
       </c>
       <c r="CL237" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950559</v>
       </c>
       <c r="CM237" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064114</v>
       </c>
       <c r="CN237" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018314</v>
       </c>
     </row>
     <row r="238">
@@ -47824,25 +47824,25 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557573</v>
       </c>
       <c r="AL238" s="368" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="AM238" s="368" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="AO238" s="380" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="AP238" s="381" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="AQ238" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="AR238" s="372" t="n">
         <v>415.6208472109543</v>
@@ -47851,7 +47851,7 @@
         <v>427.1601692832</v>
       </c>
       <c r="AT238" s="382" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="BA238" s="101" t="inlineStr">
         <is>
@@ -47859,25 +47859,25 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>99621263.56557579</v>
+        <v>99621263.56557573</v>
       </c>
       <c r="BC238" s="375" t="n">
         <v>102867455.4246792</v>
       </c>
       <c r="BD238" s="375" t="n">
-        <v>105943211.5839999</v>
+        <v>105943211.5839998</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>109119948.3533172</v>
+        <v>109119948.3533171</v>
       </c>
       <c r="BF238" s="392" t="n">
         <v>112154742.9937817</v>
       </c>
       <c r="BG238" s="386" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="BH238" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="BI238" s="372" t="n">
         <v>415.6208472109543</v>
@@ -47886,7 +47886,7 @@
         <v>427.1601692832</v>
       </c>
       <c r="BK238" s="387" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="BR238" s="101" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         </is>
       </c>
       <c r="BS238" s="391" t="n">
-        <v>99358676.85064536</v>
+        <v>99358676.8506453</v>
       </c>
       <c r="BT238" s="375" t="n">
         <v>102480003.1332628</v>
@@ -47909,10 +47909,10 @@
         <v>111338199.0650378</v>
       </c>
       <c r="BX238" s="386" t="n">
-        <v>395.6960415492859</v>
+        <v>395.6960415492857</v>
       </c>
       <c r="BY238" s="372" t="n">
-        <v>405.6559433826607</v>
+        <v>405.6559433826606</v>
       </c>
       <c r="BZ238" s="372" t="n">
         <v>415.6208472109543</v>
@@ -47921,10 +47921,10 @@
         <v>427.1601692832</v>
       </c>
       <c r="CB238" s="387" t="n">
-        <v>437.5536311497513</v>
+        <v>437.5536311497511</v>
       </c>
       <c r="CI238" s="197" t="n">
-        <v>92468586.6202051</v>
+        <v>92468586.62020506</v>
       </c>
       <c r="CJ238" s="198" t="n">
         <v>50146632.66768061</v>
@@ -47933,13 +47933,13 @@
         <v>142615219.2878857</v>
       </c>
       <c r="CL238" s="386" t="n">
-        <v>373.770530490655</v>
+        <v>373.7705304906548</v>
       </c>
       <c r="CM238" s="387" t="n">
         <v>1595.654458512763</v>
       </c>
       <c r="CN238" s="508" t="n">
-        <v>511.4938232338516</v>
+        <v>511.4938232338513</v>
       </c>
     </row>
     <row r="239">
@@ -48019,31 +48019,31 @@
         </is>
       </c>
       <c r="AK239" s="506" t="n">
-        <v>24428704.35144111</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="AL239" s="368" t="n">
-        <v>25266859.46546122</v>
+        <v>25266859.46546123</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914955</v>
       </c>
       <c r="AN239" s="368" t="n">
-        <v>26915839.6432833</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="AO239" s="380" t="n">
         <v>27898487.10720396</v>
       </c>
       <c r="AP239" s="381" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="AQ239" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="AR239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="AS239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="AT239" s="382" t="n">
         <v>473.6980203171415</v>
@@ -48054,31 +48054,31 @@
         </is>
       </c>
       <c r="BB239" s="391" t="n">
-        <v>24428704.35144111</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="BC239" s="375" t="n">
-        <v>25266859.46546122</v>
+        <v>25266859.46546123</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914955</v>
       </c>
       <c r="BE239" s="375" t="n">
-        <v>26915839.6432833</v>
+        <v>26915839.64328329</v>
       </c>
       <c r="BF239" s="392" t="n">
         <v>27898487.10720396</v>
       </c>
       <c r="BG239" s="386" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BH239" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="BI239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="BJ239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="BK239" s="387" t="n">
         <v>473.6980203171415</v>
@@ -48089,52 +48089,52 @@
         </is>
       </c>
       <c r="BS239" s="391" t="n">
-        <v>24359788.21509174</v>
+        <v>24359788.21509175</v>
       </c>
       <c r="BT239" s="375" t="n">
-        <v>25164378.88482034</v>
+        <v>25164378.88482035</v>
       </c>
       <c r="BU239" s="375" t="n">
         <v>25930189.28176446</v>
       </c>
       <c r="BV239" s="375" t="n">
-        <v>26737037.78932131</v>
+        <v>26737037.7893213</v>
       </c>
       <c r="BW239" s="392" t="n">
-        <v>27674622.01245651</v>
+        <v>27674622.01245652</v>
       </c>
       <c r="BX239" s="386" t="n">
-        <v>429.8160672674748</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BY239" s="372" t="n">
-        <v>439.8151990365075</v>
+        <v>439.8151990365076</v>
       </c>
       <c r="BZ239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011409</v>
       </c>
       <c r="CA239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146549</v>
       </c>
       <c r="CB239" s="387" t="n">
         <v>473.6980203171415</v>
       </c>
       <c r="CI239" s="197" t="n">
-        <v>22520192.04029756</v>
+        <v>22520192.04029757</v>
       </c>
       <c r="CJ239" s="198" t="n">
-        <v>23188084.77820082</v>
+        <v>23188084.77820083</v>
       </c>
       <c r="CK239" s="346" t="n">
-        <v>45708276.81849838</v>
+        <v>45708276.8184984</v>
       </c>
       <c r="CL239" s="386" t="n">
-        <v>408.0188433579295</v>
+        <v>408.0188433579297</v>
       </c>
       <c r="CM239" s="387" t="n">
-        <v>2158.838541867686</v>
+        <v>2158.838541867688</v>
       </c>
       <c r="CN239" s="508" t="n">
-        <v>693.2323776218758</v>
+        <v>693.2323776218761</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" thickBot="1">
@@ -48214,10 +48214,10 @@
         </is>
       </c>
       <c r="AK240" s="435" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="AL240" s="408" t="n">
-        <v>28456663.68210901</v>
+        <v>28456663.682109</v>
       </c>
       <c r="AM240" s="408" t="n">
         <v>33847051.4542876</v>
@@ -48226,19 +48226,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="AO240" s="409" t="n">
-        <v>46075816.37371121</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="AP240" s="410" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="AQ240" s="411" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="AR240" s="411" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="AS240" s="411" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="AT240" s="412" t="n">
         <v>10051.38944353848</v>
@@ -48249,10 +48249,10 @@
         </is>
       </c>
       <c r="BB240" s="419" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="BC240" s="420" t="n">
-        <v>28456663.68210901</v>
+        <v>28456663.682109</v>
       </c>
       <c r="BD240" s="420" t="n">
         <v>33847051.4542876</v>
@@ -48261,19 +48261,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="BF240" s="421" t="n">
-        <v>46075816.37371121</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="BG240" s="416" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="BH240" s="417" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="BI240" s="417" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="BJ240" s="417" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="BK240" s="418" t="n">
         <v>10051.38944353848</v>
@@ -48287,43 +48287,43 @@
         <v>23896135.38091505</v>
       </c>
       <c r="BT240" s="420" t="n">
-        <v>27675380.21333004</v>
+        <v>27675380.21333003</v>
       </c>
       <c r="BU240" s="420" t="n">
-        <v>32641497.62903731</v>
+        <v>32641497.6290373</v>
       </c>
       <c r="BV240" s="420" t="n">
-        <v>38590944.95395144</v>
+        <v>38590944.95395145</v>
       </c>
       <c r="BW240" s="421" t="n">
-        <v>43653353.27833574</v>
+        <v>43653353.27833575</v>
       </c>
       <c r="BX240" s="416" t="n">
         <v>8028.401824709043</v>
       </c>
       <c r="BY240" s="417" t="n">
-        <v>8410.413515735037</v>
+        <v>8410.413515735036</v>
       </c>
       <c r="BZ240" s="417" t="n">
-        <v>9023.719151809506</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="CA240" s="417" t="n">
-        <v>9626.529800154427</v>
+        <v>9626.529800154429</v>
       </c>
       <c r="CB240" s="418" t="n">
         <v>10051.38944353848</v>
       </c>
       <c r="CI240" s="211" t="n">
-        <v>17230897.74462213</v>
+        <v>17230897.74462212</v>
       </c>
       <c r="CJ240" s="213" t="n">
-        <v>211983483.7044854</v>
+        <v>211983483.7044855</v>
       </c>
       <c r="CK240" s="214" t="n">
         <v>229214381.4491076</v>
       </c>
       <c r="CL240" s="416" t="n">
-        <v>6864.899499849453</v>
+        <v>6864.899499849451</v>
       </c>
       <c r="CM240" s="418" t="n">
         <v>11988.65986339133</v>
@@ -48409,7 +48409,7 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>301977441.5881622</v>
+        <v>301977441.5881621</v>
       </c>
       <c r="AL241" s="408" t="n">
         <v>316369942.7622774</v>
@@ -48421,22 +48421,22 @@
         <v>350263780.7229214</v>
       </c>
       <c r="AO241" s="409" t="n">
-        <v>367341837.0863913</v>
+        <v>367341837.0863912</v>
       </c>
       <c r="AP241" s="436" t="n">
-        <v>212.7769907992339</v>
+        <v>212.7769907992338</v>
       </c>
       <c r="AQ241" s="437" t="n">
-        <v>220.4237268581863</v>
+        <v>220.4237268581862</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>229.1040173800734</v>
+        <v>229.1040173800736</v>
       </c>
       <c r="AS241" s="437" t="n">
-        <v>240.154187953174</v>
+        <v>240.1541879531738</v>
       </c>
       <c r="AT241" s="438" t="n">
-        <v>249.7553771891609</v>
+        <v>249.7553771891607</v>
       </c>
       <c r="BA241" s="155" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>301977441.5881622</v>
+        <v>301977441.5881621</v>
       </c>
       <c r="BC241" s="440" t="n">
         <v>316369942.7622774</v>
@@ -48456,22 +48456,22 @@
         <v>350263780.7229214</v>
       </c>
       <c r="BF241" s="441" t="n">
-        <v>367341837.0863913</v>
+        <v>367341837.0863912</v>
       </c>
       <c r="BG241" s="442" t="n">
-        <v>212.7769907992339</v>
+        <v>212.7769907992338</v>
       </c>
       <c r="BH241" s="443" t="n">
-        <v>220.4237268581863</v>
+        <v>220.4237268581862</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>229.1040173800734</v>
+        <v>229.1040173800736</v>
       </c>
       <c r="BJ241" s="443" t="n">
-        <v>240.154187953174</v>
+        <v>240.1541879531738</v>
       </c>
       <c r="BK241" s="444" t="n">
-        <v>249.7553771891609</v>
+        <v>249.7553771891607</v>
       </c>
       <c r="BR241" s="155" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         </is>
       </c>
       <c r="BS241" s="439" t="n">
-        <v>300762479.3059122</v>
+        <v>300762479.3059121</v>
       </c>
       <c r="BT241" s="440" t="n">
         <v>314486811.2550614</v>
@@ -48491,22 +48491,22 @@
         <v>346590229.4588928</v>
       </c>
       <c r="BW241" s="441" t="n">
-        <v>362533508.2332507</v>
+        <v>362533508.2332506</v>
       </c>
       <c r="BX241" s="442" t="n">
-        <v>212.4960654861003</v>
+        <v>212.4960654861002</v>
       </c>
       <c r="BY241" s="443" t="n">
-        <v>219.9658978863327</v>
+        <v>219.9658978863326</v>
       </c>
       <c r="BZ241" s="443" t="n">
-        <v>228.4034941602645</v>
+        <v>228.4034941602646</v>
       </c>
       <c r="CA241" s="443" t="n">
-        <v>239.1426675081933</v>
+        <v>239.1426675081931</v>
       </c>
       <c r="CB241" s="444" t="n">
-        <v>248.3649123529512</v>
+        <v>248.364912352951</v>
       </c>
       <c r="CI241" s="349" t="n">
         <v>272232002.8271313</v>
@@ -48518,7 +48518,7 @@
         <v>659410804.7423308</v>
       </c>
       <c r="CL241" s="509" t="n">
-        <v>197.9014177345432</v>
+        <v>197.9014177345433</v>
       </c>
       <c r="CM241" s="510" t="n">
         <v>1925.419726265115</v>
@@ -48966,7 +48966,7 @@
         </is>
       </c>
       <c r="C246" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D246" s="368" t="n">
         <v>141265555.356126</v>
@@ -48981,7 +48981,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H246" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I246" s="372" t="n">
         <v>859.4354544219096</v>
@@ -49001,7 +49001,7 @@
         </is>
       </c>
       <c r="T246" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U246" s="375" t="n">
         <v>141265555.356126</v>
@@ -49016,7 +49016,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y246" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z246" s="372" t="n">
         <v>859.4354544219096</v>
@@ -49036,13 +49036,13 @@
         </is>
       </c>
       <c r="AK246" s="506" t="n">
-        <v>126617344.1039845</v>
+        <v>126640275.6551964</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261257</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>156336436.1669483</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="AN246" s="368" t="n">
         <v>172797502.0263112</v>
@@ -49051,13 +49051,13 @@
         <v>194794539.8105857</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>808.029263805405</v>
+        <v>808.1756052452408</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>859.3947033651494</v>
+        <v>859.3947033651497</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>905.0157360453051</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="AS246" s="372" t="n">
         <v>942.7199139126482</v>
@@ -49071,13 +49071,13 @@
         </is>
       </c>
       <c r="BB246" s="391" t="n">
-        <v>126617344.1039845</v>
+        <v>126640275.6551964</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261257</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>156336436.1669483</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="BE246" s="375" t="n">
         <v>172797502.0263112</v>
@@ -49086,13 +49086,13 @@
         <v>194794539.8105857</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>808.029263805405</v>
+        <v>808.1756052452408</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>859.3947033651494</v>
+        <v>859.3947033651497</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>905.0157360453051</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="BJ246" s="372" t="n">
         <v>942.7199139126482</v>
@@ -49106,28 +49106,28 @@
         </is>
       </c>
       <c r="BS246" s="391" t="n">
-        <v>127420166.0637997</v>
+        <v>127443243.0133614</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>143078447.3193781</v>
+        <v>143078447.3193782</v>
       </c>
       <c r="BU246" s="375" t="n">
-        <v>159308459.9678397</v>
+        <v>159308459.9678395</v>
       </c>
       <c r="BV246" s="375" t="n">
-        <v>176996275.2928464</v>
+        <v>176996275.2928465</v>
       </c>
       <c r="BW246" s="392" t="n">
         <v>200399456.4644607</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>808.029263805405</v>
+        <v>808.1756052452408</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>859.3947033651494</v>
+        <v>859.3947033651497</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>905.0157360453051</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="CA246" s="372" t="n">
         <v>942.7199139126482</v>
@@ -49145,7 +49145,7 @@
         </is>
       </c>
       <c r="C247" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D247" s="368" t="n">
         <v>53602589.259965</v>
@@ -49160,7 +49160,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H247" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I247" s="372" t="n">
         <v>1655.286013279789</v>
@@ -49180,7 +49180,7 @@
         </is>
       </c>
       <c r="T247" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U247" s="375" t="n">
         <v>53602589.259965</v>
@@ -49195,7 +49195,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y247" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z247" s="372" t="n">
         <v>1655.286013279789</v>
@@ -49215,25 +49215,25 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>49640360.26519075</v>
+        <v>49646837.82727075</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996551</v>
       </c>
       <c r="AM247" s="368" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.44804496</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965886</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>72697882.80520254</v>
+        <v>72697882.80520257</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>1559.512140047496</v>
+        <v>1559.715640518639</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.28601327408</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49242,7 +49242,7 @@
         <v>1815.921500581826</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>1911.879093764564</v>
+        <v>1911.879093764565</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49250,25 +49250,25 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>49640360.26519075</v>
+        <v>49646837.82727075</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996551</v>
       </c>
       <c r="BD247" s="375" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.44804496</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965886</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>72697882.80520254</v>
+        <v>72697882.80520257</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>1559.512140047496</v>
+        <v>1559.715640518639</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.28601327408</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49277,7 +49277,7 @@
         <v>1815.921500581826</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>1911.879093764564</v>
+        <v>1911.879093764565</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49285,25 +49285,25 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>50132747.34533638</v>
+        <v>50139289.15892185</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>54567686.23948944</v>
+        <v>54567686.23948946</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>59834859.82321822</v>
+        <v>59834859.8232182</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>66366095.55613158</v>
+        <v>66366095.55613156</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>75327072.67030129</v>
+        <v>75327072.67030133</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>1559.512140047496</v>
+        <v>1559.715640518639</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.28601327408</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49312,7 +49312,7 @@
         <v>1815.921500581826</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>1911.879093764564</v>
+        <v>1911.879093764565</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49324,7 +49324,7 @@
         </is>
       </c>
       <c r="C248" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D248" s="368" t="n">
         <v>30609035.168748</v>
@@ -49339,7 +49339,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H248" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I248" s="372" t="n">
         <v>2485.680463849397</v>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="T248" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U248" s="375" t="n">
         <v>30609035.168748</v>
@@ -49374,7 +49374,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y248" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z248" s="372" t="n">
         <v>2485.680463849397</v>
@@ -49394,31 +49394,31 @@
         </is>
       </c>
       <c r="AK248" s="506" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874771</v>
       </c>
       <c r="AM248" s="368" t="n">
-        <v>34281145.60176641</v>
+        <v>34281145.6017664</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945265</v>
       </c>
       <c r="AO248" s="380" t="n">
-        <v>43774095.21109042</v>
+        <v>43774095.21109044</v>
       </c>
       <c r="AP248" s="381" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858962</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.680463852199</v>
       </c>
       <c r="AR248" s="372" t="n">
         <v>2610.628996359972</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204231</v>
       </c>
       <c r="AT248" s="382" t="n">
         <v>2797.7873408409</v>
@@ -49429,31 +49429,31 @@
         </is>
       </c>
       <c r="BB248" s="391" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874771</v>
       </c>
       <c r="BD248" s="375" t="n">
-        <v>34281145.60176641</v>
+        <v>34281145.6017664</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945265</v>
       </c>
       <c r="BF248" s="392" t="n">
-        <v>43774095.21109042</v>
+        <v>43774095.21109044</v>
       </c>
       <c r="BG248" s="386" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858962</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.680463852199</v>
       </c>
       <c r="BI248" s="372" t="n">
         <v>2610.628996359972</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204231</v>
       </c>
       <c r="BK248" s="387" t="n">
         <v>2797.7873408409</v>
@@ -49464,31 +49464,31 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>27524559.52788394</v>
+        <v>27527373.59848612</v>
       </c>
       <c r="BT248" s="375" t="n">
-        <v>30832725.79709065</v>
+        <v>30832725.79709063</v>
       </c>
       <c r="BU248" s="375" t="n">
         <v>34674878.53744324</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>39141702.84725134</v>
+        <v>39141702.84725133</v>
       </c>
       <c r="BW248" s="392" t="n">
-        <v>44556567.68142487</v>
+        <v>44556567.68142489</v>
       </c>
       <c r="BX248" s="386" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858962</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.680463852199</v>
       </c>
       <c r="BZ248" s="372" t="n">
         <v>2610.628996359972</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204231</v>
       </c>
       <c r="CB248" s="387" t="n">
         <v>2797.7873408409</v>
@@ -49579,13 +49579,13 @@
         <v>313016581.3406088</v>
       </c>
       <c r="AM249" s="408" t="n">
-        <v>353845923.7850232</v>
+        <v>353845923.7850233</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224733</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647987</v>
       </c>
       <c r="AP249" s="410" t="n">
         <v>12521.32949520669</v>
@@ -49614,13 +49614,13 @@
         <v>313016581.3406088</v>
       </c>
       <c r="BD249" s="420" t="n">
-        <v>353845923.7850232</v>
+        <v>353845923.7850233</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224733</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647987</v>
       </c>
       <c r="BG249" s="416" t="n">
         <v>12521.32949520669</v>
@@ -49649,13 +49649,13 @@
         <v>304550625.5079275</v>
       </c>
       <c r="BU249" s="420" t="n">
-        <v>344413772.2410913</v>
+        <v>344413772.2410914</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>389867207.5569915</v>
+        <v>389867207.5569914</v>
       </c>
       <c r="BW249" s="421" t="n">
-        <v>446500063.8135937</v>
+        <v>446500063.8135938</v>
       </c>
       <c r="BX249" s="416" t="n">
         <v>12521.32949520669</v>
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="C250" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D250" s="425" t="n">
         <v>538493761.125447</v>
@@ -49697,7 +49697,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="H250" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I250" s="427" t="n">
         <v>2306.219676493023</v>
@@ -49717,7 +49717,7 @@
         </is>
       </c>
       <c r="T250" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U250" s="430" t="n">
         <v>538493761.125447</v>
@@ -49732,7 +49732,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="Y250" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z250" s="433" t="n">
         <v>2306.219676493023</v>
@@ -49752,34 +49752,34 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>481161614.8533118</v>
+        <v>481193830.9101717</v>
       </c>
       <c r="AL250" s="408" t="n">
         <v>538476579.7954477</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>602828595.0017829</v>
+        <v>602828595.0017827</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.577896</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>769448594.4916773</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="AP250" s="436" t="n">
-        <v>2163.75605083753</v>
+        <v>2163.900924588507</v>
       </c>
       <c r="AQ250" s="437" t="n">
         <v>2306.26657650218</v>
       </c>
       <c r="AR250" s="437" t="n">
-        <v>2446.296897853602</v>
+        <v>2446.296897853601</v>
       </c>
       <c r="AS250" s="437" t="n">
         <v>2570.842398787373</v>
       </c>
       <c r="AT250" s="438" t="n">
-        <v>2709.041941852853</v>
+        <v>2709.041941852854</v>
       </c>
       <c r="BA250" s="155" t="inlineStr">
         <is>
@@ -49787,34 +49787,34 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>481161614.8533118</v>
+        <v>481193830.9101717</v>
       </c>
       <c r="BC250" s="440" t="n">
         <v>538476579.7954477</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>602828595.0017829</v>
+        <v>602828595.0017827</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.577896</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>769448594.4916773</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="BG250" s="442" t="n">
-        <v>2163.75605083753</v>
+        <v>2163.900924588507</v>
       </c>
       <c r="BH250" s="443" t="n">
         <v>2306.26657650218</v>
       </c>
       <c r="BI250" s="443" t="n">
-        <v>2446.296897853602</v>
+        <v>2446.296897853601</v>
       </c>
       <c r="BJ250" s="443" t="n">
         <v>2570.842398787373</v>
       </c>
       <c r="BK250" s="444" t="n">
-        <v>2709.041941852853</v>
+        <v>2709.041941852854</v>
       </c>
       <c r="BR250" s="155" t="inlineStr">
         <is>
@@ -49822,22 +49822,22 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>474951381.275288</v>
+        <v>474983814.1090374</v>
       </c>
       <c r="BT250" s="440" t="n">
         <v>533029484.8638858</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>598231970.5695925</v>
+        <v>598231970.5695924</v>
       </c>
       <c r="BV250" s="440" t="n">
         <v>672371281.2532208</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>766783160.6297805</v>
+        <v>766783160.6297807</v>
       </c>
       <c r="BX250" s="442" t="n">
-        <v>2128.802545631967</v>
+        <v>2128.947914403961</v>
       </c>
       <c r="BY250" s="443" t="n">
         <v>2262.185456546918</v>
@@ -49849,7 +49849,7 @@
         <v>2509.778431754753</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>2639.541171375336</v>
+        <v>2639.541171375337</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51872,7 +51872,7 @@
         </is>
       </c>
       <c r="C264" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D264" s="368" t="n">
         <v>141265555.356126</v>
@@ -51887,7 +51887,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H264" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I264" s="372" t="n">
         <v>859.4354544219096</v>
@@ -51907,7 +51907,7 @@
         </is>
       </c>
       <c r="T264" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U264" s="375" t="n">
         <v>141265555.356126</v>
@@ -51922,7 +51922,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y264" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z264" s="372" t="n">
         <v>859.4354544219096</v>
@@ -51942,13 +51942,13 @@
         </is>
       </c>
       <c r="AK264" s="506" t="n">
-        <v>126617344.1039845</v>
+        <v>126640275.6551964</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261257</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>156336436.1669483</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="AN264" s="368" t="n">
         <v>172797502.0263112</v>
@@ -51957,19 +51957,19 @@
         <v>194794539.8105857</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>808.0292638054075</v>
+        <v>808.1756052452382</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>859.3947033651517</v>
+        <v>859.3947033651516</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>905.015736045306</v>
+        <v>905.0157360453051</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>942.719913912647</v>
+        <v>942.7199139126471</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>989.1578434875772</v>
+        <v>989.1578434875764</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51977,13 +51977,13 @@
         </is>
       </c>
       <c r="BB264" s="391" t="n">
-        <v>126617344.1039845</v>
+        <v>126640275.6551964</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261257</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>156336436.1669483</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="BE264" s="375" t="n">
         <v>172797502.0263112</v>
@@ -51992,19 +51992,19 @@
         <v>194794539.8105857</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>808.0292638054075</v>
+        <v>808.1756052452382</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>859.3947033651517</v>
+        <v>859.3947033651516</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>905.015736045306</v>
+        <v>905.0157360453051</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>942.719913912647</v>
+        <v>942.7199139126471</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>989.1578434875772</v>
+        <v>989.1578434875764</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,13 +52012,13 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>127420166.0637997</v>
+        <v>127443243.0133614</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>143078447.3193781</v>
+        <v>143078447.3193782</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>159308459.9678397</v>
+        <v>159308459.9678395</v>
       </c>
       <c r="BV264" s="375" t="n">
         <v>176996275.2928464</v>
@@ -52027,22 +52027,22 @@
         <v>200399456.4644607</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>808.0292638054075</v>
+        <v>808.1756052452382</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>859.3947033651517</v>
+        <v>859.3947033651516</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>905.015736045306</v>
+        <v>905.0157360453051</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>942.719913912647</v>
+        <v>942.7199139126471</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>989.1578434875772</v>
+        <v>989.1578434875764</v>
       </c>
       <c r="CI264" s="396" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CJ264" s="397" t="n">
         <v>1</v>
@@ -52051,28 +52051,28 @@
         <v>1</v>
       </c>
       <c r="CL264" s="397" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="CM264" s="398" t="n">
-        <v>1.000000000000002</v>
+        <v>1.000000000000003</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.9999999999999928</v>
+        <v>0.999999999999993</v>
       </c>
       <c r="CO264" s="103" t="n">
         <v>1.000000000000016</v>
       </c>
       <c r="CP264" s="103" t="n">
-        <v>1.000000000000011</v>
+        <v>1.000000000000012</v>
       </c>
       <c r="CQ264" s="103" t="n">
-        <v>0.9999999999999879</v>
+        <v>0.9999999999999876</v>
       </c>
       <c r="CR264" s="104" t="n">
         <v>1.000000000000051</v>
       </c>
       <c r="CT264" s="396" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CU264" s="397" t="n">
         <v>1</v>
@@ -52081,10 +52081,10 @@
         <v>1</v>
       </c>
       <c r="CW264" s="397" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="CX264" s="398" t="n">
-        <v>1.000000000000002</v>
+        <v>1.000000000000003</v>
       </c>
       <c r="CY264" s="102" t="n">
         <v>1.012460167073759</v>
@@ -52093,10 +52093,10 @@
         <v>1.012992901858759</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>1.013514104921967</v>
+        <v>1.013514104921969</v>
       </c>
       <c r="DB264" s="103" t="n">
-        <v>1.013928837783293</v>
+        <v>1.013928837783292</v>
       </c>
       <c r="DC264" s="104" t="n">
         <v>1.014213282022972</v>
@@ -52117,7 +52117,7 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>91214772.24990854</v>
+        <v>91237642.06254259</v>
       </c>
       <c r="DL264" s="375" t="n">
         <v>104988005.1745399</v>
@@ -52126,10 +52126,10 @@
         <v>118016580.2209291</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>131624915.6046436</v>
+        <v>131624915.6046437</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>150667262.2450482</v>
+        <v>150667262.2450481</v>
       </c>
     </row>
     <row r="265">
@@ -52139,7 +52139,7 @@
         </is>
       </c>
       <c r="C265" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D265" s="368" t="n">
         <v>53602589.259965</v>
@@ -52154,7 +52154,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H265" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I265" s="372" t="n">
         <v>1655.286013279789</v>
@@ -52174,7 +52174,7 @@
         </is>
       </c>
       <c r="T265" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U265" s="375" t="n">
         <v>53602589.259965</v>
@@ -52189,7 +52189,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y265" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z265" s="372" t="n">
         <v>1655.286013279789</v>
@@ -52209,34 +52209,34 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>49640360.26519075</v>
+        <v>49646837.82727075</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996551</v>
       </c>
       <c r="AM265" s="368" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.44804496</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965886</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>72697882.80520254</v>
+        <v>72697882.80520257</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518628</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.28601327406</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>1741.357253135673</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="AS265" s="372" t="n">
         <v>1815.92150058184</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52244,34 +52244,34 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>49640360.26519075</v>
+        <v>49646837.82727075</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996551</v>
       </c>
       <c r="BD265" s="375" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.44804496</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965886</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>72697882.80520254</v>
+        <v>72697882.80520257</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518628</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.28601327406</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>1741.357253135673</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="BJ265" s="372" t="n">
         <v>1815.92150058184</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,37 +52279,37 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>50132747.34533639</v>
+        <v>50139289.15892185</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>54567686.23948944</v>
+        <v>54567686.23948947</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>59834859.82321823</v>
+        <v>59834859.8232182</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>66366095.55613158</v>
+        <v>66366095.55613156</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>75327072.6703013</v>
+        <v>75327072.67030133</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518628</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.28601327406</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>1741.357253135673</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="CA265" s="372" t="n">
         <v>1815.92150058184</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="CI265" s="396" t="n">
-        <v>0.999999999999995</v>
+        <v>0.9999999999999958</v>
       </c>
       <c r="CJ265" s="397" t="n">
         <v>1.000000000000002</v>
@@ -52318,13 +52318,13 @@
         <v>1.000000000000005</v>
       </c>
       <c r="CL265" s="397" t="n">
-        <v>0.9999999999999988</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CM265" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000006</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999998904</v>
+        <v>0.9999999999998905</v>
       </c>
       <c r="CO265" s="103" t="n">
         <v>1.00000000000004</v>
@@ -52333,13 +52333,13 @@
         <v>1.000000000000254</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.9999999999999182</v>
+        <v>0.9999999999999185</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>1.000000000000213</v>
+        <v>1.000000000000212</v>
       </c>
       <c r="CT265" s="396" t="n">
-        <v>0.999999999999995</v>
+        <v>0.9999999999999958</v>
       </c>
       <c r="CU265" s="397" t="n">
         <v>1.000000000000002</v>
@@ -52348,10 +52348,10 @@
         <v>1.000000000000005</v>
       </c>
       <c r="CW265" s="397" t="n">
-        <v>0.9999999999999988</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CX265" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000006</v>
       </c>
       <c r="CY265" s="102" t="n">
         <v>1.010821595180418</v>
@@ -52360,7 +52360,7 @@
         <v>1.011287059486804</v>
       </c>
       <c r="DA265" s="103" t="n">
-        <v>1.011865406606377</v>
+        <v>1.011865406606378</v>
       </c>
       <c r="DB265" s="103" t="n">
         <v>1.012224134246557</v>
@@ -52384,19 +52384,19 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>34750578.12387209</v>
+        <v>34757061.96015742</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>39059424.72251657</v>
       </c>
       <c r="DM265" s="375" t="n">
-        <v>43435991.2510025</v>
+        <v>43435991.25100248</v>
       </c>
       <c r="DN265" s="375" t="n">
         <v>48299721.45664501</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>55445858.27453825</v>
+        <v>55445858.27453823</v>
       </c>
     </row>
     <row r="266">
@@ -52406,7 +52406,7 @@
         </is>
       </c>
       <c r="C266" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D266" s="368" t="n">
         <v>30609035.168748</v>
@@ -52421,7 +52421,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H266" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I266" s="372" t="n">
         <v>2485.680463849397</v>
@@ -52441,7 +52441,7 @@
         </is>
       </c>
       <c r="T266" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U266" s="375" t="n">
         <v>30609035.168748</v>
@@ -52456,7 +52456,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y266" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z266" s="372" t="n">
         <v>2485.680463849397</v>
@@ -52476,34 +52476,34 @@
         </is>
       </c>
       <c r="AK266" s="506" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874771</v>
       </c>
       <c r="AM266" s="368" t="n">
-        <v>34281145.60176641</v>
+        <v>34281145.6017664</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945265</v>
       </c>
       <c r="AO266" s="380" t="n">
-        <v>43774095.21109042</v>
+        <v>43774095.21109044</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2485.680463852156</v>
+        <v>2485.680463852155</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2610.628996359927</v>
+        <v>2610.628996359926</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204243</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52511,34 +52511,34 @@
         </is>
       </c>
       <c r="BB266" s="391" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874771</v>
       </c>
       <c r="BD266" s="375" t="n">
-        <v>34281145.60176641</v>
+        <v>34281145.6017664</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945265</v>
       </c>
       <c r="BF266" s="392" t="n">
-        <v>43774095.21109042</v>
+        <v>43774095.21109044</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2485.680463852156</v>
+        <v>2485.680463852155</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2610.628996359927</v>
+        <v>2610.628996359926</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204243</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52546,37 +52546,37 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>27524559.52788394</v>
+        <v>27527373.59848612</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>30832725.79709065</v>
+        <v>30832725.79709063</v>
       </c>
       <c r="BU266" s="375" t="n">
-        <v>34674878.53744324</v>
+        <v>34674878.53744323</v>
       </c>
       <c r="BV266" s="375" t="n">
-        <v>39141702.84725134</v>
+        <v>39141702.84725133</v>
       </c>
       <c r="BW266" s="392" t="n">
-        <v>44556567.68142486</v>
+        <v>44556567.68142488</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2485.680463852156</v>
+        <v>2485.680463852155</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2610.628996359927</v>
+        <v>2610.628996359926</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204243</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="CI266" s="396" t="n">
-        <v>0.999999999999993</v>
+        <v>0.9999999999999926</v>
       </c>
       <c r="CJ266" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52585,10 +52585,10 @@
         <v>1.000000000000021</v>
       </c>
       <c r="CL266" s="397" t="n">
-        <v>0.9999999999999699</v>
+        <v>0.9999999999999705</v>
       </c>
       <c r="CM266" s="398" t="n">
-        <v>0.9999999999999597</v>
+        <v>0.9999999999999596</v>
       </c>
       <c r="CN266" s="102" t="n">
         <v>0.9999999999999944</v>
@@ -52600,13 +52600,13 @@
         <v>1.000000000000113</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999997716</v>
+        <v>0.9999999999997717</v>
       </c>
       <c r="CR266" s="104" t="n">
-        <v>0.999999999999751</v>
+        <v>0.9999999999997506</v>
       </c>
       <c r="CT266" s="396" t="n">
-        <v>0.999999999999993</v>
+        <v>0.9999999999999926</v>
       </c>
       <c r="CU266" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52615,13 +52615,13 @@
         <v>1.000000000000021</v>
       </c>
       <c r="CW266" s="397" t="n">
-        <v>0.9999999999999699</v>
+        <v>0.9999999999999705</v>
       </c>
       <c r="CX266" s="398" t="n">
-        <v>0.9999999999999597</v>
+        <v>0.9999999999999596</v>
       </c>
       <c r="CY266" s="102" t="n">
-        <v>1.011153716208353</v>
+        <v>1.011153716208352</v>
       </c>
       <c r="CZ266" s="103" t="n">
         <v>1.011529745696788</v>
@@ -52651,7 +52651,7 @@
         <v>0</v>
       </c>
       <c r="DK266" s="391" t="n">
-        <v>18936636.2269968</v>
+        <v>18939430.84554336</v>
       </c>
       <c r="DL266" s="375" t="n">
         <v>21655757.8344942</v>
@@ -52663,7 +52663,7 @@
         <v>28165319.75429519</v>
       </c>
       <c r="DO266" s="392" t="n">
-        <v>32487496.48842778</v>
+        <v>32487496.48842776</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1" thickBot="1">
@@ -52749,25 +52749,25 @@
         <v>313016581.3406088</v>
       </c>
       <c r="AM267" s="408" t="n">
-        <v>353845923.7850232</v>
+        <v>353845923.7850233</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224733</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647987</v>
       </c>
       <c r="AP267" s="410" t="n">
         <v>12521.3294952065</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>12813.16039477739</v>
+        <v>12813.16039477738</v>
       </c>
       <c r="AR267" s="411" t="n">
         <v>13089.82884659031</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="AT267" s="412" t="n">
         <v>13705.7889236738</v>
@@ -52784,25 +52784,25 @@
         <v>313016581.3406088</v>
       </c>
       <c r="BD267" s="420" t="n">
-        <v>353845923.7850232</v>
+        <v>353845923.7850233</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224733</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647987</v>
       </c>
       <c r="BG267" s="416" t="n">
         <v>12521.3294952065</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>12813.16039477739</v>
+        <v>12813.16039477738</v>
       </c>
       <c r="BI267" s="417" t="n">
         <v>13089.82884659031</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="BK267" s="418" t="n">
         <v>13705.7889236738</v>
@@ -52819,25 +52819,25 @@
         <v>304550625.5079275</v>
       </c>
       <c r="BU267" s="420" t="n">
-        <v>344413772.2410913</v>
+        <v>344413772.2410914</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>389867207.5569916</v>
+        <v>389867207.5569914</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>446500063.8135937</v>
+        <v>446500063.8135938</v>
       </c>
       <c r="BX267" s="416" t="n">
         <v>12521.3294952065</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>12813.16039477739</v>
+        <v>12813.16039477738</v>
       </c>
       <c r="BZ267" s="417" t="n">
         <v>13089.82884659031</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="CB267" s="418" t="n">
         <v>13705.7889236738</v>
@@ -52846,10 +52846,10 @@
         <v>0.9999999999997755</v>
       </c>
       <c r="CJ267" s="423" t="n">
-        <v>1.000000000000281</v>
+        <v>1.000000000000282</v>
       </c>
       <c r="CK267" s="423" t="n">
-        <v>0.9999999999997824</v>
+        <v>0.9999999999997825</v>
       </c>
       <c r="CL267" s="423" t="n">
         <v>1.000000000000173</v>
@@ -52858,7 +52858,7 @@
         <v>1.000000000000534</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>1.000000000000436</v>
+        <v>1.000000000000435</v>
       </c>
       <c r="CO267" s="133" t="n">
         <v>0.9999999999995581</v>
@@ -52867,19 +52867,19 @@
         <v>1.000000000000194</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>0.9999999999997883</v>
+        <v>0.9999999999997886</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>0.9999999999996199</v>
+        <v>0.9999999999996195</v>
       </c>
       <c r="CT267" s="422" t="n">
         <v>0.9999999999997755</v>
       </c>
       <c r="CU267" s="423" t="n">
-        <v>1.000000000000281</v>
+        <v>1.000000000000282</v>
       </c>
       <c r="CV267" s="423" t="n">
-        <v>0.9999999999997824</v>
+        <v>0.9999999999997825</v>
       </c>
       <c r="CW267" s="423" t="n">
         <v>1.000000000000173</v>
@@ -52930,7 +52930,7 @@
         <v>246346883.7616723</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>286688358.6587306</v>
+        <v>286688358.6587307</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -52940,7 +52940,7 @@
         </is>
       </c>
       <c r="C268" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D268" s="425" t="n">
         <v>538493761.125447</v>
@@ -52955,7 +52955,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="H268" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I268" s="427" t="n">
         <v>2306.219676493023</v>
@@ -52975,7 +52975,7 @@
         </is>
       </c>
       <c r="T268" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U268" s="430" t="n">
         <v>538493761.125447</v>
@@ -52990,7 +52990,7 @@
         <v>769480271.1597129</v>
       </c>
       <c r="Y268" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z268" s="433" t="n">
         <v>2306.219676493023</v>
@@ -53010,28 +53010,28 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>481161614.8533118</v>
+        <v>481193830.9101717</v>
       </c>
       <c r="AL268" s="408" t="n">
         <v>538476579.7954477</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>602828595.0017829</v>
+        <v>602828595.0017827</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.577896</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>769448594.4916773</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>2163.756050837529</v>
+        <v>2163.900924588495</v>
       </c>
       <c r="AQ268" s="437" t="n">
         <v>2306.266576502182</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>2446.296897853598</v>
+        <v>2446.296897853597</v>
       </c>
       <c r="AS268" s="437" t="n">
         <v>2570.842398787376</v>
@@ -53045,28 +53045,28 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>481161614.8533118</v>
+        <v>481193830.9101717</v>
       </c>
       <c r="BC268" s="440" t="n">
         <v>538476579.7954477</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>602828595.0017829</v>
+        <v>602828595.0017827</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.577896</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>769448594.4916773</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>2163.756050837529</v>
+        <v>2163.900924588495</v>
       </c>
       <c r="BH268" s="443" t="n">
         <v>2306.266576502182</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>2446.296897853598</v>
+        <v>2446.296897853597</v>
       </c>
       <c r="BJ268" s="443" t="n">
         <v>2570.842398787376</v>
@@ -53080,22 +53080,22 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>474951381.275288</v>
+        <v>474983814.1090373</v>
       </c>
       <c r="BT268" s="440" t="n">
         <v>533029484.8638858</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>598231970.5695925</v>
+        <v>598231970.5695924</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>672371281.2532209</v>
+        <v>672371281.2532207</v>
       </c>
       <c r="BW268" s="441" t="n">
         <v>766783160.6297807</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>2128.802545631966</v>
+        <v>2128.947914403949</v>
       </c>
       <c r="BY268" s="443" t="n">
         <v>2262.185456546919</v>
@@ -53104,10 +53104,10 @@
         <v>2393.088848784539</v>
       </c>
       <c r="CA268" s="443" t="n">
-        <v>2509.778431754757</v>
+        <v>2509.778431754756</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2639.541171375331</v>
+        <v>2639.541171375329</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,19 +53125,19 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>308699048.2713143</v>
+        <v>308731196.5387801</v>
       </c>
       <c r="DL268" s="440" t="n">
-        <v>353793145.220949</v>
+        <v>353793145.2209489</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>402085870.8963986</v>
+        <v>402085870.8963987</v>
       </c>
       <c r="DN268" s="440" t="n">
-        <v>454436840.577256</v>
+        <v>454436840.5772561</v>
       </c>
       <c r="DO268" s="441" t="n">
-        <v>525288975.6667447</v>
+        <v>525288975.6667448</v>
       </c>
     </row>
     <row r="269">
@@ -58406,7 +58406,7 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178444</v>
       </c>
       <c r="BY294" s="190" t="n">
         <v>2163.155319482305</v>
@@ -58418,10 +58418,10 @@
         <v>2615.148328173791</v>
       </c>
       <c r="CB294" s="198" t="n">
-        <v>2879.554573332821</v>
+        <v>2879.554573332822</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178444</v>
       </c>
       <c r="CD294" s="200" t="n">
         <v>2163.155319482305</v>
@@ -58433,7 +58433,7 @@
         <v>2615.148328173791</v>
       </c>
       <c r="CG294" s="201" t="n">
-        <v>2879.554573332821</v>
+        <v>2879.554573332822</v>
       </c>
       <c r="CI294" s="199" t="n">
         <v>0</v>
@@ -58463,7 +58463,7 @@
         <v>0</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178444</v>
       </c>
       <c r="CX294" s="200" t="n">
         <v>2163.155319482305</v>
@@ -58475,7 +58475,7 @@
         <v>2615.148328173791</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>2879.554573332821</v>
+        <v>2879.554573332822</v>
       </c>
     </row>
     <row r="295">
@@ -58701,34 +58701,34 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>347.8756485031443</v>
+        <v>347.8756485031444</v>
       </c>
       <c r="BY295" s="190" t="n">
         <v>372.0859813342885</v>
       </c>
       <c r="BZ295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314257</v>
       </c>
       <c r="CA295" s="190" t="n">
         <v>446.7528256294977</v>
       </c>
       <c r="CB295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.971096646771</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>347.8756485031443</v>
+        <v>347.8756485031444</v>
       </c>
       <c r="CD295" s="190" t="n">
         <v>372.0859813342885</v>
       </c>
       <c r="CE295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314257</v>
       </c>
       <c r="CF295" s="190" t="n">
         <v>446.7528256294977</v>
       </c>
       <c r="CG295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.971096646771</v>
       </c>
       <c r="CI295" s="197" t="n">
         <v>0</v>
@@ -58758,19 +58758,19 @@
         <v>0</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>347.8756485031443</v>
+        <v>347.8756485031444</v>
       </c>
       <c r="CX295" s="190" t="n">
         <v>372.0859813342885</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314257</v>
       </c>
       <c r="CZ295" s="190" t="n">
         <v>446.7528256294977</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.971096646771</v>
       </c>
     </row>
     <row r="296">
@@ -59291,31 +59291,31 @@
         <v>0</v>
       </c>
       <c r="BX297" s="211" t="n">
-        <v>663.9327169755791</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>753.6182474419337</v>
+        <v>753.6182474419338</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>854.1693686245005</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CA297" s="212" t="n">
-        <v>950.5574286398272</v>
+        <v>950.5574286398273</v>
       </c>
       <c r="CB297" s="213" t="n">
         <v>1093.349295717359</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>663.9327169755791</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CD297" s="212" t="n">
-        <v>753.6182474419337</v>
+        <v>753.6182474419338</v>
       </c>
       <c r="CE297" s="212" t="n">
-        <v>854.1693686245005</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CF297" s="212" t="n">
-        <v>950.5574286398272</v>
+        <v>950.5574286398273</v>
       </c>
       <c r="CG297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59348,16 +59348,16 @@
         <v>0</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>663.9327169755791</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>753.6182474419337</v>
+        <v>753.6182474419338</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>854.1693686245005</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>950.5574286398272</v>
+        <v>950.5574286398273</v>
       </c>
       <c r="DA297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59586,31 +59586,31 @@
         <v>0</v>
       </c>
       <c r="BX298" s="221" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028078</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652925</v>
       </c>
       <c r="BZ298" s="222" t="n">
         <v>3798.519391217832</v>
       </c>
       <c r="CA298" s="222" t="n">
-        <v>4186.715162875506</v>
+        <v>4186.715162875507</v>
       </c>
       <c r="CB298" s="214" t="n">
         <v>4656.789813562893</v>
       </c>
       <c r="CC298" s="222" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028078</v>
       </c>
       <c r="CD298" s="222" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652925</v>
       </c>
       <c r="CE298" s="222" t="n">
         <v>3798.519391217832</v>
       </c>
       <c r="CF298" s="222" t="n">
-        <v>4186.715162875506</v>
+        <v>4186.715162875507</v>
       </c>
       <c r="CG298" s="214" t="n">
         <v>4656.789813562893</v>
@@ -59643,10 +59643,10 @@
         <v>0</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028078</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652925</v>
       </c>
       <c r="CY298" s="212" t="n">
         <v>3798.519391217832</v>
@@ -59655,7 +59655,7 @@
         <v>4186.715162875506</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>4656.789813562892</v>
+        <v>4656.789813562893</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -71183,49 +71183,49 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>1587676.557723578</v>
+        <v>1587964.10037067</v>
       </c>
       <c r="BT368" s="375" t="n">
-        <v>1859004.224119246</v>
+        <v>1859004.224119245</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>2152911.242958716</v>
+        <v>2152911.242958714</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>2465352.406804799</v>
+        <v>2465352.4068048</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>2848333.991962684</v>
+        <v>2848333.991962682</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>808.0292638054075</v>
+        <v>808.1756052452382</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>859.3947033651517</v>
+        <v>859.3947033651516</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>905.0157360453061</v>
+        <v>905.0157360453051</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>942.719913912647</v>
+        <v>942.7199139126473</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>989.1578434875771</v>
+        <v>989.1578434875763</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>1587676.557723578</v>
+        <v>1587964.10037067</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>1859004.224119246</v>
+        <v>1859004.224119245</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>2152911.242958716</v>
+        <v>2152911.242958714</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>2465352.406804799</v>
+        <v>2465352.4068048</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>2848333.991962684</v>
+        <v>2848333.991962682</v>
       </c>
     </row>
     <row r="369">
@@ -71375,49 +71375,49 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>542516.2970675451</v>
+        <v>542587.0899259149</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>615908.7206380002</v>
+        <v>615908.7206380006</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>709964.941013598</v>
+        <v>709964.9410135967</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>811268.0615062945</v>
+        <v>811268.0615062946</v>
       </c>
       <c r="BW369" s="392" t="n">
-        <v>938677.3753216255</v>
+        <v>938677.3753216261</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518628</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.28601327406</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1741.357253135673</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="CA369" s="372" t="n">
         <v>1815.92150058184</v>
       </c>
       <c r="CB369" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>542516.2970675451</v>
+        <v>542587.0899259149</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>615908.7206380002</v>
+        <v>615908.7206380006</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>709964.941013598</v>
+        <v>709964.9410135967</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>811268.0615062945</v>
+        <v>811268.0615062946</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>938677.3753216255</v>
+        <v>938677.3753216261</v>
       </c>
     </row>
     <row r="370">
@@ -71567,49 +71567,49 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>307001.125736809</v>
+        <v>307032.5130816964</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>355493.4875794519</v>
+        <v>355493.4875794518</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>411894.9442278919</v>
+        <v>411894.9442278917</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>471930.3932272116</v>
+        <v>471930.3932272114</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195741</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BY370" s="372" t="n">
-        <v>2485.680463852156</v>
+        <v>2485.680463852155</v>
       </c>
       <c r="BZ370" s="372" t="n">
-        <v>2610.628996359927</v>
+        <v>2610.628996359926</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204243</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840877</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>307001.125736809</v>
+        <v>307032.5130816964</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>355493.4875794519</v>
+        <v>355493.4875794518</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>411894.9442278919</v>
+        <v>411894.9442278917</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>471930.3932272116</v>
+        <v>471930.3932272114</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195741</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71759,10 +71759,10 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>8313320.311898906</v>
+        <v>8313320.31189891</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>9656231.480904531</v>
+        <v>9656231.480904529</v>
       </c>
       <c r="BU371" s="420" t="n">
         <v>11180930.84129482</v>
@@ -71771,28 +71771,28 @@
         <v>12713050.33670374</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694953</v>
       </c>
       <c r="BX371" s="416" t="n">
         <v>12521.3294952065</v>
       </c>
       <c r="BY371" s="417" t="n">
-        <v>12813.16039477739</v>
+        <v>12813.16039477738</v>
       </c>
       <c r="BZ371" s="417" t="n">
         <v>13089.82884659031</v>
       </c>
       <c r="CA371" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="CB371" s="418" t="n">
         <v>13705.7889236738</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>8313320.311898906</v>
+        <v>8313320.31189891</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>9656231.480904531</v>
+        <v>9656231.480904529</v>
       </c>
       <c r="CY371" s="420" t="n">
         <v>11180930.84129482</v>
@@ -71801,7 +71801,7 @@
         <v>12713050.33670374</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694953</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71951,49 +71951,49 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>10750514.29242684</v>
+        <v>10750904.01527719</v>
       </c>
       <c r="BT372" s="440" t="n">
         <v>12486637.91324123</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>14455701.96949503</v>
+        <v>14455701.96949502</v>
       </c>
       <c r="BV372" s="440" t="n">
         <v>16461601.19824205</v>
       </c>
       <c r="BW372" s="441" t="n">
-        <v>19311960.7534534</v>
+        <v>19311960.75345341</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3459.703149101259</v>
+        <v>3459.828568717099</v>
       </c>
       <c r="BY372" s="443" t="n">
         <v>3638.429096053079</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>3805.614893770603</v>
+        <v>3805.614893770601</v>
       </c>
       <c r="CA372" s="443" t="n">
-        <v>3931.86556950675</v>
+        <v>3931.865569506749</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>4147.05441443961</v>
+        <v>4147.054414439612</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>10750514.29242684</v>
+        <v>10750904.01527719</v>
       </c>
       <c r="CX372" s="420" t="n">
         <v>12486637.91324123</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>14455701.96949503</v>
+        <v>14455701.96949502</v>
       </c>
       <c r="CZ372" s="420" t="n">
         <v>16461601.19824205</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>19311960.7534534</v>
+        <v>19311960.75345341</v>
       </c>
     </row>
     <row r="375">
